--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$993</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$994</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="299">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -723,12 +723,12 @@
     <t>https://heatlabs.net/playground</t>
   </si>
   <si>
-    <t>https://heatlabs.net/playground/alpha-3-playtest</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/playground/configurator</t>
   </si>
   <si>
+    <t>https://heatlabs.net/playground/countdown</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/playground/game-data</t>
   </si>
   <si>
@@ -880,6 +880,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/tournaments</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/tournaments/brackets</t>
   </si>
   <si>
     <t>https://heatlabs.net/tournaments/open-alpha-1-tournament</t>
@@ -1418,7 +1421,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1428,7 +1431,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="4">
@@ -1532,7 +1535,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="8">
@@ -1626,7 +1629,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1730,7 +1733,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -5657,7 +5660,7 @@
         <v>8</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>15</v>
@@ -5678,7 +5681,7 @@
         <v>8</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>15</v>
@@ -6053,10 +6056,10 @@
         <v>237</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>15</v>
@@ -7145,10 +7148,10 @@
         <v>289</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D273" s="6" t="s">
         <v>15</v>
@@ -7211,7 +7214,7 @@
         <v>7</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>15</v>
@@ -7229,7 +7232,7 @@
         <v>293</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>8</v>
@@ -7250,7 +7253,7 @@
         <v>294</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>8</v>
@@ -7313,16 +7316,16 @@
         <v>297</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D281" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E281" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
@@ -7330,11 +7333,21 @@
       <c r="I281" s="2"/>
     </row>
     <row r="282">
-      <c r="A282" s="16"/>
-      <c r="B282" s="17"/>
-      <c r="C282" s="17"/>
-      <c r="D282" s="17"/>
-      <c r="E282" s="17"/>
+      <c r="A282" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="B282" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C282" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D282" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E282" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
@@ -15161,11 +15174,22 @@
       <c r="H993" s="2"/>
       <c r="I993" s="2"/>
     </row>
+    <row r="994">
+      <c r="A994" s="16"/>
+      <c r="B994" s="17"/>
+      <c r="C994" s="17"/>
+      <c r="D994" s="17"/>
+      <c r="E994" s="17"/>
+      <c r="F994" s="2"/>
+      <c r="G994" s="2"/>
+      <c r="H994" s="2"/>
+      <c r="I994" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$993">
-    <sortState ref="A1:E993">
-      <sortCondition ref="A1:A993"/>
-      <sortCondition ref="D1:D993"/>
+  <autoFilter ref="$A$1:$E$994">
+    <sortState ref="A1:E994">
+      <sortCondition ref="A1:A994"/>
+      <sortCondition ref="D1:D994"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -15175,13 +15199,13 @@
     <mergeCell ref="G13:I13"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C993">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C994">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D993">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D994">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E993">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E994">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15466,7 +15490,8 @@
     <hyperlink r:id="rId278" ref="A279"/>
     <hyperlink r:id="rId279" ref="A280"/>
     <hyperlink r:id="rId280" ref="A281"/>
+    <hyperlink r:id="rId281" ref="A282"/>
   </hyperlinks>
-  <drawing r:id="rId281"/>
+  <drawing r:id="rId282"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -1525,7 +1525,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1535,7 +1535,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
@@ -6059,7 +6059,7 @@
         <v>8</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
         <v>15</v>

--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$994</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$995</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1426" uniqueCount="299">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="300">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -178,6 +178,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/blog/alpha-2-fuel-crit-multiplier</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/blog/are-we-approaching-the-launch</t>
   </si>
   <si>
     <t>https://heatlabs.net/blog/damage-calculation</t>
@@ -1421,7 +1424,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1525,7 +1528,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1629,7 +1632,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1733,7 +1736,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -2279,7 +2282,7 @@
         <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>15</v>
@@ -2293,11 +2296,11 @@
       <c r="I41" s="2"/>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="5" t="s">
         <v>58</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>7</v>
@@ -2314,7 +2317,7 @@
       <c r="I42" s="2"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="14" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="6" t="s">
@@ -2339,10 +2342,10 @@
         <v>60</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>15</v>
@@ -2363,7 +2366,7 @@
         <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>15</v>
@@ -2408,10 +2411,10 @@
         <v>7</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2426,13 +2429,13 @@
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2615,7 +2618,7 @@
         <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>15</v>
@@ -2671,7 +2674,7 @@
       <c r="I59" s="2"/>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B60" s="6" t="s">
@@ -2681,10 +2684,10 @@
         <v>7</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
@@ -2692,7 +2695,7 @@
       <c r="I60" s="2"/>
     </row>
     <row r="61">
-      <c r="A61" s="5" t="s">
+      <c r="A61" s="14" t="s">
         <v>77</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -2720,13 +2723,13 @@
         <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -2734,7 +2737,7 @@
       <c r="I62" s="2"/>
     </row>
     <row r="63">
-      <c r="A63" s="14" t="s">
+      <c r="A63" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B63" s="6" t="s">
@@ -2755,7 +2758,7 @@
       <c r="I63" s="2"/>
     </row>
     <row r="64">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="14" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="6" t="s">
@@ -2801,10 +2804,10 @@
         <v>82</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>15</v>
@@ -2822,16 +2825,16 @@
         <v>83</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C67" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F67" s="2"/>
       <c r="G67" s="2"/>
@@ -2843,16 +2846,16 @@
         <v>84</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -2864,7 +2867,7 @@
         <v>85</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>7</v>
@@ -2909,7 +2912,7 @@
         <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>15</v>
@@ -2948,10 +2951,10 @@
         <v>89</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D73" s="6" t="s">
         <v>15</v>
@@ -2969,10 +2972,10 @@
         <v>90</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>15</v>
@@ -2993,7 +2996,7 @@
         <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>15</v>
@@ -3014,7 +3017,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -3035,7 +3038,7 @@
         <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>15</v>
@@ -3053,7 +3056,7 @@
         <v>94</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>7</v>
@@ -3074,7 +3077,7 @@
         <v>95</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>7</v>
@@ -3161,7 +3164,7 @@
         <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="6" t="s">
         <v>15</v>
@@ -3175,7 +3178,7 @@
       <c r="I83" s="2"/>
     </row>
     <row r="84">
-      <c r="A84" s="14" t="s">
+      <c r="A84" s="5" t="s">
         <v>100</v>
       </c>
       <c r="B84" s="6" t="s">
@@ -3196,20 +3199,20 @@
       <c r="I84" s="2"/>
     </row>
     <row r="85">
-      <c r="A85" s="5" t="s">
+      <c r="A85" s="14" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -3269,10 +3272,10 @@
         <v>7</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -3374,10 +3377,10 @@
         <v>7</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -3395,10 +3398,10 @@
         <v>7</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -3406,14 +3409,14 @@
       <c r="I94" s="2"/>
     </row>
     <row r="95">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="5" t="s">
         <v>111</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>15</v>
@@ -3427,20 +3430,20 @@
       <c r="I95" s="2"/>
     </row>
     <row r="96">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="14" t="s">
         <v>112</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -3452,16 +3455,16 @@
         <v>113</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -3473,16 +3476,16 @@
         <v>114</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -3497,13 +3500,13 @@
         <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -3515,16 +3518,16 @@
         <v>116</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -3536,7 +3539,7 @@
         <v>117</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>7</v>
@@ -3563,10 +3566,10 @@
         <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3584,10 +3587,10 @@
         <v>7</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3599,16 +3602,16 @@
         <v>120</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3620,7 +3623,7 @@
         <v>121</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>7</v>
@@ -3641,7 +3644,7 @@
         <v>122</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>7</v>
@@ -3662,10 +3665,10 @@
         <v>123</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>15</v>
@@ -3686,7 +3689,7 @@
         <v>7</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>15</v>
@@ -3749,7 +3752,7 @@
         <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3770,7 +3773,7 @@
         <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -4103,7 +4106,7 @@
         <v>144</v>
       </c>
       <c r="B128" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>7</v>
@@ -4166,7 +4169,7 @@
         <v>147</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>7</v>
@@ -4187,7 +4190,7 @@
         <v>148</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>7</v>
@@ -4208,7 +4211,7 @@
         <v>149</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>7</v>
@@ -4274,7 +4277,7 @@
         <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -4295,7 +4298,7 @@
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -4337,7 +4340,7 @@
         <v>7</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D139" s="6" t="s">
         <v>15</v>
@@ -4358,7 +4361,7 @@
         <v>7</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -4403,10 +4406,10 @@
         <v>7</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -4424,10 +4427,10 @@
         <v>7</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -4439,7 +4442,7 @@
         <v>160</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C144" s="6" t="s">
         <v>7</v>
@@ -4460,7 +4463,7 @@
         <v>161</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>7</v>
@@ -4568,7 +4571,7 @@
         <v>7</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>15</v>
@@ -4589,7 +4592,7 @@
         <v>7</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>15</v>
@@ -4694,7 +4697,7 @@
         <v>7</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>15</v>
@@ -4736,7 +4739,7 @@
         <v>7</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>15</v>
@@ -4820,7 +4823,7 @@
         <v>7</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>15</v>
@@ -4841,7 +4844,7 @@
         <v>7</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>15</v>
@@ -4967,7 +4970,7 @@
         <v>7</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>15</v>
@@ -4988,7 +4991,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>15</v>
@@ -5090,7 +5093,7 @@
         <v>191</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>7</v>
@@ -5111,7 +5114,7 @@
         <v>192</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>7</v>
@@ -5132,10 +5135,10 @@
         <v>193</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>15</v>
@@ -5153,7 +5156,7 @@
         <v>194</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>8</v>
@@ -5216,7 +5219,7 @@
         <v>197</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>8</v>
@@ -5237,10 +5240,10 @@
         <v>198</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>15</v>
@@ -5258,7 +5261,7 @@
         <v>199</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>7</v>
@@ -5282,7 +5285,7 @@
         <v>8</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>15</v>
@@ -5303,7 +5306,7 @@
         <v>8</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>15</v>
@@ -5321,7 +5324,7 @@
         <v>202</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>7</v>
@@ -5342,10 +5345,10 @@
         <v>203</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D187" s="6" t="s">
         <v>15</v>
@@ -5363,10 +5366,10 @@
         <v>204</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5510,10 +5513,10 @@
         <v>211</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C195" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D195" s="6" t="s">
         <v>15</v>
@@ -5594,7 +5597,7 @@
         <v>215</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C199" s="6" t="s">
         <v>8</v>
@@ -5639,7 +5642,7 @@
         <v>7</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>15</v>
@@ -5657,7 +5660,7 @@
         <v>218</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>7</v>
@@ -5702,7 +5705,7 @@
         <v>8</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>15</v>
@@ -5741,7 +5744,7 @@
         <v>222</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>8</v>
@@ -5765,7 +5768,7 @@
         <v>7</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D207" s="6" t="s">
         <v>15</v>
@@ -5783,7 +5786,7 @@
         <v>224</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>7</v>
@@ -5825,16 +5828,16 @@
         <v>226</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C210" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D210" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E210" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
@@ -5846,16 +5849,16 @@
         <v>227</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -5912,7 +5915,7 @@
         <v>8</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>15</v>
@@ -5954,7 +5957,7 @@
         <v>8</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>15</v>
@@ -5972,7 +5975,7 @@
         <v>233</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>7</v>
@@ -5993,16 +5996,16 @@
         <v>234</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -6014,7 +6017,7 @@
         <v>235</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
@@ -6041,10 +6044,10 @@
         <v>7</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -6056,7 +6059,7 @@
         <v>237</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>7</v>
@@ -6073,7 +6076,7 @@
       <c r="I221" s="2"/>
     </row>
     <row r="222">
-      <c r="A222" s="14" t="s">
+      <c r="A222" s="5" t="s">
         <v>238</v>
       </c>
       <c r="B222" s="6" t="s">
@@ -6094,11 +6097,11 @@
       <c r="I222" s="2"/>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="s">
+      <c r="A223" s="14" t="s">
         <v>239</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>7</v>
@@ -6199,14 +6202,14 @@
       <c r="I227" s="2"/>
     </row>
     <row r="228">
-      <c r="A228" s="14" t="s">
+      <c r="A228" s="5" t="s">
         <v>244</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D228" s="6" t="s">
         <v>15</v>
@@ -6220,14 +6223,14 @@
       <c r="I228" s="2"/>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="s">
+      <c r="A229" s="14" t="s">
         <v>245</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D229" s="6" t="s">
         <v>15</v>
@@ -6245,7 +6248,7 @@
         <v>246</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C230" s="6" t="s">
         <v>7</v>
@@ -6266,16 +6269,16 @@
         <v>247</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D231" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E231" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
@@ -6287,16 +6290,16 @@
         <v>248</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C232" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
@@ -6308,7 +6311,7 @@
         <v>249</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>7</v>
@@ -6350,16 +6353,16 @@
         <v>251</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C235" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
@@ -6371,7 +6374,7 @@
         <v>252</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>7</v>
@@ -6398,10 +6401,10 @@
         <v>7</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
@@ -6430,20 +6433,20 @@
       <c r="I238" s="2"/>
     </row>
     <row r="239">
-      <c r="A239" s="14" t="s">
+      <c r="A239" s="5" t="s">
         <v>255</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -6451,11 +6454,11 @@
       <c r="I239" s="2"/>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="s">
+      <c r="A240" s="14" t="s">
         <v>256</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>7</v>
@@ -6472,20 +6475,20 @@
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="14" t="s">
+      <c r="A241" s="5" t="s">
         <v>257</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -6493,20 +6496,20 @@
       <c r="I241" s="2"/>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="s">
+      <c r="A242" s="14" t="s">
         <v>258</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -6524,10 +6527,10 @@
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6545,10 +6548,10 @@
         <v>7</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -6566,10 +6569,10 @@
         <v>7</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -6703,7 +6706,7 @@
       <c r="I251" s="2"/>
     </row>
     <row r="252">
-      <c r="A252" s="15" t="s">
+      <c r="A252" s="5" t="s">
         <v>268</v>
       </c>
       <c r="B252" s="6" t="s">
@@ -6724,7 +6727,7 @@
       <c r="I252" s="2"/>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="s">
+      <c r="A253" s="15" t="s">
         <v>269</v>
       </c>
       <c r="B253" s="6" t="s">
@@ -6965,10 +6968,10 @@
         <v>7</v>
       </c>
       <c r="D264" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E264" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
@@ -6986,10 +6989,10 @@
         <v>7</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
@@ -7133,10 +7136,10 @@
         <v>7</v>
       </c>
       <c r="D272" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E272" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
@@ -7148,16 +7151,16 @@
         <v>289</v>
       </c>
       <c r="B273" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
@@ -7169,10 +7172,10 @@
         <v>290</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D274" s="6" t="s">
         <v>15</v>
@@ -7235,7 +7238,7 @@
         <v>7</v>
       </c>
       <c r="C277" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D277" s="6" t="s">
         <v>15</v>
@@ -7253,7 +7256,7 @@
         <v>294</v>
       </c>
       <c r="B278" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C278" s="6" t="s">
         <v>8</v>
@@ -7274,7 +7277,7 @@
         <v>295</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>8</v>
@@ -7337,16 +7340,16 @@
         <v>298</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D282" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E282" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
@@ -7354,11 +7357,21 @@
       <c r="I282" s="2"/>
     </row>
     <row r="283">
-      <c r="A283" s="16"/>
-      <c r="B283" s="17"/>
-      <c r="C283" s="17"/>
-      <c r="D283" s="17"/>
-      <c r="E283" s="17"/>
+      <c r="A283" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="B283" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C283" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D283" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E283" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
@@ -15185,11 +15198,22 @@
       <c r="H994" s="2"/>
       <c r="I994" s="2"/>
     </row>
+    <row r="995">
+      <c r="A995" s="16"/>
+      <c r="B995" s="17"/>
+      <c r="C995" s="17"/>
+      <c r="D995" s="17"/>
+      <c r="E995" s="17"/>
+      <c r="F995" s="2"/>
+      <c r="G995" s="2"/>
+      <c r="H995" s="2"/>
+      <c r="I995" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$994">
-    <sortState ref="A1:E994">
-      <sortCondition ref="A1:A994"/>
-      <sortCondition ref="D1:D994"/>
+  <autoFilter ref="$A$1:$E$995">
+    <sortState ref="A1:E995">
+      <sortCondition ref="A1:A995"/>
+      <sortCondition ref="D1:D995"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -15199,13 +15223,13 @@
     <mergeCell ref="G13:I13"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C994">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C995">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D994">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D995">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E994">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E995">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15491,7 +15515,8 @@
     <hyperlink r:id="rId279" ref="A280"/>
     <hyperlink r:id="rId280" ref="A281"/>
     <hyperlink r:id="rId281" ref="A282"/>
+    <hyperlink r:id="rId282" ref="A283"/>
   </hyperlinks>
-  <drawing r:id="rId282"/>
+  <drawing r:id="rId283"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$995</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$996</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1431" uniqueCount="300">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="301">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -784,6 +784,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/steam-news/heat-wrapped-2025-in-review</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/steam-news/human-machine-synergy</t>
   </si>
   <si>
     <t>https://heatlabs.net/steam-news/join-the-lodestar-program</t>
@@ -1424,7 +1427,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1528,7 +1531,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1632,7 +1635,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1736,7 +1739,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -6475,20 +6478,20 @@
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="s">
+      <c r="A241" s="14" t="s">
         <v>257</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -6496,20 +6499,20 @@
       <c r="I241" s="2"/>
     </row>
     <row r="242">
-      <c r="A242" s="14" t="s">
+      <c r="A242" s="5" t="s">
         <v>258</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -6517,20 +6520,20 @@
       <c r="I242" s="2"/>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="s">
+      <c r="A243" s="14" t="s">
         <v>259</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6548,10 +6551,10 @@
         <v>7</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -6569,10 +6572,10 @@
         <v>7</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -6590,10 +6593,10 @@
         <v>7</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -6727,7 +6730,7 @@
       <c r="I252" s="2"/>
     </row>
     <row r="253">
-      <c r="A253" s="15" t="s">
+      <c r="A253" s="5" t="s">
         <v>269</v>
       </c>
       <c r="B253" s="6" t="s">
@@ -6748,7 +6751,7 @@
       <c r="I253" s="2"/>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="s">
+      <c r="A254" s="15" t="s">
         <v>270</v>
       </c>
       <c r="B254" s="6" t="s">
@@ -6989,10 +6992,10 @@
         <v>7</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
@@ -7010,10 +7013,10 @@
         <v>7</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
@@ -7157,10 +7160,10 @@
         <v>7</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
@@ -7172,16 +7175,16 @@
         <v>290</v>
       </c>
       <c r="B274" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
@@ -7193,10 +7196,10 @@
         <v>291</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D275" s="6" t="s">
         <v>15</v>
@@ -7259,7 +7262,7 @@
         <v>7</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D278" s="6" t="s">
         <v>15</v>
@@ -7277,7 +7280,7 @@
         <v>295</v>
       </c>
       <c r="B279" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C279" s="6" t="s">
         <v>8</v>
@@ -7298,7 +7301,7 @@
         <v>296</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>8</v>
@@ -7361,16 +7364,16 @@
         <v>299</v>
       </c>
       <c r="B283" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D283" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E283" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
@@ -7378,11 +7381,21 @@
       <c r="I283" s="2"/>
     </row>
     <row r="284">
-      <c r="A284" s="16"/>
-      <c r="B284" s="17"/>
-      <c r="C284" s="17"/>
-      <c r="D284" s="17"/>
-      <c r="E284" s="17"/>
+      <c r="A284" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="B284" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C284" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D284" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E284" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
@@ -15209,11 +15222,22 @@
       <c r="H995" s="2"/>
       <c r="I995" s="2"/>
     </row>
+    <row r="996">
+      <c r="A996" s="16"/>
+      <c r="B996" s="17"/>
+      <c r="C996" s="17"/>
+      <c r="D996" s="17"/>
+      <c r="E996" s="17"/>
+      <c r="F996" s="2"/>
+      <c r="G996" s="2"/>
+      <c r="H996" s="2"/>
+      <c r="I996" s="2"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$995">
-    <sortState ref="A1:E995">
-      <sortCondition ref="A1:A995"/>
-      <sortCondition ref="D1:D995"/>
+  <autoFilter ref="$A$1:$E$996">
+    <sortState ref="A1:E996">
+      <sortCondition ref="A1:A996"/>
+      <sortCondition ref="D1:D996"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -15223,13 +15247,13 @@
     <mergeCell ref="G13:I13"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C995">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C996">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D995">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D996">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E995">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E996">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15516,7 +15540,8 @@
     <hyperlink r:id="rId280" ref="A281"/>
     <hyperlink r:id="rId281" ref="A282"/>
     <hyperlink r:id="rId282" ref="A283"/>
+    <hyperlink r:id="rId283" ref="A284"/>
   </hyperlinks>
-  <drawing r:id="rId283"/>
+  <drawing r:id="rId284"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -1531,7 +1531,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1541,7 +1541,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>212</v>
+        <v>215</v>
       </c>
     </row>
     <row r="8">
@@ -2159,7 +2159,7 @@
         <v>7</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>15</v>
@@ -5960,7 +5960,7 @@
         <v>8</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>15</v>
@@ -6485,7 +6485,7 @@
         <v>8</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>15</v>

--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1436" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="302">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -775,6 +775,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/resources/support-us</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/steam-news/announcing-the-heat-creators-contest</t>
   </si>
   <si>
     <t>https://heatlabs.net/steam-news/announcing-world-of-tanks-heat</t>
@@ -1427,7 +1430,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1531,7 +1534,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1635,7 +1638,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1739,7 +1742,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -6415,14 +6418,14 @@
       <c r="I237" s="2"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="s">
+      <c r="A238" s="14" t="s">
         <v>254</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D238" s="6" t="s">
         <v>15</v>
@@ -6457,20 +6460,20 @@
       <c r="I239" s="2"/>
     </row>
     <row r="240">
-      <c r="A240" s="14" t="s">
+      <c r="A240" s="5" t="s">
         <v>256</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -6488,10 +6491,10 @@
         <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -6499,20 +6502,20 @@
       <c r="I241" s="2"/>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="s">
+      <c r="A242" s="14" t="s">
         <v>258</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -6520,20 +6523,20 @@
       <c r="I242" s="2"/>
     </row>
     <row r="243">
-      <c r="A243" s="14" t="s">
+      <c r="A243" s="5" t="s">
         <v>259</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6541,20 +6544,20 @@
       <c r="I243" s="2"/>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="s">
+      <c r="A244" s="14" t="s">
         <v>260</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C244" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -6572,10 +6575,10 @@
         <v>7</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -6593,10 +6596,10 @@
         <v>7</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -6614,10 +6617,10 @@
         <v>7</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -7013,10 +7016,10 @@
         <v>7</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
@@ -7034,10 +7037,10 @@
         <v>7</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
@@ -7181,10 +7184,10 @@
         <v>7</v>
       </c>
       <c r="D274" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E274" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
@@ -7196,16 +7199,16 @@
         <v>291</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
@@ -7217,10 +7220,10 @@
         <v>292</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D276" s="6" t="s">
         <v>15</v>
@@ -7283,7 +7286,7 @@
         <v>7</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D279" s="6" t="s">
         <v>15</v>
@@ -7301,7 +7304,7 @@
         <v>296</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>8</v>
@@ -7322,7 +7325,7 @@
         <v>297</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>8</v>
@@ -7385,16 +7388,16 @@
         <v>300</v>
       </c>
       <c r="B284" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D284" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E284" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
@@ -7402,11 +7405,21 @@
       <c r="I284" s="2"/>
     </row>
     <row r="285">
-      <c r="A285" s="16"/>
-      <c r="B285" s="17"/>
-      <c r="C285" s="17"/>
-      <c r="D285" s="17"/>
-      <c r="E285" s="17"/>
+      <c r="A285" s="5" t="s">
+        <v>301</v>
+      </c>
+      <c r="B285" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C285" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D285" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E285" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
@@ -15541,7 +15554,8 @@
     <hyperlink r:id="rId281" ref="A282"/>
     <hyperlink r:id="rId282" ref="A283"/>
     <hyperlink r:id="rId283" ref="A284"/>
+    <hyperlink r:id="rId284" ref="A285"/>
   </hyperlinks>
-  <drawing r:id="rId284"/>
+  <drawing r:id="rId285"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -1534,7 +1534,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1544,7 +1544,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>215</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8">
@@ -2771,7 +2771,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>15</v>
@@ -3212,7 +3212,7 @@
         <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>15</v>
@@ -5165,7 +5165,7 @@
         <v>8</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>15</v>

--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -1534,7 +1534,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1544,7 +1544,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -2582,7 +2582,7 @@
         <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>15</v>
@@ -5249,7 +5249,7 @@
         <v>8</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>15</v>

--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1441" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="303">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/guides/general-guides</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/guides/general-guides/shell-crit-cone-mechanic</t>
   </si>
   <si>
     <t>https://heatlabs.net/guides/map-guides</t>
@@ -1430,7 +1433,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1534,7 +1537,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1544,7 +1547,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8">
@@ -1638,7 +1641,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1742,7 +1745,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -3310,14 +3313,14 @@
       <c r="I89" s="2"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="14" t="s">
         <v>106</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>15</v>
@@ -3404,10 +3407,10 @@
         <v>7</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
@@ -3425,10 +3428,10 @@
         <v>7</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -3436,14 +3439,14 @@
       <c r="I95" s="2"/>
     </row>
     <row r="96">
-      <c r="A96" s="14" t="s">
+      <c r="A96" s="5" t="s">
         <v>112</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>15</v>
@@ -3457,20 +3460,20 @@
       <c r="I96" s="2"/>
     </row>
     <row r="97">
-      <c r="A97" s="5" t="s">
+      <c r="A97" s="14" t="s">
         <v>113</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -3482,16 +3485,16 @@
         <v>114</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -3503,16 +3506,16 @@
         <v>115</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
@@ -3527,13 +3530,13 @@
         <v>7</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -3545,16 +3548,16 @@
         <v>117</v>
       </c>
       <c r="B101" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C101" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C101" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="D101" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -3566,7 +3569,7 @@
         <v>118</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>7</v>
@@ -3593,10 +3596,10 @@
         <v>7</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3614,10 +3617,10 @@
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3629,16 +3632,16 @@
         <v>121</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -3650,7 +3653,7 @@
         <v>122</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>7</v>
@@ -3671,7 +3674,7 @@
         <v>123</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>7</v>
@@ -3692,10 +3695,10 @@
         <v>124</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>15</v>
@@ -3716,7 +3719,7 @@
         <v>7</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>15</v>
@@ -3779,7 +3782,7 @@
         <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -3800,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>15</v>
@@ -4133,7 +4136,7 @@
         <v>145</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>7</v>
@@ -4196,7 +4199,7 @@
         <v>148</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>7</v>
@@ -4217,7 +4220,7 @@
         <v>149</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>7</v>
@@ -4238,7 +4241,7 @@
         <v>150</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>7</v>
@@ -4304,7 +4307,7 @@
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -4325,7 +4328,7 @@
         <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>15</v>
@@ -4367,7 +4370,7 @@
         <v>7</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -4388,7 +4391,7 @@
         <v>7</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>15</v>
@@ -4433,10 +4436,10 @@
         <v>7</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
@@ -4454,10 +4457,10 @@
         <v>7</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -4469,7 +4472,7 @@
         <v>161</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C145" s="6" t="s">
         <v>7</v>
@@ -4490,7 +4493,7 @@
         <v>162</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>7</v>
@@ -4598,7 +4601,7 @@
         <v>7</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>15</v>
@@ -4619,7 +4622,7 @@
         <v>7</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>15</v>
@@ -4724,7 +4727,7 @@
         <v>7</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>15</v>
@@ -4766,7 +4769,7 @@
         <v>7</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4850,7 +4853,7 @@
         <v>7</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>15</v>
@@ -4871,7 +4874,7 @@
         <v>7</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>15</v>
@@ -4997,7 +5000,7 @@
         <v>7</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>15</v>
@@ -5018,7 +5021,7 @@
         <v>7</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>15</v>
@@ -5120,7 +5123,7 @@
         <v>192</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>7</v>
@@ -5141,7 +5144,7 @@
         <v>193</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>7</v>
@@ -5162,7 +5165,7 @@
         <v>194</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C178" s="6" t="s">
         <v>7</v>
@@ -5183,10 +5186,10 @@
         <v>195</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>15</v>
@@ -5228,7 +5231,7 @@
         <v>7</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>15</v>
@@ -5246,10 +5249,10 @@
         <v>198</v>
       </c>
       <c r="B182" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C182" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>15</v>
@@ -5267,7 +5270,7 @@
         <v>199</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>7</v>
@@ -5288,7 +5291,7 @@
         <v>200</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>7</v>
@@ -5312,7 +5315,7 @@
         <v>8</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>15</v>
@@ -5333,7 +5336,7 @@
         <v>8</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>15</v>
@@ -5351,7 +5354,7 @@
         <v>203</v>
       </c>
       <c r="B187" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C187" s="6" t="s">
         <v>7</v>
@@ -5372,10 +5375,10 @@
         <v>204</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5393,10 +5396,10 @@
         <v>205</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>15</v>
@@ -5540,10 +5543,10 @@
         <v>212</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C196" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D196" s="6" t="s">
         <v>15</v>
@@ -5624,7 +5627,7 @@
         <v>216</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>8</v>
@@ -5669,7 +5672,7 @@
         <v>7</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>15</v>
@@ -5687,7 +5690,7 @@
         <v>219</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>7</v>
@@ -5732,7 +5735,7 @@
         <v>8</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>15</v>
@@ -5753,7 +5756,7 @@
         <v>8</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>15</v>
@@ -5771,7 +5774,7 @@
         <v>223</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>8</v>
@@ -5795,7 +5798,7 @@
         <v>7</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>15</v>
@@ -5813,7 +5816,7 @@
         <v>225</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>7</v>
@@ -5855,16 +5858,16 @@
         <v>227</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -5876,16 +5879,16 @@
         <v>228</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -5942,7 +5945,7 @@
         <v>8</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D215" s="6" t="s">
         <v>15</v>
@@ -5963,7 +5966,7 @@
         <v>8</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>15</v>
@@ -6002,7 +6005,7 @@
         <v>234</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>7</v>
@@ -6023,16 +6026,16 @@
         <v>235</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
@@ -6044,7 +6047,7 @@
         <v>236</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>7</v>
@@ -6071,10 +6074,10 @@
         <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -6086,7 +6089,7 @@
         <v>238</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>7</v>
@@ -6103,7 +6106,7 @@
       <c r="I222" s="2"/>
     </row>
     <row r="223">
-      <c r="A223" s="14" t="s">
+      <c r="A223" s="5" t="s">
         <v>239</v>
       </c>
       <c r="B223" s="6" t="s">
@@ -6124,11 +6127,11 @@
       <c r="I223" s="2"/>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="s">
+      <c r="A224" s="14" t="s">
         <v>240</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>7</v>
@@ -6229,14 +6232,14 @@
       <c r="I228" s="2"/>
     </row>
     <row r="229">
-      <c r="A229" s="14" t="s">
+      <c r="A229" s="5" t="s">
         <v>245</v>
       </c>
       <c r="B229" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D229" s="6" t="s">
         <v>15</v>
@@ -6250,14 +6253,14 @@
       <c r="I229" s="2"/>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="s">
+      <c r="A230" s="14" t="s">
         <v>246</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>15</v>
@@ -6275,7 +6278,7 @@
         <v>247</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C231" s="6" t="s">
         <v>7</v>
@@ -6296,16 +6299,16 @@
         <v>248</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C232" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D232" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E232" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
@@ -6317,16 +6320,16 @@
         <v>249</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C233" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
@@ -6338,7 +6341,7 @@
         <v>250</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>7</v>
@@ -6380,16 +6383,16 @@
         <v>252</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D236" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E236" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
@@ -6401,7 +6404,7 @@
         <v>253</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>7</v>
@@ -6418,20 +6421,20 @@
       <c r="I237" s="2"/>
     </row>
     <row r="238">
-      <c r="A238" s="14" t="s">
+      <c r="A238" s="5" t="s">
         <v>254</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -6439,14 +6442,14 @@
       <c r="I238" s="2"/>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="s">
+      <c r="A239" s="14" t="s">
         <v>255</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D239" s="6" t="s">
         <v>15</v>
@@ -6481,20 +6484,20 @@
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="14" t="s">
+      <c r="A241" s="5" t="s">
         <v>257</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C241" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
@@ -6512,10 +6515,10 @@
         <v>7</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -6523,20 +6526,20 @@
       <c r="I242" s="2"/>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="s">
+      <c r="A243" s="14" t="s">
         <v>259</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6544,20 +6547,20 @@
       <c r="I243" s="2"/>
     </row>
     <row r="244">
-      <c r="A244" s="14" t="s">
+      <c r="A244" s="5" t="s">
         <v>260</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C244" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -6565,20 +6568,20 @@
       <c r="I244" s="2"/>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="s">
+      <c r="A245" s="14" t="s">
         <v>261</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C245" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D245" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
@@ -6596,10 +6599,10 @@
         <v>7</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -6617,10 +6620,10 @@
         <v>7</v>
       </c>
       <c r="D247" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E247" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
@@ -6638,10 +6641,10 @@
         <v>7</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
@@ -7037,10 +7040,10 @@
         <v>7</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
@@ -7058,10 +7061,10 @@
         <v>7</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
@@ -7205,10 +7208,10 @@
         <v>7</v>
       </c>
       <c r="D275" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E275" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
@@ -7220,16 +7223,16 @@
         <v>292</v>
       </c>
       <c r="B276" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
@@ -7241,7 +7244,7 @@
         <v>293</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>7</v>
@@ -7307,7 +7310,7 @@
         <v>7</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D280" s="6" t="s">
         <v>15</v>
@@ -7325,7 +7328,7 @@
         <v>297</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>8</v>
@@ -7346,7 +7349,7 @@
         <v>298</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C282" s="6" t="s">
         <v>8</v>
@@ -7409,16 +7412,16 @@
         <v>301</v>
       </c>
       <c r="B285" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
@@ -7426,11 +7429,21 @@
       <c r="I285" s="2"/>
     </row>
     <row r="286">
-      <c r="A286" s="16"/>
-      <c r="B286" s="17"/>
-      <c r="C286" s="17"/>
-      <c r="D286" s="17"/>
-      <c r="E286" s="17"/>
+      <c r="A286" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B286" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C286" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D286" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E286" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
@@ -15555,7 +15568,8 @@
     <hyperlink r:id="rId282" ref="A283"/>
     <hyperlink r:id="rId283" ref="A284"/>
     <hyperlink r:id="rId284" ref="A285"/>
+    <hyperlink r:id="rId285" ref="A286"/>
   </hyperlinks>
-  <drawing r:id="rId285"/>
+  <drawing r:id="rId286"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1446" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="306">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -342,6 +342,9 @@
     <t>https://heatlabs.net/guides/tank-guides</t>
   </si>
   <si>
+    <t>https://heatlabs.net/guides/tank-guides/alvt-players-guide</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/guides/tank-guides/bat-4m-basic-guide</t>
   </si>
   <si>
@@ -837,6 +840,9 @@
     <t>https://heatlabs.net/tanks/m1-railgun</t>
   </si>
   <si>
+    <t>https://heatlabs.net/tanks/m1150-abv</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/tanks/m1e1</t>
   </si>
   <si>
@@ -877,6 +883,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/tanks/t-72b</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/tanks/t-72sh</t>
   </si>
   <si>
     <t>https://heatlabs.net/tanks/xm1-90</t>
@@ -1433,7 +1442,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1537,7 +1546,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1641,7 +1650,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1745,7 +1754,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -3334,14 +3343,14 @@
       <c r="I90" s="2"/>
     </row>
     <row r="91">
-      <c r="A91" s="5" t="s">
-        <v>107</v>
+      <c r="A91" s="14" t="s">
+        <v>106</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>15</v>
@@ -3356,7 +3365,7 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>7</v>
@@ -3377,7 +3386,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
@@ -3397,14 +3406,14 @@
       <c r="I93" s="2"/>
     </row>
     <row r="94">
-      <c r="A94" s="5" t="s">
-        <v>110</v>
+      <c r="A94" s="14" t="s">
+        <v>109</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>15</v>
@@ -3419,7 +3428,7 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>7</v>
@@ -3428,10 +3437,10 @@
         <v>7</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F95" s="2"/>
       <c r="G95" s="2"/>
@@ -3440,7 +3449,7 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
@@ -3460,20 +3469,20 @@
       <c r="I96" s="2"/>
     </row>
     <row r="97">
-      <c r="A97" s="14" t="s">
-        <v>113</v>
+      <c r="A97" s="5" t="s">
+        <v>112</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -3482,7 +3491,7 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
@@ -3491,10 +3500,10 @@
         <v>7</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -3502,14 +3511,14 @@
       <c r="I98" s="2"/>
     </row>
     <row r="99">
-      <c r="A99" s="5" t="s">
-        <v>115</v>
+      <c r="A99" s="14" t="s">
+        <v>114</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3524,7 +3533,7 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>7</v>
@@ -3545,10 +3554,10 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>8</v>
@@ -3566,10 +3575,10 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>7</v>
@@ -3587,19 +3596,19 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3608,19 +3617,19 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3629,7 +3638,7 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -3650,10 +3659,10 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>7</v>
@@ -3671,7 +3680,7 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>7</v>
@@ -3680,10 +3689,10 @@
         <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -3692,7 +3701,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>8</v>
@@ -3713,13 +3722,13 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>15</v>
@@ -3734,10 +3743,10 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>7</v>
@@ -3755,13 +3764,13 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3776,7 +3785,7 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>7</v>
@@ -3797,13 +3806,13 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D113" s="6" t="s">
         <v>15</v>
@@ -3818,7 +3827,7 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>7</v>
@@ -3839,13 +3848,13 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>15</v>
@@ -3860,7 +3869,7 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B116" s="6" t="s">
         <v>7</v>
@@ -3881,7 +3890,7 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>7</v>
@@ -3902,7 +3911,7 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>7</v>
@@ -3923,7 +3932,7 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
@@ -3944,7 +3953,7 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
@@ -3965,7 +3974,7 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>7</v>
@@ -3986,7 +3995,7 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>7</v>
@@ -4007,7 +4016,7 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>7</v>
@@ -4028,7 +4037,7 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>7</v>
@@ -4049,7 +4058,7 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>7</v>
@@ -4070,7 +4079,7 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>7</v>
@@ -4091,7 +4100,7 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
@@ -4112,7 +4121,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
@@ -4133,7 +4142,7 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
@@ -4154,10 +4163,10 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>7</v>
@@ -4175,10 +4184,10 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>7</v>
@@ -4196,7 +4205,7 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>8</v>
@@ -4217,10 +4226,10 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>7</v>
@@ -4238,7 +4247,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>8</v>
@@ -4259,7 +4268,7 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
@@ -4280,10 +4289,10 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>7</v>
@@ -4301,7 +4310,7 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
@@ -4322,13 +4331,13 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>15</v>
@@ -4343,7 +4352,7 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>7</v>
@@ -4364,13 +4373,13 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -4385,13 +4394,13 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>15</v>
@@ -4406,7 +4415,7 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>7</v>
@@ -4427,13 +4436,13 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4448,7 +4457,7 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>7</v>
@@ -4457,10 +4466,10 @@
         <v>7</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
@@ -4469,7 +4478,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>7</v>
@@ -4490,19 +4499,19 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B146" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C146" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4511,7 +4520,7 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>7</v>
@@ -4532,10 +4541,10 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>7</v>
@@ -4553,7 +4562,7 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>7</v>
@@ -4574,7 +4583,7 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>7</v>
@@ -4595,7 +4604,7 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>7</v>
@@ -4616,13 +4625,13 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>15</v>
@@ -4637,7 +4646,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>7</v>
@@ -4658,13 +4667,13 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>15</v>
@@ -4679,7 +4688,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>7</v>
@@ -4700,7 +4709,7 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>7</v>
@@ -4721,7 +4730,7 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>7</v>
@@ -4742,13 +4751,13 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>15</v>
@@ -4763,13 +4772,13 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4784,13 +4793,13 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>15</v>
@@ -4805,13 +4814,13 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>15</v>
@@ -4826,7 +4835,7 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B162" s="6" t="s">
         <v>7</v>
@@ -4847,7 +4856,7 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>7</v>
@@ -4868,13 +4877,13 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B164" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>15</v>
@@ -4889,7 +4898,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>7</v>
@@ -4910,13 +4919,13 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B166" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>15</v>
@@ -4931,7 +4940,7 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>7</v>
@@ -4952,7 +4961,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>7</v>
@@ -4973,7 +4982,7 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B169" s="6" t="s">
         <v>7</v>
@@ -4994,7 +5003,7 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B170" s="6" t="s">
         <v>7</v>
@@ -5015,13 +5024,13 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>15</v>
@@ -5036,7 +5045,7 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B172" s="6" t="s">
         <v>7</v>
@@ -5057,13 +5066,13 @@
     </row>
     <row r="173">
       <c r="A173" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>15</v>
@@ -5078,7 +5087,7 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B174" s="6" t="s">
         <v>7</v>
@@ -5099,7 +5108,7 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B175" s="6" t="s">
         <v>7</v>
@@ -5120,7 +5129,7 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>7</v>
@@ -5141,10 +5150,10 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C177" s="6" t="s">
         <v>7</v>
@@ -5162,7 +5171,7 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B178" s="6" t="s">
         <v>7</v>
@@ -5183,7 +5192,7 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B179" s="6" t="s">
         <v>8</v>
@@ -5204,13 +5213,13 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>15</v>
@@ -5225,10 +5234,10 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>7</v>
@@ -5246,7 +5255,7 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>7</v>
@@ -5267,10 +5276,10 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>7</v>
@@ -5288,13 +5297,13 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B184" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D184" s="6" t="s">
         <v>15</v>
@@ -5309,7 +5318,7 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B185" s="6" t="s">
         <v>8</v>
@@ -5330,13 +5339,13 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>15</v>
@@ -5351,7 +5360,7 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>8</v>
@@ -5372,13 +5381,13 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5393,13 +5402,13 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B189" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>15</v>
@@ -5414,7 +5423,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>7</v>
@@ -5435,13 +5444,13 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>15</v>
@@ -5456,7 +5465,7 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>7</v>
@@ -5477,7 +5486,7 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>7</v>
@@ -5498,7 +5507,7 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B194" s="6" t="s">
         <v>7</v>
@@ -5519,7 +5528,7 @@
     </row>
     <row r="195">
       <c r="A195" s="5" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>7</v>
@@ -5540,7 +5549,7 @@
     </row>
     <row r="196">
       <c r="A196" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B196" s="6" t="s">
         <v>7</v>
@@ -5561,13 +5570,13 @@
     </row>
     <row r="197">
       <c r="A197" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D197" s="6" t="s">
         <v>15</v>
@@ -5582,13 +5591,13 @@
     </row>
     <row r="198">
       <c r="A198" s="5" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B198" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D198" s="6" t="s">
         <v>15</v>
@@ -5603,7 +5612,7 @@
     </row>
     <row r="199">
       <c r="A199" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B199" s="6" t="s">
         <v>8</v>
@@ -5624,7 +5633,7 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B200" s="6" t="s">
         <v>8</v>
@@ -5645,10 +5654,10 @@
     </row>
     <row r="201">
       <c r="A201" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>8</v>
@@ -5666,10 +5675,10 @@
     </row>
     <row r="202">
       <c r="A202" s="5" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C202" s="6" t="s">
         <v>8</v>
@@ -5687,13 +5696,13 @@
     </row>
     <row r="203">
       <c r="A203" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>15</v>
@@ -5708,13 +5717,13 @@
     </row>
     <row r="204">
       <c r="A204" s="5" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>15</v>
@@ -5729,10 +5738,10 @@
     </row>
     <row r="205">
       <c r="A205" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C205" s="6" t="s">
         <v>7</v>
@@ -5750,7 +5759,7 @@
     </row>
     <row r="206">
       <c r="A206" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>8</v>
@@ -5771,13 +5780,13 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D207" s="6" t="s">
         <v>15</v>
@@ -5792,13 +5801,13 @@
     </row>
     <row r="208">
       <c r="A208" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>15</v>
@@ -5813,13 +5822,13 @@
     </row>
     <row r="209">
       <c r="A209" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D209" s="6" t="s">
         <v>15</v>
@@ -5834,13 +5843,13 @@
     </row>
     <row r="210">
       <c r="A210" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>15</v>
@@ -5855,10 +5864,10 @@
     </row>
     <row r="211">
       <c r="A211" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>7</v>
@@ -5876,19 +5885,19 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -5897,7 +5906,7 @@
     </row>
     <row r="213">
       <c r="A213" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>8</v>
@@ -5918,19 +5927,19 @@
     </row>
     <row r="214">
       <c r="A214" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -5939,7 +5948,7 @@
     </row>
     <row r="215">
       <c r="A215" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>8</v>
@@ -5960,13 +5969,13 @@
     </row>
     <row r="216">
       <c r="A216" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C216" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D216" s="6" t="s">
         <v>15</v>
@@ -5981,7 +5990,7 @@
     </row>
     <row r="217">
       <c r="A217" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B217" s="6" t="s">
         <v>8</v>
@@ -6002,13 +6011,13 @@
     </row>
     <row r="218">
       <c r="A218" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>15</v>
@@ -6023,10 +6032,10 @@
     </row>
     <row r="219">
       <c r="A219" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
@@ -6044,7 +6053,7 @@
     </row>
     <row r="220">
       <c r="A220" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>8</v>
@@ -6053,10 +6062,10 @@
         <v>7</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -6065,7 +6074,7 @@
     </row>
     <row r="221">
       <c r="A221" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>7</v>
@@ -6074,10 +6083,10 @@
         <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -6086,19 +6095,19 @@
     </row>
     <row r="222">
       <c r="A222" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -6107,19 +6116,19 @@
     </row>
     <row r="223">
       <c r="A223" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B223" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C223" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -6127,11 +6136,11 @@
       <c r="I223" s="2"/>
     </row>
     <row r="224">
-      <c r="A224" s="14" t="s">
-        <v>240</v>
+      <c r="A224" s="5" t="s">
+        <v>239</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>7</v>
@@ -6149,10 +6158,10 @@
     </row>
     <row r="225">
       <c r="A225" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>7</v>
@@ -6169,11 +6178,11 @@
       <c r="I225" s="2"/>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="s">
-        <v>242</v>
+      <c r="A226" s="14" t="s">
+        <v>241</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>7</v>
@@ -6191,7 +6200,7 @@
     </row>
     <row r="227">
       <c r="A227" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>7</v>
@@ -6212,7 +6221,7 @@
     </row>
     <row r="228">
       <c r="A228" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>7</v>
@@ -6233,7 +6242,7 @@
     </row>
     <row r="229">
       <c r="A229" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>7</v>
@@ -6253,14 +6262,14 @@
       <c r="I229" s="2"/>
     </row>
     <row r="230">
-      <c r="A230" s="14" t="s">
-        <v>246</v>
+      <c r="A230" s="5" t="s">
+        <v>245</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>15</v>
@@ -6275,7 +6284,7 @@
     </row>
     <row r="231">
       <c r="A231" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>7</v>
@@ -6295,14 +6304,14 @@
       <c r="I231" s="2"/>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="s">
-        <v>248</v>
+      <c r="A232" s="14" t="s">
+        <v>247</v>
       </c>
       <c r="B232" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D232" s="6" t="s">
         <v>15</v>
@@ -6317,7 +6326,7 @@
     </row>
     <row r="233">
       <c r="A233" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>7</v>
@@ -6326,10 +6335,10 @@
         <v>7</v>
       </c>
       <c r="D233" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E233" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
@@ -6338,7 +6347,7 @@
     </row>
     <row r="234">
       <c r="A234" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>8</v>
@@ -6359,7 +6368,7 @@
     </row>
     <row r="235">
       <c r="A235" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B235" s="6" t="s">
         <v>7</v>
@@ -6368,10 +6377,10 @@
         <v>7</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
@@ -6380,10 +6389,10 @@
     </row>
     <row r="236">
       <c r="A236" s="5" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>7</v>
@@ -6401,19 +6410,19 @@
     </row>
     <row r="237">
       <c r="A237" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C237" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
@@ -6422,7 +6431,7 @@
     </row>
     <row r="238">
       <c r="A238" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>7</v>
@@ -6431,10 +6440,10 @@
         <v>7</v>
       </c>
       <c r="D238" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E238" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
@@ -6442,20 +6451,20 @@
       <c r="I238" s="2"/>
     </row>
     <row r="239">
-      <c r="A239" s="14" t="s">
-        <v>255</v>
+      <c r="A239" s="5" t="s">
+        <v>254</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -6464,7 +6473,7 @@
     </row>
     <row r="240">
       <c r="A240" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>7</v>
@@ -6473,10 +6482,10 @@
         <v>7</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -6484,14 +6493,14 @@
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="s">
-        <v>257</v>
+      <c r="A241" s="14" t="s">
+        <v>256</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>15</v>
@@ -6505,20 +6514,20 @@
       <c r="I241" s="2"/>
     </row>
     <row r="242">
-      <c r="A242" s="14" t="s">
-        <v>258</v>
+      <c r="A242" s="5" t="s">
+        <v>257</v>
       </c>
       <c r="B242" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C242" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D242" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
@@ -6526,11 +6535,11 @@
       <c r="I242" s="2"/>
     </row>
     <row r="243">
-      <c r="A243" s="14" t="s">
-        <v>259</v>
+      <c r="A243" s="5" t="s">
+        <v>258</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
@@ -6547,11 +6556,11 @@
       <c r="I243" s="2"/>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="s">
-        <v>260</v>
+      <c r="A244" s="14" t="s">
+        <v>259</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C244" s="6" t="s">
         <v>7</v>
@@ -6569,7 +6578,7 @@
     </row>
     <row r="245">
       <c r="A245" s="14" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>8</v>
@@ -6590,7 +6599,7 @@
     </row>
     <row r="246">
       <c r="A246" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B246" s="6" t="s">
         <v>7</v>
@@ -6610,11 +6619,11 @@
       <c r="I246" s="2"/>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="s">
-        <v>263</v>
+      <c r="A247" s="14" t="s">
+        <v>262</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C247" s="6" t="s">
         <v>7</v>
@@ -6632,7 +6641,7 @@
     </row>
     <row r="248">
       <c r="A248" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>7</v>
@@ -6653,7 +6662,7 @@
     </row>
     <row r="249">
       <c r="A249" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>7</v>
@@ -6674,7 +6683,7 @@
     </row>
     <row r="250">
       <c r="A250" s="5" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B250" s="6" t="s">
         <v>7</v>
@@ -6683,10 +6692,10 @@
         <v>7</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
@@ -6695,7 +6704,7 @@
     </row>
     <row r="251">
       <c r="A251" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>7</v>
@@ -6716,7 +6725,7 @@
     </row>
     <row r="252">
       <c r="A252" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>7</v>
@@ -6737,7 +6746,7 @@
     </row>
     <row r="253">
       <c r="A253" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>7</v>
@@ -6758,7 +6767,7 @@
     </row>
     <row r="254">
       <c r="A254" s="15" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>7</v>
@@ -6779,7 +6788,7 @@
     </row>
     <row r="255">
       <c r="A255" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B255" s="6" t="s">
         <v>7</v>
@@ -6800,7 +6809,7 @@
     </row>
     <row r="256">
       <c r="A256" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>7</v>
@@ -6821,7 +6830,7 @@
     </row>
     <row r="257">
       <c r="A257" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B257" s="6" t="s">
         <v>7</v>
@@ -6842,7 +6851,7 @@
     </row>
     <row r="258">
       <c r="A258" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>7</v>
@@ -6863,7 +6872,7 @@
     </row>
     <row r="259">
       <c r="A259" s="5" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B259" s="6" t="s">
         <v>7</v>
@@ -6883,14 +6892,14 @@
       <c r="I259" s="2"/>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="s">
-        <v>276</v>
+      <c r="A260" s="14" t="s">
+        <v>275</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>15</v>
@@ -6905,7 +6914,7 @@
     </row>
     <row r="261">
       <c r="A261" s="5" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>7</v>
@@ -6926,7 +6935,7 @@
     </row>
     <row r="262">
       <c r="A262" s="5" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B262" s="6" t="s">
         <v>7</v>
@@ -6947,7 +6956,7 @@
     </row>
     <row r="263">
       <c r="A263" s="5" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>7</v>
@@ -6968,7 +6977,7 @@
     </row>
     <row r="264">
       <c r="A264" s="5" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B264" s="6" t="s">
         <v>7</v>
@@ -6989,7 +6998,7 @@
     </row>
     <row r="265">
       <c r="A265" s="5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B265" s="6" t="s">
         <v>7</v>
@@ -7010,7 +7019,7 @@
     </row>
     <row r="266">
       <c r="A266" s="5" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B266" s="6" t="s">
         <v>7</v>
@@ -7031,7 +7040,7 @@
     </row>
     <row r="267">
       <c r="A267" s="5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B267" s="6" t="s">
         <v>7</v>
@@ -7052,7 +7061,7 @@
     </row>
     <row r="268">
       <c r="A268" s="5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B268" s="6" t="s">
         <v>7</v>
@@ -7061,10 +7070,10 @@
         <v>7</v>
       </c>
       <c r="D268" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E268" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
@@ -7073,7 +7082,7 @@
     </row>
     <row r="269">
       <c r="A269" s="5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B269" s="6" t="s">
         <v>7</v>
@@ -7094,7 +7103,7 @@
     </row>
     <row r="270">
       <c r="A270" s="5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B270" s="6" t="s">
         <v>7</v>
@@ -7115,7 +7124,7 @@
     </row>
     <row r="271">
       <c r="A271" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>7</v>
@@ -7124,10 +7133,10 @@
         <v>7</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
@@ -7136,7 +7145,7 @@
     </row>
     <row r="272">
       <c r="A272" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B272" s="6" t="s">
         <v>7</v>
@@ -7157,7 +7166,7 @@
     </row>
     <row r="273">
       <c r="A273" s="5" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>7</v>
@@ -7178,7 +7187,7 @@
     </row>
     <row r="274">
       <c r="A274" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B274" s="6" t="s">
         <v>7</v>
@@ -7198,14 +7207,14 @@
       <c r="I274" s="2"/>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="s">
-        <v>291</v>
+      <c r="A275" s="14" t="s">
+        <v>290</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D275" s="6" t="s">
         <v>15</v>
@@ -7220,7 +7229,7 @@
     </row>
     <row r="276">
       <c r="A276" s="5" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B276" s="6" t="s">
         <v>7</v>
@@ -7229,10 +7238,10 @@
         <v>7</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
@@ -7241,10 +7250,10 @@
     </row>
     <row r="277">
       <c r="A277" s="5" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B277" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>7</v>
@@ -7262,7 +7271,7 @@
     </row>
     <row r="278">
       <c r="A278" s="5" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B278" s="6" t="s">
         <v>7</v>
@@ -7283,7 +7292,7 @@
     </row>
     <row r="279">
       <c r="A279" s="5" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B279" s="6" t="s">
         <v>7</v>
@@ -7304,7 +7313,7 @@
     </row>
     <row r="280">
       <c r="A280" s="5" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B280" s="6" t="s">
         <v>7</v>
@@ -7313,10 +7322,10 @@
         <v>7</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
@@ -7325,13 +7334,13 @@
     </row>
     <row r="281">
       <c r="A281" s="5" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D281" s="6" t="s">
         <v>15</v>
@@ -7346,13 +7355,13 @@
     </row>
     <row r="282">
       <c r="A282" s="5" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B282" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C282" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D282" s="6" t="s">
         <v>15</v>
@@ -7367,13 +7376,13 @@
     </row>
     <row r="283">
       <c r="A283" s="5" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C283" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D283" s="6" t="s">
         <v>15</v>
@@ -7388,13 +7397,13 @@
     </row>
     <row r="284">
       <c r="A284" s="5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B284" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C284" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D284" s="6" t="s">
         <v>15</v>
@@ -7409,7 +7418,7 @@
     </row>
     <row r="285">
       <c r="A285" s="5" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B285" s="6" t="s">
         <v>7</v>
@@ -7430,19 +7439,19 @@
     </row>
     <row r="286">
       <c r="A286" s="5" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B286" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D286" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E286" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
@@ -7450,44 +7459,84 @@
       <c r="I286" s="2"/>
     </row>
     <row r="287">
-      <c r="A287" s="16"/>
-      <c r="B287" s="17"/>
-      <c r="C287" s="17"/>
-      <c r="D287" s="17"/>
-      <c r="E287" s="17"/>
+      <c r="A287" s="5" t="s">
+        <v>302</v>
+      </c>
+      <c r="B287" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C287" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D287" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E287" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
     </row>
     <row r="288">
-      <c r="A288" s="16"/>
-      <c r="B288" s="17"/>
-      <c r="C288" s="17"/>
-      <c r="D288" s="17"/>
-      <c r="E288" s="17"/>
+      <c r="A288" s="5" t="s">
+        <v>303</v>
+      </c>
+      <c r="B288" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C288" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D288" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E288" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
     <row r="289">
-      <c r="A289" s="16"/>
-      <c r="B289" s="17"/>
-      <c r="C289" s="17"/>
-      <c r="D289" s="17"/>
-      <c r="E289" s="17"/>
+      <c r="A289" s="5" t="s">
+        <v>304</v>
+      </c>
+      <c r="B289" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C289" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D289" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E289" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
     </row>
     <row r="290">
-      <c r="A290" s="16"/>
-      <c r="B290" s="17"/>
-      <c r="C290" s="17"/>
-      <c r="D290" s="17"/>
-      <c r="E290" s="17"/>
+      <c r="A290" s="5" t="s">
+        <v>305</v>
+      </c>
+      <c r="B290" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C290" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D290" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E290" s="6" t="s">
+        <v>40</v>
+      </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
@@ -15569,7 +15618,11 @@
     <hyperlink r:id="rId283" ref="A284"/>
     <hyperlink r:id="rId284" ref="A285"/>
     <hyperlink r:id="rId285" ref="A286"/>
+    <hyperlink r:id="rId286" ref="A287"/>
+    <hyperlink r:id="rId287" ref="A288"/>
+    <hyperlink r:id="rId288" ref="A289"/>
+    <hyperlink r:id="rId289" ref="A290"/>
   </hyperlinks>
-  <drawing r:id="rId286"/>
+  <drawing r:id="rId290"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="311">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -108,6 +108,9 @@
     <t>https://heatlabs.net/agents/fantome</t>
   </si>
   <si>
+    <t>https://heatlabs.net/agents/flair</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/agents/hound</t>
   </si>
   <si>
@@ -429,6 +432,9 @@
     <t>https://heatlabs.net/maps/duga</t>
   </si>
   <si>
+    <t>https://heatlabs.net/maps/eden</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/maps/evergreen</t>
   </si>
   <si>
@@ -747,6 +753,9 @@
     <t>https://heatlabs.net/playground/heat-labs-app</t>
   </si>
   <si>
+    <t>https://heatlabs.net/playground/player-records</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/playground/roulette</t>
   </si>
   <si>
@@ -762,6 +771,9 @@
     <t>https://heatlabs.net/playground/tierlist</t>
   </si>
   <si>
+    <t>https://heatlabs.net/playground/weekend-chase-stats</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/playground/wordle</t>
   </si>
   <si>
@@ -832,6 +844,9 @@
   </si>
   <si>
     <t>https://heatlabs.net/tanks/leopard-2fk</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/tanks/leopard-2k-st</t>
   </si>
   <si>
     <t>https://heatlabs.net/tanks/leopard-2k14</t>
@@ -1442,7 +1457,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1546,7 +1561,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1650,7 +1665,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1754,7 +1769,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -1775,7 +1790,7 @@
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>15</v>
@@ -1793,10 +1808,10 @@
         <v>32</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>15</v>
@@ -1814,10 +1829,10 @@
         <v>33</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>15</v>
@@ -1835,7 +1850,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>7</v>
@@ -1856,7 +1871,7 @@
         <v>35</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="6" t="s">
         <v>7</v>
@@ -1877,7 +1892,7 @@
         <v>36</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>7</v>
@@ -1940,16 +1955,16 @@
         <v>39</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F24" s="2"/>
       <c r="G24" s="2"/>
@@ -1958,19 +1973,19 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="C25" s="6" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1982,7 +1997,7 @@
         <v>42</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>7</v>
@@ -2048,7 +2063,7 @@
         <v>7</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>15</v>
@@ -2069,7 +2084,7 @@
         <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>15</v>
@@ -2198,10 +2213,10 @@
         <v>7</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F36" s="2"/>
       <c r="G36" s="2"/>
@@ -2234,16 +2249,16 @@
         <v>54</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2321,7 +2336,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>15</v>
@@ -2335,11 +2350,11 @@
       <c r="I42" s="2"/>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="s">
+      <c r="A43" s="5" t="s">
         <v>59</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
         <v>7</v>
@@ -2356,7 +2371,7 @@
       <c r="I43" s="2"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B44" s="6" t="s">
@@ -2381,10 +2396,10 @@
         <v>61</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>15</v>
@@ -2405,7 +2420,7 @@
         <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>15</v>
@@ -2450,10 +2465,10 @@
         <v>7</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2468,13 +2483,13 @@
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2594,7 +2609,7 @@
         <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>15</v>
@@ -2615,7 +2630,7 @@
         <v>8</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D56" s="6" t="s">
         <v>15</v>
@@ -2657,7 +2672,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>15</v>
@@ -2713,7 +2728,7 @@
       <c r="I60" s="2"/>
     </row>
     <row r="61">
-      <c r="A61" s="14" t="s">
+      <c r="A61" s="5" t="s">
         <v>77</v>
       </c>
       <c r="B61" s="6" t="s">
@@ -2723,10 +2738,10 @@
         <v>7</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F61" s="2"/>
       <c r="G61" s="2"/>
@@ -2734,7 +2749,7 @@
       <c r="I61" s="2"/>
     </row>
     <row r="62">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="14" t="s">
         <v>78</v>
       </c>
       <c r="B62" s="6" t="s">
@@ -2762,13 +2777,13 @@
         <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -2776,14 +2791,14 @@
       <c r="I63" s="2"/>
     </row>
     <row r="64">
-      <c r="A64" s="14" t="s">
+      <c r="A64" s="5" t="s">
         <v>80</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>15</v>
@@ -2797,14 +2812,14 @@
       <c r="I64" s="2"/>
     </row>
     <row r="65">
-      <c r="A65" s="5" t="s">
+      <c r="A65" s="14" t="s">
         <v>81</v>
       </c>
       <c r="B65" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D65" s="6" t="s">
         <v>15</v>
@@ -2843,10 +2858,10 @@
         <v>83</v>
       </c>
       <c r="B67" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>15</v>
@@ -2864,16 +2879,16 @@
         <v>84</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C68" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F68" s="2"/>
       <c r="G68" s="2"/>
@@ -2885,16 +2900,16 @@
         <v>85</v>
       </c>
       <c r="B69" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -2906,7 +2921,7 @@
         <v>86</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>7</v>
@@ -2951,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D72" s="6" t="s">
         <v>15</v>
@@ -2990,10 +3005,10 @@
         <v>90</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>15</v>
@@ -3011,10 +3026,10 @@
         <v>91</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>15</v>
@@ -3035,7 +3050,7 @@
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -3056,7 +3071,7 @@
         <v>8</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D77" s="6" t="s">
         <v>15</v>
@@ -3077,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>15</v>
@@ -3095,7 +3110,7 @@
         <v>95</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
         <v>7</v>
@@ -3116,7 +3131,7 @@
         <v>96</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>7</v>
@@ -3203,7 +3218,7 @@
         <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>15</v>
@@ -3217,14 +3232,14 @@
       <c r="I84" s="2"/>
     </row>
     <row r="85">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="5" t="s">
         <v>101</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>15</v>
@@ -3238,20 +3253,20 @@
       <c r="I85" s="2"/>
     </row>
     <row r="86">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -3311,10 +3326,10 @@
         <v>7</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -3322,14 +3337,14 @@
       <c r="I89" s="2"/>
     </row>
     <row r="90">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="5" t="s">
         <v>106</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>15</v>
@@ -3344,7 +3359,7 @@
     </row>
     <row r="91">
       <c r="A91" s="14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>8</v>
@@ -3364,14 +3379,14 @@
       <c r="I91" s="2"/>
     </row>
     <row r="92">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="14" t="s">
         <v>107</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -3406,14 +3421,14 @@
       <c r="I93" s="2"/>
     </row>
     <row r="94">
-      <c r="A94" s="14" t="s">
+      <c r="A94" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D94" s="6" t="s">
         <v>15</v>
@@ -3427,14 +3442,14 @@
       <c r="I94" s="2"/>
     </row>
     <row r="95">
-      <c r="A95" s="5" t="s">
+      <c r="A95" s="14" t="s">
         <v>110</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>15</v>
@@ -3479,10 +3494,10 @@
         <v>7</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F97" s="2"/>
       <c r="G97" s="2"/>
@@ -3500,10 +3515,10 @@
         <v>7</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -3511,11 +3526,11 @@
       <c r="I98" s="2"/>
     </row>
     <row r="99">
-      <c r="A99" s="14" t="s">
+      <c r="A99" s="5" t="s">
         <v>114</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>7</v>
@@ -3532,20 +3547,20 @@
       <c r="I99" s="2"/>
     </row>
     <row r="100">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="14" t="s">
         <v>115</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -3557,16 +3572,16 @@
         <v>116</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -3578,16 +3593,16 @@
         <v>117</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3602,13 +3617,13 @@
         <v>7</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3620,16 +3635,16 @@
         <v>119</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3641,7 +3656,7 @@
         <v>120</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>7</v>
@@ -3668,10 +3683,10 @@
         <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -3689,10 +3704,10 @@
         <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -3704,16 +3719,16 @@
         <v>123</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -3725,7 +3740,7 @@
         <v>124</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>7</v>
@@ -3746,7 +3761,7 @@
         <v>125</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>7</v>
@@ -3767,10 +3782,10 @@
         <v>126</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3791,7 +3806,7 @@
         <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -3854,7 +3869,7 @@
         <v>7</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>15</v>
@@ -3875,7 +3890,7 @@
         <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>15</v>
@@ -4040,10 +4055,10 @@
         <v>139</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>15</v>
@@ -4208,7 +4223,7 @@
         <v>147</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>7</v>
@@ -4229,7 +4244,7 @@
         <v>148</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>7</v>
@@ -4271,7 +4286,7 @@
         <v>150</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>7</v>
@@ -4334,7 +4349,7 @@
         <v>153</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>7</v>
@@ -4379,7 +4394,7 @@
         <v>7</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -4421,7 +4436,7 @@
         <v>7</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>15</v>
@@ -4442,7 +4457,7 @@
         <v>7</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4484,7 +4499,7 @@
         <v>7</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>15</v>
@@ -4508,10 +4523,10 @@
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4544,16 +4559,16 @@
         <v>163</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -4586,7 +4601,7 @@
         <v>165</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>7</v>
@@ -4673,7 +4688,7 @@
         <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>15</v>
@@ -4715,7 +4730,7 @@
         <v>7</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>15</v>
@@ -4799,7 +4814,7 @@
         <v>7</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>15</v>
@@ -4820,7 +4835,7 @@
         <v>7</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>15</v>
@@ -4841,7 +4856,7 @@
         <v>7</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>15</v>
@@ -4862,7 +4877,7 @@
         <v>7</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>15</v>
@@ -4925,7 +4940,7 @@
         <v>7</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>15</v>
@@ -4967,7 +4982,7 @@
         <v>7</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>15</v>
@@ -5072,7 +5087,7 @@
         <v>7</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>15</v>
@@ -5114,7 +5129,7 @@
         <v>7</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>15</v>
@@ -5195,7 +5210,7 @@
         <v>194</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>7</v>
@@ -5261,7 +5276,7 @@
         <v>7</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D182" s="6" t="s">
         <v>15</v>
@@ -5279,7 +5294,7 @@
         <v>198</v>
       </c>
       <c r="B183" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>7</v>
@@ -5321,7 +5336,7 @@
         <v>200</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>7</v>
@@ -5345,7 +5360,7 @@
         <v>7</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>15</v>
@@ -5384,10 +5399,10 @@
         <v>203</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5426,10 +5441,10 @@
         <v>205</v>
       </c>
       <c r="B190" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>15</v>
@@ -5450,7 +5465,7 @@
         <v>8</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D191" s="6" t="s">
         <v>15</v>
@@ -5489,10 +5504,10 @@
         <v>208</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D193" s="6" t="s">
         <v>15</v>
@@ -5615,10 +5630,10 @@
         <v>214</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>15</v>
@@ -5636,10 +5651,10 @@
         <v>215</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>15</v>
@@ -5699,7 +5714,7 @@
         <v>218</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C203" s="6" t="s">
         <v>8</v>
@@ -5720,7 +5735,7 @@
         <v>219</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C204" s="6" t="s">
         <v>8</v>
@@ -5744,7 +5759,7 @@
         <v>7</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>15</v>
@@ -5762,10 +5777,10 @@
         <v>221</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>15</v>
@@ -5783,7 +5798,7 @@
         <v>222</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>7</v>
@@ -5828,7 +5843,7 @@
         <v>8</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D209" s="6" t="s">
         <v>15</v>
@@ -5846,10 +5861,10 @@
         <v>225</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>15</v>
@@ -5867,10 +5882,10 @@
         <v>226</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>15</v>
@@ -5888,10 +5903,10 @@
         <v>227</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D212" s="6" t="s">
         <v>15</v>
@@ -5909,7 +5924,7 @@
         <v>228</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>7</v>
@@ -5930,16 +5945,16 @@
         <v>229</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D214" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E214" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
@@ -5972,16 +5987,16 @@
         <v>231</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -6017,7 +6032,7 @@
         <v>8</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>15</v>
@@ -6059,7 +6074,7 @@
         <v>8</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>15</v>
@@ -6077,7 +6092,7 @@
         <v>236</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>7</v>
@@ -6104,10 +6119,10 @@
         <v>7</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -6125,10 +6140,10 @@
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -6140,16 +6155,16 @@
         <v>239</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -6161,16 +6176,16 @@
         <v>240</v>
       </c>
       <c r="B225" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C225" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
@@ -6178,11 +6193,11 @@
       <c r="I225" s="2"/>
     </row>
     <row r="226">
-      <c r="A226" s="14" t="s">
+      <c r="A226" s="5" t="s">
         <v>241</v>
       </c>
       <c r="B226" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C226" s="6" t="s">
         <v>7</v>
@@ -6203,7 +6218,7 @@
         <v>242</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>7</v>
@@ -6220,11 +6235,11 @@
       <c r="I227" s="2"/>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="14" t="s">
         <v>243</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>7</v>
@@ -6283,14 +6298,14 @@
       <c r="I230" s="2"/>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="s">
+      <c r="A231" s="14" t="s">
         <v>246</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D231" s="6" t="s">
         <v>15</v>
@@ -6304,14 +6319,14 @@
       <c r="I231" s="2"/>
     </row>
     <row r="232">
-      <c r="A232" s="14" t="s">
+      <c r="A232" s="5" t="s">
         <v>247</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D232" s="6" t="s">
         <v>15</v>
@@ -6350,7 +6365,7 @@
         <v>249</v>
       </c>
       <c r="B234" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C234" s="6" t="s">
         <v>7</v>
@@ -6367,20 +6382,20 @@
       <c r="I234" s="2"/>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="s">
+      <c r="A235" s="14" t="s">
         <v>250</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
@@ -6392,7 +6407,7 @@
         <v>251</v>
       </c>
       <c r="B236" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C236" s="6" t="s">
         <v>7</v>
@@ -6409,14 +6424,14 @@
       <c r="I236" s="2"/>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="s">
+      <c r="A237" s="14" t="s">
         <v>252</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D237" s="6" t="s">
         <v>15</v>
@@ -6434,7 +6449,7 @@
         <v>253</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>7</v>
@@ -6455,7 +6470,7 @@
         <v>254</v>
       </c>
       <c r="B239" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C239" s="6" t="s">
         <v>7</v>
@@ -6476,16 +6491,16 @@
         <v>255</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D240" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E240" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
@@ -6493,14 +6508,14 @@
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="14" t="s">
+      <c r="A241" s="5" t="s">
         <v>256</v>
       </c>
       <c r="B241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D241" s="6" t="s">
         <v>15</v>
@@ -6539,16 +6554,16 @@
         <v>258</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6556,11 +6571,11 @@
       <c r="I243" s="2"/>
     </row>
     <row r="244">
-      <c r="A244" s="14" t="s">
+      <c r="A244" s="5" t="s">
         <v>259</v>
       </c>
       <c r="B244" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C244" s="6" t="s">
         <v>7</v>
@@ -6584,7 +6599,7 @@
         <v>8</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D245" s="6" t="s">
         <v>15</v>
@@ -6608,10 +6623,10 @@
         <v>7</v>
       </c>
       <c r="D246" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E246" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
@@ -6619,11 +6634,11 @@
       <c r="I246" s="2"/>
     </row>
     <row r="247">
-      <c r="A247" s="14" t="s">
+      <c r="A247" s="5" t="s">
         <v>262</v>
       </c>
       <c r="B247" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C247" s="6" t="s">
         <v>7</v>
@@ -6640,11 +6655,11 @@
       <c r="I247" s="2"/>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="s">
+      <c r="A248" s="14" t="s">
         <v>263</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C248" s="6" t="s">
         <v>7</v>
@@ -6661,11 +6676,11 @@
       <c r="I248" s="2"/>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="s">
+      <c r="A249" s="14" t="s">
         <v>264</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>7</v>
@@ -6703,11 +6718,11 @@
       <c r="I250" s="2"/>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="s">
+      <c r="A251" s="14" t="s">
         <v>266</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C251" s="6" t="s">
         <v>7</v>
@@ -6734,10 +6749,10 @@
         <v>7</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
@@ -6776,10 +6791,10 @@
         <v>7</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
@@ -6892,14 +6907,14 @@
       <c r="I259" s="2"/>
     </row>
     <row r="260">
-      <c r="A260" s="14" t="s">
+      <c r="A260" s="5" t="s">
         <v>275</v>
       </c>
       <c r="B260" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C260" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D260" s="6" t="s">
         <v>15</v>
@@ -6938,10 +6953,10 @@
         <v>277</v>
       </c>
       <c r="B262" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C262" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D262" s="6" t="s">
         <v>15</v>
@@ -6997,14 +7012,14 @@
       <c r="I264" s="2"/>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="s">
+      <c r="A265" s="14" t="s">
         <v>280</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D265" s="6" t="s">
         <v>15</v>
@@ -7133,10 +7148,10 @@
         <v>7</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
@@ -7207,14 +7222,14 @@
       <c r="I274" s="2"/>
     </row>
     <row r="275">
-      <c r="A275" s="14" t="s">
+      <c r="A275" s="5" t="s">
         <v>290</v>
       </c>
       <c r="B275" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C275" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D275" s="6" t="s">
         <v>15</v>
@@ -7238,10 +7253,10 @@
         <v>7</v>
       </c>
       <c r="D276" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E276" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
@@ -7312,20 +7327,20 @@
       <c r="I279" s="2"/>
     </row>
     <row r="280">
-      <c r="A280" s="5" t="s">
+      <c r="A280" s="14" t="s">
         <v>295</v>
       </c>
       <c r="B280" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C280" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D280" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E280" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
@@ -7337,7 +7352,7 @@
         <v>296</v>
       </c>
       <c r="B281" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C281" s="6" t="s">
         <v>7</v>
@@ -7424,13 +7439,13 @@
         <v>7</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D285" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E285" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
@@ -7445,7 +7460,7 @@
         <v>8</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D286" s="6" t="s">
         <v>15</v>
@@ -7466,7 +7481,7 @@
         <v>7</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D287" s="6" t="s">
         <v>15</v>
@@ -7487,7 +7502,7 @@
         <v>7</v>
       </c>
       <c r="C288" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D288" s="6" t="s">
         <v>15</v>
@@ -7508,7 +7523,7 @@
         <v>7</v>
       </c>
       <c r="C289" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D289" s="6" t="s">
         <v>15</v>
@@ -7526,16 +7541,16 @@
         <v>305</v>
       </c>
       <c r="B290" s="6" t="s">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="C290" s="6" t="s">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D290" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="E290" s="6" t="s">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
@@ -7543,55 +7558,105 @@
       <c r="I290" s="2"/>
     </row>
     <row r="291">
-      <c r="A291" s="16"/>
-      <c r="B291" s="17"/>
-      <c r="C291" s="17"/>
-      <c r="D291" s="17"/>
-      <c r="E291" s="17"/>
+      <c r="A291" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="B291" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C291" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D291" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E291" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
     </row>
     <row r="292">
-      <c r="A292" s="16"/>
-      <c r="B292" s="17"/>
-      <c r="C292" s="17"/>
-      <c r="D292" s="17"/>
-      <c r="E292" s="17"/>
+      <c r="A292" s="5" t="s">
+        <v>307</v>
+      </c>
+      <c r="B292" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C292" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D292" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E292" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
     </row>
     <row r="293">
-      <c r="A293" s="16"/>
-      <c r="B293" s="17"/>
-      <c r="C293" s="17"/>
-      <c r="D293" s="17"/>
-      <c r="E293" s="17"/>
+      <c r="A293" s="5" t="s">
+        <v>308</v>
+      </c>
+      <c r="B293" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C293" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D293" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E293" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
     </row>
     <row r="294">
-      <c r="A294" s="16"/>
-      <c r="B294" s="17"/>
-      <c r="C294" s="17"/>
-      <c r="D294" s="17"/>
-      <c r="E294" s="17"/>
+      <c r="A294" s="5" t="s">
+        <v>309</v>
+      </c>
+      <c r="B294" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D294" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E294" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
     </row>
     <row r="295">
-      <c r="A295" s="16"/>
-      <c r="B295" s="17"/>
-      <c r="C295" s="17"/>
-      <c r="D295" s="17"/>
-      <c r="E295" s="17"/>
+      <c r="A295" s="5" t="s">
+        <v>310</v>
+      </c>
+      <c r="B295" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C295" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D295" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E295" s="6" t="s">
+        <v>41</v>
+      </c>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
@@ -15622,7 +15687,12 @@
     <hyperlink r:id="rId287" ref="A288"/>
     <hyperlink r:id="rId288" ref="A289"/>
     <hyperlink r:id="rId289" ref="A290"/>
+    <hyperlink r:id="rId290" ref="A291"/>
+    <hyperlink r:id="rId291" ref="A292"/>
+    <hyperlink r:id="rId292" ref="A293"/>
+    <hyperlink r:id="rId293" ref="A294"/>
+    <hyperlink r:id="rId294" ref="A295"/>
   </hyperlinks>
-  <drawing r:id="rId290"/>
+  <drawing r:id="rId295"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$996</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$967</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1491" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="282">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -381,18 +381,9 @@
     <t>https://heatlabs.net/maps</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/afghanistan</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/afghanistan-2</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/aircraft-carrier</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/avalanche</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/baikonur</t>
   </si>
   <si>
@@ -402,63 +393,15 @@
     <t>https://heatlabs.net/maps/blossom-crash</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/citadel</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/classified</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/comms</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/critical-harbor</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/crossroads</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/deadly-fields</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/desert-city</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/deserted</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/dolcegusta</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/duga</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/eden</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/evergreen</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/fatal-acres</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/harvest</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/height-911rs</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/height-911tb</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/hydro</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/inferno</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/kerak</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/military-training</t>
   </si>
   <si>
@@ -471,39 +414,15 @@
     <t>https://heatlabs.net/maps/nord-oko</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/port</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/project-phoenix</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/red-alert</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/ring-of-fury</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/scarred-city</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/spillway</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/sundered-city</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/sunstroke</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/surveillance</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/tajbeg</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/zenith</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/news</t>
   </si>
   <si>
@@ -849,9 +768,6 @@
     <t>https://heatlabs.net/tanks/leopard-2k-st</t>
   </si>
   <si>
-    <t>https://heatlabs.net/tanks/leopard-2k14</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/tanks/m1-railgun</t>
   </si>
   <si>
@@ -895,9 +811,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/tanks/t-72au</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/tanks/t-72b</t>
   </si>
   <si>
     <t>https://heatlabs.net/tanks/t-72sh</t>
@@ -1467,7 +1380,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>189</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4">
@@ -1561,7 +1474,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1571,7 +1484,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>224</v>
+        <v>198</v>
       </c>
     </row>
     <row r="8">
@@ -1665,7 +1578,7 @@
       <c r="G11" s="10">
         <f>COUNTIF(D:D,"UNKNOWN")
 </f>
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="H11" s="10">
         <f>COUNTIF(D:D,"NOT HTTPS")
@@ -1675,7 +1588,7 @@
       <c r="I11" s="10">
         <f>COUNTIF(D:D,"HTTPS")
 </f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12">
@@ -1769,7 +1682,7 @@
       <c r="G15" s="10">
         <f>COUNTIF(E:E,"UNKNOWN")
 </f>
-        <v>260</v>
+        <v>232</v>
       </c>
       <c r="H15" s="10">
         <f>COUNTIF(E:E,"INVALID")
@@ -1779,7 +1692,7 @@
       <c r="I15" s="10">
         <f>COUNTIF(E:E,"VALID")
 </f>
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="16">
@@ -3698,7 +3611,7 @@
         <v>122</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>7</v>
@@ -3719,16 +3632,16 @@
         <v>123</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -3740,10 +3653,10 @@
         <v>124</v>
       </c>
       <c r="B109" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>15</v>
@@ -3782,7 +3695,7 @@
         <v>126</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>7</v>
@@ -3803,7 +3716,7 @@
         <v>127</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>8</v>
@@ -3866,7 +3779,7 @@
         <v>130</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>7</v>
@@ -3887,10 +3800,10 @@
         <v>131</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>15</v>
@@ -3908,7 +3821,7 @@
         <v>132</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
@@ -3929,7 +3842,7 @@
         <v>133</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>7</v>
@@ -3998,10 +3911,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -4034,7 +3947,7 @@
         <v>138</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
@@ -4055,10 +3968,10 @@
         <v>139</v>
       </c>
       <c r="B124" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>15</v>
@@ -4163,7 +4076,7 @@
         <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>15</v>
@@ -4265,7 +4178,7 @@
         <v>149</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
         <v>7</v>
@@ -4286,10 +4199,10 @@
         <v>150</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>15</v>
@@ -4307,10 +4220,10 @@
         <v>151</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -4349,7 +4262,7 @@
         <v>153</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
         <v>7</v>
@@ -4415,7 +4328,7 @@
         <v>7</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>15</v>
@@ -4436,7 +4349,7 @@
         <v>7</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D142" s="6" t="s">
         <v>15</v>
@@ -4499,7 +4412,7 @@
         <v>7</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>15</v>
@@ -4562,13 +4475,13 @@
         <v>7</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -4601,7 +4514,7 @@
         <v>165</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>7</v>
@@ -4685,7 +4598,7 @@
         <v>169</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>7</v>
@@ -4727,10 +4640,10 @@
         <v>171</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>15</v>
@@ -4751,7 +4664,7 @@
         <v>7</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>15</v>
@@ -4793,7 +4706,7 @@
         <v>7</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4811,7 +4724,7 @@
         <v>175</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>7</v>
@@ -4853,10 +4766,10 @@
         <v>177</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>15</v>
@@ -4874,7 +4787,7 @@
         <v>178</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C163" s="6" t="s">
         <v>8</v>
@@ -4895,7 +4808,7 @@
         <v>179</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>7</v>
@@ -4937,10 +4850,10 @@
         <v>181</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>15</v>
@@ -4982,7 +4895,7 @@
         <v>7</v>
       </c>
       <c r="C168" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D168" s="6" t="s">
         <v>15</v>
@@ -5105,10 +5018,10 @@
         <v>189</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C174" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D174" s="6" t="s">
         <v>15</v>
@@ -5126,7 +5039,7 @@
         <v>190</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C175" s="6" t="s">
         <v>8</v>
@@ -5147,10 +5060,10 @@
         <v>191</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>15</v>
@@ -5168,10 +5081,10 @@
         <v>192</v>
       </c>
       <c r="B177" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>15</v>
@@ -5192,7 +5105,7 @@
         <v>7</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>15</v>
@@ -5213,7 +5126,7 @@
         <v>7</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>15</v>
@@ -5273,7 +5186,7 @@
         <v>197</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>7</v>
@@ -5315,7 +5228,7 @@
         <v>199</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>8</v>
@@ -5339,7 +5252,7 @@
         <v>7</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>15</v>
@@ -5360,7 +5273,7 @@
         <v>7</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D186" s="6" t="s">
         <v>15</v>
@@ -5399,7 +5312,7 @@
         <v>203</v>
       </c>
       <c r="B188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
         <v>7</v>
@@ -5420,16 +5333,16 @@
         <v>204</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -5444,7 +5357,7 @@
         <v>8</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D190" s="6" t="s">
         <v>15</v>
@@ -5483,7 +5396,7 @@
         <v>207</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>7</v>
@@ -5525,7 +5438,7 @@
         <v>209</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>7</v>
@@ -5546,7 +5459,7 @@
         <v>210</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>7</v>
@@ -5588,16 +5501,16 @@
         <v>212</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -5615,10 +5528,10 @@
         <v>7</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -5651,7 +5564,7 @@
         <v>215</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>7</v>
@@ -5668,14 +5581,14 @@
       <c r="I200" s="2"/>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="s">
+      <c r="A201" s="14" t="s">
         <v>216</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C201" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D201" s="6" t="s">
         <v>15</v>
@@ -5693,10 +5606,10 @@
         <v>217</v>
       </c>
       <c r="B202" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C202" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D202" s="6" t="s">
         <v>15</v>
@@ -5714,10 +5627,10 @@
         <v>218</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>15</v>
@@ -5731,7 +5644,7 @@
       <c r="I203" s="2"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="s">
+      <c r="A204" s="14" t="s">
         <v>219</v>
       </c>
       <c r="B204" s="6" t="s">
@@ -5759,7 +5672,7 @@
         <v>7</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>15</v>
@@ -5780,7 +5693,7 @@
         <v>7</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>15</v>
@@ -5815,14 +5728,14 @@
       <c r="I207" s="2"/>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="s">
+      <c r="A208" s="14" t="s">
         <v>223</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>15</v>
@@ -5840,7 +5753,7 @@
         <v>224</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>7</v>
@@ -5857,14 +5770,14 @@
       <c r="I209" s="2"/>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="s">
+      <c r="A210" s="14" t="s">
         <v>225</v>
       </c>
       <c r="B210" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>15</v>
@@ -5885,7 +5798,7 @@
         <v>8</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D211" s="6" t="s">
         <v>15</v>
@@ -5906,13 +5819,13 @@
         <v>7</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D212" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E212" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
@@ -5924,7 +5837,7 @@
         <v>228</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C213" s="6" t="s">
         <v>7</v>
@@ -5945,7 +5858,7 @@
         <v>229</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C214" s="6" t="s">
         <v>7</v>
@@ -5966,7 +5879,7 @@
         <v>230</v>
       </c>
       <c r="B215" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C215" s="6" t="s">
         <v>7</v>
@@ -5987,7 +5900,7 @@
         <v>231</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>7</v>
@@ -6008,16 +5921,16 @@
         <v>232</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -6025,14 +5938,14 @@
       <c r="I217" s="2"/>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="s">
+      <c r="A218" s="14" t="s">
         <v>233</v>
       </c>
       <c r="B218" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D218" s="6" t="s">
         <v>15</v>
@@ -6050,7 +5963,7 @@
         <v>234</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
@@ -6071,10 +5984,10 @@
         <v>235</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C220" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D220" s="6" t="s">
         <v>15</v>
@@ -6088,7 +6001,7 @@
       <c r="I220" s="2"/>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="s">
+      <c r="A221" s="14" t="s">
         <v>236</v>
       </c>
       <c r="B221" s="6" t="s">
@@ -6098,10 +6011,10 @@
         <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -6109,7 +6022,7 @@
       <c r="I221" s="2"/>
     </row>
     <row r="222">
-      <c r="A222" s="5" t="s">
+      <c r="A222" s="14" t="s">
         <v>237</v>
       </c>
       <c r="B222" s="6" t="s">
@@ -6140,10 +6053,10 @@
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -6151,7 +6064,7 @@
       <c r="I223" s="2"/>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="s">
+      <c r="A224" s="14" t="s">
         <v>239</v>
       </c>
       <c r="B224" s="6" t="s">
@@ -6161,10 +6074,10 @@
         <v>7</v>
       </c>
       <c r="D224" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E224" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
@@ -6214,20 +6127,20 @@
       <c r="I226" s="2"/>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="s">
+      <c r="A227" s="15" t="s">
         <v>242</v>
       </c>
       <c r="B227" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C227" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
@@ -6235,11 +6148,11 @@
       <c r="I227" s="2"/>
     </row>
     <row r="228">
-      <c r="A228" s="14" t="s">
+      <c r="A228" s="5" t="s">
         <v>243</v>
       </c>
       <c r="B228" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C228" s="6" t="s">
         <v>7</v>
@@ -6298,14 +6211,14 @@
       <c r="I230" s="2"/>
     </row>
     <row r="231">
-      <c r="A231" s="14" t="s">
+      <c r="A231" s="5" t="s">
         <v>246</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D231" s="6" t="s">
         <v>15</v>
@@ -6382,7 +6295,7 @@
       <c r="I234" s="2"/>
     </row>
     <row r="235">
-      <c r="A235" s="14" t="s">
+      <c r="A235" s="5" t="s">
         <v>250</v>
       </c>
       <c r="B235" s="6" t="s">
@@ -6449,7 +6362,7 @@
         <v>253</v>
       </c>
       <c r="B238" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C238" s="6" t="s">
         <v>7</v>
@@ -6476,10 +6389,10 @@
         <v>7</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
@@ -6491,7 +6404,7 @@
         <v>255</v>
       </c>
       <c r="B240" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C240" s="6" t="s">
         <v>7</v>
@@ -6554,16 +6467,16 @@
         <v>258</v>
       </c>
       <c r="B243" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C243" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6581,10 +6494,10 @@
         <v>7</v>
       </c>
       <c r="D244" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
@@ -6592,14 +6505,14 @@
       <c r="I244" s="2"/>
     </row>
     <row r="245">
-      <c r="A245" s="14" t="s">
+      <c r="A245" s="5" t="s">
         <v>260</v>
       </c>
       <c r="B245" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D245" s="6" t="s">
         <v>15</v>
@@ -6655,11 +6568,11 @@
       <c r="I247" s="2"/>
     </row>
     <row r="248">
-      <c r="A248" s="14" t="s">
+      <c r="A248" s="5" t="s">
         <v>263</v>
       </c>
       <c r="B248" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C248" s="6" t="s">
         <v>7</v>
@@ -6676,11 +6589,11 @@
       <c r="I248" s="2"/>
     </row>
     <row r="249">
-      <c r="A249" s="14" t="s">
+      <c r="A249" s="5" t="s">
         <v>264</v>
       </c>
       <c r="B249" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C249" s="6" t="s">
         <v>7</v>
@@ -6707,10 +6620,10 @@
         <v>7</v>
       </c>
       <c r="D250" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E250" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
@@ -6725,7 +6638,7 @@
         <v>8</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D251" s="6" t="s">
         <v>15</v>
@@ -6749,10 +6662,10 @@
         <v>7</v>
       </c>
       <c r="D252" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E252" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
@@ -6781,7 +6694,7 @@
       <c r="I253" s="2"/>
     </row>
     <row r="254">
-      <c r="A254" s="15" t="s">
+      <c r="A254" s="5" t="s">
         <v>269</v>
       </c>
       <c r="B254" s="6" t="s">
@@ -6791,10 +6704,10 @@
         <v>7</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E254" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
@@ -6833,10 +6746,10 @@
         <v>7</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
@@ -6848,7 +6761,7 @@
         <v>272</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C257" s="6" t="s">
         <v>7</v>
@@ -6935,7 +6848,7 @@
         <v>7</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D261" s="6" t="s">
         <v>15</v>
@@ -6977,7 +6890,7 @@
         <v>7</v>
       </c>
       <c r="C263" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D263" s="6" t="s">
         <v>15</v>
@@ -6998,7 +6911,7 @@
         <v>7</v>
       </c>
       <c r="C264" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D264" s="6" t="s">
         <v>15</v>
@@ -7012,11 +6925,11 @@
       <c r="I264" s="2"/>
     </row>
     <row r="265">
-      <c r="A265" s="14" t="s">
+      <c r="A265" s="5" t="s">
         <v>280</v>
       </c>
       <c r="B265" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C265" s="6" t="s">
         <v>8</v>
@@ -7037,16 +6950,16 @@
         <v>281</v>
       </c>
       <c r="B266" s="6" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="C266" s="6" t="s">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D266" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="E266" s="6" t="s">
-        <v>15</v>
+        <v>41</v>
       </c>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
@@ -7054,609 +6967,319 @@
       <c r="I266" s="2"/>
     </row>
     <row r="267">
-      <c r="A267" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B267" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C267" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D267" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E267" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A267" s="16"/>
+      <c r="B267" s="17"/>
+      <c r="C267" s="17"/>
+      <c r="D267" s="17"/>
+      <c r="E267" s="17"/>
       <c r="F267" s="2"/>
       <c r="G267" s="2"/>
       <c r="H267" s="2"/>
       <c r="I267" s="2"/>
     </row>
     <row r="268">
-      <c r="A268" s="5" t="s">
-        <v>283</v>
-      </c>
-      <c r="B268" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C268" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D268" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E268" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A268" s="16"/>
+      <c r="B268" s="17"/>
+      <c r="C268" s="17"/>
+      <c r="D268" s="17"/>
+      <c r="E268" s="17"/>
       <c r="F268" s="2"/>
       <c r="G268" s="2"/>
       <c r="H268" s="2"/>
       <c r="I268" s="2"/>
     </row>
     <row r="269">
-      <c r="A269" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="B269" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C269" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D269" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E269" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A269" s="16"/>
+      <c r="B269" s="17"/>
+      <c r="C269" s="17"/>
+      <c r="D269" s="17"/>
+      <c r="E269" s="17"/>
       <c r="F269" s="2"/>
       <c r="G269" s="2"/>
       <c r="H269" s="2"/>
       <c r="I269" s="2"/>
     </row>
     <row r="270">
-      <c r="A270" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B270" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C270" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D270" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E270" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A270" s="16"/>
+      <c r="B270" s="17"/>
+      <c r="C270" s="17"/>
+      <c r="D270" s="17"/>
+      <c r="E270" s="17"/>
       <c r="F270" s="2"/>
       <c r="G270" s="2"/>
       <c r="H270" s="2"/>
       <c r="I270" s="2"/>
     </row>
     <row r="271">
-      <c r="A271" s="5" t="s">
-        <v>286</v>
-      </c>
-      <c r="B271" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C271" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D271" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E271" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A271" s="16"/>
+      <c r="B271" s="17"/>
+      <c r="C271" s="17"/>
+      <c r="D271" s="17"/>
+      <c r="E271" s="17"/>
       <c r="F271" s="2"/>
       <c r="G271" s="2"/>
       <c r="H271" s="2"/>
       <c r="I271" s="2"/>
     </row>
     <row r="272">
-      <c r="A272" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="B272" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C272" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D272" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E272" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A272" s="16"/>
+      <c r="B272" s="17"/>
+      <c r="C272" s="17"/>
+      <c r="D272" s="17"/>
+      <c r="E272" s="17"/>
       <c r="F272" s="2"/>
       <c r="G272" s="2"/>
       <c r="H272" s="2"/>
       <c r="I272" s="2"/>
     </row>
     <row r="273">
-      <c r="A273" s="5" t="s">
-        <v>288</v>
-      </c>
-      <c r="B273" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C273" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D273" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E273" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A273" s="16"/>
+      <c r="B273" s="17"/>
+      <c r="C273" s="17"/>
+      <c r="D273" s="17"/>
+      <c r="E273" s="17"/>
       <c r="F273" s="2"/>
       <c r="G273" s="2"/>
       <c r="H273" s="2"/>
       <c r="I273" s="2"/>
     </row>
     <row r="274">
-      <c r="A274" s="5" t="s">
-        <v>289</v>
-      </c>
-      <c r="B274" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C274" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D274" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E274" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A274" s="16"/>
+      <c r="B274" s="17"/>
+      <c r="C274" s="17"/>
+      <c r="D274" s="17"/>
+      <c r="E274" s="17"/>
       <c r="F274" s="2"/>
       <c r="G274" s="2"/>
       <c r="H274" s="2"/>
       <c r="I274" s="2"/>
     </row>
     <row r="275">
-      <c r="A275" s="5" t="s">
-        <v>290</v>
-      </c>
-      <c r="B275" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C275" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D275" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E275" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A275" s="16"/>
+      <c r="B275" s="17"/>
+      <c r="C275" s="17"/>
+      <c r="D275" s="17"/>
+      <c r="E275" s="17"/>
       <c r="F275" s="2"/>
       <c r="G275" s="2"/>
       <c r="H275" s="2"/>
       <c r="I275" s="2"/>
     </row>
     <row r="276">
-      <c r="A276" s="5" t="s">
-        <v>291</v>
-      </c>
-      <c r="B276" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C276" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D276" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E276" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A276" s="16"/>
+      <c r="B276" s="17"/>
+      <c r="C276" s="17"/>
+      <c r="D276" s="17"/>
+      <c r="E276" s="17"/>
       <c r="F276" s="2"/>
       <c r="G276" s="2"/>
       <c r="H276" s="2"/>
       <c r="I276" s="2"/>
     </row>
     <row r="277">
-      <c r="A277" s="5" t="s">
-        <v>292</v>
-      </c>
-      <c r="B277" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C277" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D277" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E277" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A277" s="16"/>
+      <c r="B277" s="17"/>
+      <c r="C277" s="17"/>
+      <c r="D277" s="17"/>
+      <c r="E277" s="17"/>
       <c r="F277" s="2"/>
       <c r="G277" s="2"/>
       <c r="H277" s="2"/>
       <c r="I277" s="2"/>
     </row>
     <row r="278">
-      <c r="A278" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="B278" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C278" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D278" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E278" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A278" s="16"/>
+      <c r="B278" s="17"/>
+      <c r="C278" s="17"/>
+      <c r="D278" s="17"/>
+      <c r="E278" s="17"/>
       <c r="F278" s="2"/>
       <c r="G278" s="2"/>
       <c r="H278" s="2"/>
       <c r="I278" s="2"/>
     </row>
     <row r="279">
-      <c r="A279" s="5" t="s">
-        <v>294</v>
-      </c>
-      <c r="B279" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C279" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D279" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E279" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A279" s="16"/>
+      <c r="B279" s="17"/>
+      <c r="C279" s="17"/>
+      <c r="D279" s="17"/>
+      <c r="E279" s="17"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
       <c r="H279" s="2"/>
       <c r="I279" s="2"/>
     </row>
     <row r="280">
-      <c r="A280" s="14" t="s">
-        <v>295</v>
-      </c>
-      <c r="B280" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C280" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D280" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E280" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A280" s="16"/>
+      <c r="B280" s="17"/>
+      <c r="C280" s="17"/>
+      <c r="D280" s="17"/>
+      <c r="E280" s="17"/>
       <c r="F280" s="2"/>
       <c r="G280" s="2"/>
       <c r="H280" s="2"/>
       <c r="I280" s="2"/>
     </row>
     <row r="281">
-      <c r="A281" s="5" t="s">
-        <v>296</v>
-      </c>
-      <c r="B281" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C281" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D281" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E281" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A281" s="16"/>
+      <c r="B281" s="17"/>
+      <c r="C281" s="17"/>
+      <c r="D281" s="17"/>
+      <c r="E281" s="17"/>
       <c r="F281" s="2"/>
       <c r="G281" s="2"/>
       <c r="H281" s="2"/>
       <c r="I281" s="2"/>
     </row>
     <row r="282">
-      <c r="A282" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="B282" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C282" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D282" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E282" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A282" s="16"/>
+      <c r="B282" s="17"/>
+      <c r="C282" s="17"/>
+      <c r="D282" s="17"/>
+      <c r="E282" s="17"/>
       <c r="F282" s="2"/>
       <c r="G282" s="2"/>
       <c r="H282" s="2"/>
       <c r="I282" s="2"/>
     </row>
     <row r="283">
-      <c r="A283" s="5" t="s">
-        <v>298</v>
-      </c>
-      <c r="B283" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C283" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D283" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E283" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A283" s="16"/>
+      <c r="B283" s="17"/>
+      <c r="C283" s="17"/>
+      <c r="D283" s="17"/>
+      <c r="E283" s="17"/>
       <c r="F283" s="2"/>
       <c r="G283" s="2"/>
       <c r="H283" s="2"/>
       <c r="I283" s="2"/>
     </row>
     <row r="284">
-      <c r="A284" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="B284" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D284" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E284" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A284" s="16"/>
+      <c r="B284" s="17"/>
+      <c r="C284" s="17"/>
+      <c r="D284" s="17"/>
+      <c r="E284" s="17"/>
       <c r="F284" s="2"/>
       <c r="G284" s="2"/>
       <c r="H284" s="2"/>
       <c r="I284" s="2"/>
     </row>
     <row r="285">
-      <c r="A285" s="5" t="s">
-        <v>300</v>
-      </c>
-      <c r="B285" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C285" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D285" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E285" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A285" s="16"/>
+      <c r="B285" s="17"/>
+      <c r="C285" s="17"/>
+      <c r="D285" s="17"/>
+      <c r="E285" s="17"/>
       <c r="F285" s="2"/>
       <c r="G285" s="2"/>
       <c r="H285" s="2"/>
       <c r="I285" s="2"/>
     </row>
     <row r="286">
-      <c r="A286" s="5" t="s">
-        <v>301</v>
-      </c>
-      <c r="B286" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C286" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D286" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E286" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A286" s="16"/>
+      <c r="B286" s="17"/>
+      <c r="C286" s="17"/>
+      <c r="D286" s="17"/>
+      <c r="E286" s="17"/>
       <c r="F286" s="2"/>
       <c r="G286" s="2"/>
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
     </row>
     <row r="287">
-      <c r="A287" s="5" t="s">
-        <v>302</v>
-      </c>
-      <c r="B287" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C287" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D287" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E287" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A287" s="16"/>
+      <c r="B287" s="17"/>
+      <c r="C287" s="17"/>
+      <c r="D287" s="17"/>
+      <c r="E287" s="17"/>
       <c r="F287" s="2"/>
       <c r="G287" s="2"/>
       <c r="H287" s="2"/>
       <c r="I287" s="2"/>
     </row>
     <row r="288">
-      <c r="A288" s="5" t="s">
-        <v>303</v>
-      </c>
-      <c r="B288" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C288" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D288" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E288" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A288" s="16"/>
+      <c r="B288" s="17"/>
+      <c r="C288" s="17"/>
+      <c r="D288" s="17"/>
+      <c r="E288" s="17"/>
       <c r="F288" s="2"/>
       <c r="G288" s="2"/>
       <c r="H288" s="2"/>
       <c r="I288" s="2"/>
     </row>
     <row r="289">
-      <c r="A289" s="5" t="s">
-        <v>304</v>
-      </c>
-      <c r="B289" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C289" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D289" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E289" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A289" s="16"/>
+      <c r="B289" s="17"/>
+      <c r="C289" s="17"/>
+      <c r="D289" s="17"/>
+      <c r="E289" s="17"/>
       <c r="F289" s="2"/>
       <c r="G289" s="2"/>
       <c r="H289" s="2"/>
       <c r="I289" s="2"/>
     </row>
     <row r="290">
-      <c r="A290" s="5" t="s">
-        <v>305</v>
-      </c>
-      <c r="B290" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C290" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D290" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E290" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A290" s="16"/>
+      <c r="B290" s="17"/>
+      <c r="C290" s="17"/>
+      <c r="D290" s="17"/>
+      <c r="E290" s="17"/>
       <c r="F290" s="2"/>
       <c r="G290" s="2"/>
       <c r="H290" s="2"/>
       <c r="I290" s="2"/>
     </row>
     <row r="291">
-      <c r="A291" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="B291" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C291" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D291" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E291" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A291" s="16"/>
+      <c r="B291" s="17"/>
+      <c r="C291" s="17"/>
+      <c r="D291" s="17"/>
+      <c r="E291" s="17"/>
       <c r="F291" s="2"/>
       <c r="G291" s="2"/>
       <c r="H291" s="2"/>
       <c r="I291" s="2"/>
     </row>
     <row r="292">
-      <c r="A292" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="B292" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C292" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D292" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E292" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A292" s="16"/>
+      <c r="B292" s="17"/>
+      <c r="C292" s="17"/>
+      <c r="D292" s="17"/>
+      <c r="E292" s="17"/>
       <c r="F292" s="2"/>
       <c r="G292" s="2"/>
       <c r="H292" s="2"/>
       <c r="I292" s="2"/>
     </row>
     <row r="293">
-      <c r="A293" s="5" t="s">
-        <v>308</v>
-      </c>
-      <c r="B293" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C293" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D293" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E293" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A293" s="16"/>
+      <c r="B293" s="17"/>
+      <c r="C293" s="17"/>
+      <c r="D293" s="17"/>
+      <c r="E293" s="17"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
       <c r="H293" s="2"/>
       <c r="I293" s="2"/>
     </row>
     <row r="294">
-      <c r="A294" s="5" t="s">
-        <v>309</v>
-      </c>
-      <c r="B294" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C294" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D294" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E294" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A294" s="16"/>
+      <c r="B294" s="17"/>
+      <c r="C294" s="17"/>
+      <c r="D294" s="17"/>
+      <c r="E294" s="17"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
       <c r="H294" s="2"/>
       <c r="I294" s="2"/>
     </row>
     <row r="295">
-      <c r="A295" s="5" t="s">
-        <v>310</v>
-      </c>
-      <c r="B295" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C295" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D295" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E295" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="A295" s="16"/>
+      <c r="B295" s="17"/>
+      <c r="C295" s="17"/>
+      <c r="D295" s="17"/>
+      <c r="E295" s="17"/>
       <c r="F295" s="2"/>
       <c r="G295" s="2"/>
       <c r="H295" s="2"/>
@@ -15054,330 +14677,11 @@
       <c r="H967" s="2"/>
       <c r="I967" s="2"/>
     </row>
-    <row r="968">
-      <c r="A968" s="16"/>
-      <c r="B968" s="17"/>
-      <c r="C968" s="17"/>
-      <c r="D968" s="17"/>
-      <c r="E968" s="17"/>
-      <c r="F968" s="2"/>
-      <c r="G968" s="2"/>
-      <c r="H968" s="2"/>
-      <c r="I968" s="2"/>
-    </row>
-    <row r="969">
-      <c r="A969" s="16"/>
-      <c r="B969" s="17"/>
-      <c r="C969" s="17"/>
-      <c r="D969" s="17"/>
-      <c r="E969" s="17"/>
-      <c r="F969" s="2"/>
-      <c r="G969" s="2"/>
-      <c r="H969" s="2"/>
-      <c r="I969" s="2"/>
-    </row>
-    <row r="970">
-      <c r="A970" s="16"/>
-      <c r="B970" s="17"/>
-      <c r="C970" s="17"/>
-      <c r="D970" s="17"/>
-      <c r="E970" s="17"/>
-      <c r="F970" s="2"/>
-      <c r="G970" s="2"/>
-      <c r="H970" s="2"/>
-      <c r="I970" s="2"/>
-    </row>
-    <row r="971">
-      <c r="A971" s="16"/>
-      <c r="B971" s="17"/>
-      <c r="C971" s="17"/>
-      <c r="D971" s="17"/>
-      <c r="E971" s="17"/>
-      <c r="F971" s="2"/>
-      <c r="G971" s="2"/>
-      <c r="H971" s="2"/>
-      <c r="I971" s="2"/>
-    </row>
-    <row r="972">
-      <c r="A972" s="16"/>
-      <c r="B972" s="17"/>
-      <c r="C972" s="17"/>
-      <c r="D972" s="17"/>
-      <c r="E972" s="17"/>
-      <c r="F972" s="2"/>
-      <c r="G972" s="2"/>
-      <c r="H972" s="2"/>
-      <c r="I972" s="2"/>
-    </row>
-    <row r="973">
-      <c r="A973" s="16"/>
-      <c r="B973" s="17"/>
-      <c r="C973" s="17"/>
-      <c r="D973" s="17"/>
-      <c r="E973" s="17"/>
-      <c r="F973" s="2"/>
-      <c r="G973" s="2"/>
-      <c r="H973" s="2"/>
-      <c r="I973" s="2"/>
-    </row>
-    <row r="974">
-      <c r="A974" s="16"/>
-      <c r="B974" s="17"/>
-      <c r="C974" s="17"/>
-      <c r="D974" s="17"/>
-      <c r="E974" s="17"/>
-      <c r="F974" s="2"/>
-      <c r="G974" s="2"/>
-      <c r="H974" s="2"/>
-      <c r="I974" s="2"/>
-    </row>
-    <row r="975">
-      <c r="A975" s="16"/>
-      <c r="B975" s="17"/>
-      <c r="C975" s="17"/>
-      <c r="D975" s="17"/>
-      <c r="E975" s="17"/>
-      <c r="F975" s="2"/>
-      <c r="G975" s="2"/>
-      <c r="H975" s="2"/>
-      <c r="I975" s="2"/>
-    </row>
-    <row r="976">
-      <c r="A976" s="16"/>
-      <c r="B976" s="17"/>
-      <c r="C976" s="17"/>
-      <c r="D976" s="17"/>
-      <c r="E976" s="17"/>
-      <c r="F976" s="2"/>
-      <c r="G976" s="2"/>
-      <c r="H976" s="2"/>
-      <c r="I976" s="2"/>
-    </row>
-    <row r="977">
-      <c r="A977" s="16"/>
-      <c r="B977" s="17"/>
-      <c r="C977" s="17"/>
-      <c r="D977" s="17"/>
-      <c r="E977" s="17"/>
-      <c r="F977" s="2"/>
-      <c r="G977" s="2"/>
-      <c r="H977" s="2"/>
-      <c r="I977" s="2"/>
-    </row>
-    <row r="978">
-      <c r="A978" s="16"/>
-      <c r="B978" s="17"/>
-      <c r="C978" s="17"/>
-      <c r="D978" s="17"/>
-      <c r="E978" s="17"/>
-      <c r="F978" s="2"/>
-      <c r="G978" s="2"/>
-      <c r="H978" s="2"/>
-      <c r="I978" s="2"/>
-    </row>
-    <row r="979">
-      <c r="A979" s="16"/>
-      <c r="B979" s="17"/>
-      <c r="C979" s="17"/>
-      <c r="D979" s="17"/>
-      <c r="E979" s="17"/>
-      <c r="F979" s="2"/>
-      <c r="G979" s="2"/>
-      <c r="H979" s="2"/>
-      <c r="I979" s="2"/>
-    </row>
-    <row r="980">
-      <c r="A980" s="16"/>
-      <c r="B980" s="17"/>
-      <c r="C980" s="17"/>
-      <c r="D980" s="17"/>
-      <c r="E980" s="17"/>
-      <c r="F980" s="2"/>
-      <c r="G980" s="2"/>
-      <c r="H980" s="2"/>
-      <c r="I980" s="2"/>
-    </row>
-    <row r="981">
-      <c r="A981" s="16"/>
-      <c r="B981" s="17"/>
-      <c r="C981" s="17"/>
-      <c r="D981" s="17"/>
-      <c r="E981" s="17"/>
-      <c r="F981" s="2"/>
-      <c r="G981" s="2"/>
-      <c r="H981" s="2"/>
-      <c r="I981" s="2"/>
-    </row>
-    <row r="982">
-      <c r="A982" s="16"/>
-      <c r="B982" s="17"/>
-      <c r="C982" s="17"/>
-      <c r="D982" s="17"/>
-      <c r="E982" s="17"/>
-      <c r="F982" s="2"/>
-      <c r="G982" s="2"/>
-      <c r="H982" s="2"/>
-      <c r="I982" s="2"/>
-    </row>
-    <row r="983">
-      <c r="A983" s="16"/>
-      <c r="B983" s="17"/>
-      <c r="C983" s="17"/>
-      <c r="D983" s="17"/>
-      <c r="E983" s="17"/>
-      <c r="F983" s="2"/>
-      <c r="G983" s="2"/>
-      <c r="H983" s="2"/>
-      <c r="I983" s="2"/>
-    </row>
-    <row r="984">
-      <c r="A984" s="16"/>
-      <c r="B984" s="17"/>
-      <c r="C984" s="17"/>
-      <c r="D984" s="17"/>
-      <c r="E984" s="17"/>
-      <c r="F984" s="2"/>
-      <c r="G984" s="2"/>
-      <c r="H984" s="2"/>
-      <c r="I984" s="2"/>
-    </row>
-    <row r="985">
-      <c r="A985" s="16"/>
-      <c r="B985" s="17"/>
-      <c r="C985" s="17"/>
-      <c r="D985" s="17"/>
-      <c r="E985" s="17"/>
-      <c r="F985" s="2"/>
-      <c r="G985" s="2"/>
-      <c r="H985" s="2"/>
-      <c r="I985" s="2"/>
-    </row>
-    <row r="986">
-      <c r="A986" s="16"/>
-      <c r="B986" s="17"/>
-      <c r="C986" s="17"/>
-      <c r="D986" s="17"/>
-      <c r="E986" s="17"/>
-      <c r="F986" s="2"/>
-      <c r="G986" s="2"/>
-      <c r="H986" s="2"/>
-      <c r="I986" s="2"/>
-    </row>
-    <row r="987">
-      <c r="A987" s="16"/>
-      <c r="B987" s="17"/>
-      <c r="C987" s="17"/>
-      <c r="D987" s="17"/>
-      <c r="E987" s="17"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-      <c r="H987" s="2"/>
-      <c r="I987" s="2"/>
-    </row>
-    <row r="988">
-      <c r="A988" s="16"/>
-      <c r="B988" s="17"/>
-      <c r="C988" s="17"/>
-      <c r="D988" s="17"/>
-      <c r="E988" s="17"/>
-      <c r="F988" s="2"/>
-      <c r="G988" s="2"/>
-      <c r="H988" s="2"/>
-      <c r="I988" s="2"/>
-    </row>
-    <row r="989">
-      <c r="A989" s="16"/>
-      <c r="B989" s="17"/>
-      <c r="C989" s="17"/>
-      <c r="D989" s="17"/>
-      <c r="E989" s="17"/>
-      <c r="F989" s="2"/>
-      <c r="G989" s="2"/>
-      <c r="H989" s="2"/>
-      <c r="I989" s="2"/>
-    </row>
-    <row r="990">
-      <c r="A990" s="16"/>
-      <c r="B990" s="17"/>
-      <c r="C990" s="17"/>
-      <c r="D990" s="17"/>
-      <c r="E990" s="17"/>
-      <c r="F990" s="2"/>
-      <c r="G990" s="2"/>
-      <c r="H990" s="2"/>
-      <c r="I990" s="2"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="16"/>
-      <c r="B991" s="17"/>
-      <c r="C991" s="17"/>
-      <c r="D991" s="17"/>
-      <c r="E991" s="17"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-      <c r="H991" s="2"/>
-      <c r="I991" s="2"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="16"/>
-      <c r="B992" s="17"/>
-      <c r="C992" s="17"/>
-      <c r="D992" s="17"/>
-      <c r="E992" s="17"/>
-      <c r="F992" s="2"/>
-      <c r="G992" s="2"/>
-      <c r="H992" s="2"/>
-      <c r="I992" s="2"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="16"/>
-      <c r="B993" s="17"/>
-      <c r="C993" s="17"/>
-      <c r="D993" s="17"/>
-      <c r="E993" s="17"/>
-      <c r="F993" s="2"/>
-      <c r="G993" s="2"/>
-      <c r="H993" s="2"/>
-      <c r="I993" s="2"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="16"/>
-      <c r="B994" s="17"/>
-      <c r="C994" s="17"/>
-      <c r="D994" s="17"/>
-      <c r="E994" s="17"/>
-      <c r="F994" s="2"/>
-      <c r="G994" s="2"/>
-      <c r="H994" s="2"/>
-      <c r="I994" s="2"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="16"/>
-      <c r="B995" s="17"/>
-      <c r="C995" s="17"/>
-      <c r="D995" s="17"/>
-      <c r="E995" s="17"/>
-      <c r="F995" s="2"/>
-      <c r="G995" s="2"/>
-      <c r="H995" s="2"/>
-      <c r="I995" s="2"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="16"/>
-      <c r="B996" s="17"/>
-      <c r="C996" s="17"/>
-      <c r="D996" s="17"/>
-      <c r="E996" s="17"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-      <c r="H996" s="2"/>
-      <c r="I996" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$996">
-    <sortState ref="A1:E996">
-      <sortCondition ref="A1:A996"/>
-      <sortCondition ref="D1:D996"/>
+  <autoFilter ref="$A$1:$E$967">
+    <sortState ref="A1:E967">
+      <sortCondition ref="A1:A967"/>
+      <sortCondition ref="D1:D967"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -15387,13 +14691,13 @@
     <mergeCell ref="G13:I13"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C996">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C967">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D996">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D967">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E996">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E967">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -15663,36 +14967,7 @@
     <hyperlink r:id="rId263" ref="A264"/>
     <hyperlink r:id="rId264" ref="A265"/>
     <hyperlink r:id="rId265" ref="A266"/>
-    <hyperlink r:id="rId266" ref="A267"/>
-    <hyperlink r:id="rId267" ref="A268"/>
-    <hyperlink r:id="rId268" ref="A269"/>
-    <hyperlink r:id="rId269" ref="A270"/>
-    <hyperlink r:id="rId270" ref="A271"/>
-    <hyperlink r:id="rId271" ref="A272"/>
-    <hyperlink r:id="rId272" ref="A273"/>
-    <hyperlink r:id="rId273" ref="A274"/>
-    <hyperlink r:id="rId274" ref="A275"/>
-    <hyperlink r:id="rId275" ref="A276"/>
-    <hyperlink r:id="rId276" ref="A277"/>
-    <hyperlink r:id="rId277" ref="A278"/>
-    <hyperlink r:id="rId278" ref="A279"/>
-    <hyperlink r:id="rId279" ref="A280"/>
-    <hyperlink r:id="rId280" ref="A281"/>
-    <hyperlink r:id="rId281" ref="A282"/>
-    <hyperlink r:id="rId282" ref="A283"/>
-    <hyperlink r:id="rId283" ref="A284"/>
-    <hyperlink r:id="rId284" ref="A285"/>
-    <hyperlink r:id="rId285" ref="A286"/>
-    <hyperlink r:id="rId286" ref="A287"/>
-    <hyperlink r:id="rId287" ref="A288"/>
-    <hyperlink r:id="rId288" ref="A289"/>
-    <hyperlink r:id="rId289" ref="A290"/>
-    <hyperlink r:id="rId290" ref="A291"/>
-    <hyperlink r:id="rId291" ref="A292"/>
-    <hyperlink r:id="rId292" ref="A293"/>
-    <hyperlink r:id="rId293" ref="A294"/>
-    <hyperlink r:id="rId294" ref="A295"/>
   </hyperlinks>
-  <drawing r:id="rId295"/>
+  <drawing r:id="rId266"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$967</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$960</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="274">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -81,15 +81,6 @@
     <t>HTTPS PAGE STATUS</t>
   </si>
   <si>
-    <t>https://heatlabs.net/agents/arblast</t>
-  </si>
-  <si>
-    <t>NOT HTTPS</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/agents/atom</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/agents/blitz</t>
   </si>
   <si>
@@ -105,24 +96,15 @@
     <t>INVALID</t>
   </si>
   <si>
-    <t>https://heatlabs.net/agents/fantome</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/agents/flair</t>
   </si>
   <si>
     <t>https://heatlabs.net/agents/hound</t>
   </si>
   <si>
-    <t>https://heatlabs.net/agents/jager</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/agents/kent</t>
   </si>
   <si>
-    <t>https://heatlabs.net/agents/punch</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/agents/raketa</t>
   </si>
   <si>
@@ -820,12 +802,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/tanks/xm1-v</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/tanks/xm551</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/tanks/xm808-twister</t>
   </si>
   <si>
     <t>https://heatlabs.net/tournaments</t>
@@ -1380,7 +1356,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>160</v>
+        <v>153</v>
       </c>
     </row>
     <row r="4">
@@ -1474,7 +1450,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1484,7 +1460,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
     <row r="8">
@@ -1548,48 +1524,32 @@
         <v>15</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>9</v>
-      </c>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="10">
-        <f>COUNTIF(D:D,"UNKNOWN")
-</f>
-        <v>232</v>
-      </c>
-      <c r="H11" s="10">
-        <f>COUNTIF(D:D,"NOT HTTPS")
-</f>
-        <v>0</v>
-      </c>
-      <c r="I11" s="10">
-        <f>COUNTIF(D:D,"HTTPS")
-</f>
-        <v>31</v>
-      </c>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
@@ -1608,19 +1568,25 @@
         <v>15</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
+      <c r="G12" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="I12" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>15</v>
@@ -1629,18 +1595,16 @@
         <v>15</v>
       </c>
       <c r="F13" s="2"/>
-      <c r="G13" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
         <v>28</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>7</v>
@@ -1652,22 +1616,16 @@
         <v>15</v>
       </c>
       <c r="F14" s="2"/>
-      <c r="G14" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H14" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="I14" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C15" s="6" t="s">
         <v>7</v>
@@ -1679,31 +1637,19 @@
         <v>15</v>
       </c>
       <c r="F15" s="2"/>
-      <c r="G15" s="10">
-        <f>COUNTIF(E:E,"UNKNOWN")
-</f>
-        <v>232</v>
-      </c>
-      <c r="H15" s="10">
-        <f>COUNTIF(E:E,"INVALID")
-</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="10">
-        <f>COUNTIF(E:E,"VALID")
-</f>
-        <v>31</v>
-      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>15</v>
@@ -1718,10 +1664,10 @@
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>7</v>
@@ -1739,13 +1685,13 @@
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>15</v>
@@ -1760,10 +1706,10 @@
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="6" t="s">
         <v>7</v>
@@ -1781,19 +1727,19 @@
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="C20" s="6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1889,16 +1835,16 @@
         <v>40</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>41</v>
+        <v>7</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
@@ -1907,10 +1853,10 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="6" t="s">
         <v>7</v>
@@ -1928,7 +1874,7 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>7</v>
@@ -1949,7 +1895,7 @@
     </row>
     <row r="28">
       <c r="A28" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>7</v>
@@ -1970,7 +1916,7 @@
     </row>
     <row r="29">
       <c r="A29" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>7</v>
@@ -1991,13 +1937,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>15</v>
@@ -2012,7 +1958,7 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>7</v>
@@ -2033,7 +1979,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>7</v>
@@ -2042,10 +1988,10 @@
         <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2054,7 +2000,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>7</v>
@@ -2063,10 +2009,10 @@
         <v>7</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -2075,13 +2021,13 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>15</v>
@@ -2096,13 +2042,13 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>15</v>
@@ -2117,13 +2063,13 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>15</v>
@@ -2138,19 +2084,19 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
@@ -2159,19 +2105,19 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F38" s="2"/>
       <c r="G38" s="2"/>
@@ -2179,14 +2125,14 @@
       <c r="I38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="s">
-        <v>55</v>
+      <c r="A39" s="14" t="s">
+        <v>54</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>15</v>
@@ -2201,13 +2147,13 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>15</v>
@@ -2222,7 +2168,7 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
@@ -2243,13 +2189,13 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>15</v>
@@ -2264,7 +2210,7 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
@@ -2284,20 +2230,20 @@
       <c r="I43" s="2"/>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="s">
-        <v>60</v>
+      <c r="A44" s="5" t="s">
+        <v>59</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -2306,13 +2252,13 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>15</v>
@@ -2327,7 +2273,7 @@
     </row>
     <row r="46">
       <c r="A46" s="5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -2348,13 +2294,13 @@
     </row>
     <row r="47">
       <c r="A47" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D47" s="6" t="s">
         <v>15</v>
@@ -2369,13 +2315,13 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>15</v>
@@ -2390,19 +2336,19 @@
     </row>
     <row r="49">
       <c r="A49" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2411,7 +2357,7 @@
     </row>
     <row r="50">
       <c r="A50" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
@@ -2432,13 +2378,13 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>15</v>
@@ -2453,7 +2399,7 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" s="6" t="s">
         <v>8</v>
@@ -2474,7 +2420,7 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>8</v>
@@ -2495,13 +2441,13 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B54" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>15</v>
@@ -2516,13 +2462,13 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B55" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>15</v>
@@ -2537,7 +2483,7 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -2557,20 +2503,20 @@
       <c r="I56" s="2"/>
     </row>
     <row r="57">
-      <c r="A57" s="5" t="s">
-        <v>73</v>
+      <c r="A57" s="14" t="s">
+        <v>72</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -2579,19 +2525,19 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -2600,13 +2546,13 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B59" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>15</v>
@@ -2620,8 +2566,8 @@
       <c r="I59" s="2"/>
     </row>
     <row r="60">
-      <c r="A60" s="5" t="s">
-        <v>76</v>
+      <c r="A60" s="14" t="s">
+        <v>75</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>8</v>
@@ -2642,13 +2588,13 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>15</v>
@@ -2662,20 +2608,20 @@
       <c r="I61" s="2"/>
     </row>
     <row r="62">
-      <c r="A62" s="14" t="s">
-        <v>78</v>
+      <c r="A62" s="5" t="s">
+        <v>77</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F62" s="2"/>
       <c r="G62" s="2"/>
@@ -2684,19 +2630,19 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F63" s="2"/>
       <c r="G63" s="2"/>
@@ -2705,19 +2651,19 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B64" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -2725,11 +2671,11 @@
       <c r="I64" s="2"/>
     </row>
     <row r="65">
-      <c r="A65" s="14" t="s">
-        <v>81</v>
+      <c r="A65" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>7</v>
@@ -2747,13 +2693,13 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D66" s="6" t="s">
         <v>15</v>
@@ -2768,13 +2714,13 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D67" s="6" t="s">
         <v>15</v>
@@ -2789,13 +2735,13 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B68" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>15</v>
@@ -2810,19 +2756,19 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F69" s="2"/>
       <c r="G69" s="2"/>
@@ -2831,7 +2777,7 @@
     </row>
     <row r="70">
       <c r="A70" s="5" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>7</v>
@@ -2852,13 +2798,13 @@
     </row>
     <row r="71">
       <c r="A71" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>15</v>
@@ -2873,7 +2819,7 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>8</v>
@@ -2894,7 +2840,7 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>8</v>
@@ -2915,13 +2861,13 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B74" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>15</v>
@@ -2936,7 +2882,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>7</v>
@@ -2957,13 +2903,13 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -2978,7 +2924,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>8</v>
@@ -2999,13 +2945,13 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>15</v>
@@ -3020,7 +2966,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
@@ -3041,13 +2987,13 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>15</v>
@@ -3061,8 +3007,8 @@
       <c r="I80" s="2"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="s">
-        <v>97</v>
+      <c r="A81" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>8</v>
@@ -3083,19 +3029,19 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -3104,19 +3050,19 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -3125,19 +3071,19 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -3146,13 +3092,13 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="6" t="s">
         <v>15</v>
@@ -3167,13 +3113,13 @@
     </row>
     <row r="86">
       <c r="A86" s="14" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" s="6" t="s">
         <v>15</v>
@@ -3187,20 +3133,20 @@
       <c r="I86" s="2"/>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="s">
-        <v>103</v>
+      <c r="A87" s="14" t="s">
+        <v>101</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -3209,7 +3155,7 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>7</v>
@@ -3218,10 +3164,10 @@
         <v>7</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -3230,7 +3176,7 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B89" s="6" t="s">
         <v>7</v>
@@ -3239,10 +3185,10 @@
         <v>7</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -3250,14 +3196,14 @@
       <c r="I89" s="2"/>
     </row>
     <row r="90">
-      <c r="A90" s="5" t="s">
-        <v>106</v>
+      <c r="A90" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>15</v>
@@ -3271,14 +3217,14 @@
       <c r="I90" s="2"/>
     </row>
     <row r="91">
-      <c r="A91" s="14" t="s">
-        <v>107</v>
+      <c r="A91" s="5" t="s">
+        <v>105</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D91" s="6" t="s">
         <v>15</v>
@@ -3292,14 +3238,14 @@
       <c r="I91" s="2"/>
     </row>
     <row r="92">
-      <c r="A92" s="14" t="s">
-        <v>107</v>
+      <c r="A92" s="5" t="s">
+        <v>106</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -3314,7 +3260,7 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
@@ -3323,10 +3269,10 @@
         <v>7</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -3335,7 +3281,7 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
@@ -3356,13 +3302,13 @@
     </row>
     <row r="95">
       <c r="A95" s="14" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D95" s="6" t="s">
         <v>15</v>
@@ -3377,7 +3323,7 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>7</v>
@@ -3386,10 +3332,10 @@
         <v>7</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -3398,13 +3344,13 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>15</v>
@@ -3419,7 +3365,7 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>7</v>
@@ -3440,13 +3386,13 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3460,8 +3406,8 @@
       <c r="I99" s="2"/>
     </row>
     <row r="100">
-      <c r="A100" s="14" t="s">
-        <v>115</v>
+      <c r="A100" s="5" t="s">
+        <v>114</v>
       </c>
       <c r="B100" s="6" t="s">
         <v>8</v>
@@ -3470,10 +3416,10 @@
         <v>7</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -3482,7 +3428,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -3503,13 +3449,13 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
         <v>15</v>
@@ -3524,19 +3470,19 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3545,7 +3491,7 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -3566,19 +3512,19 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B105" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -3587,7 +3533,7 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B106" s="6" t="s">
         <v>7</v>
@@ -3596,10 +3542,10 @@
         <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -3608,13 +3554,13 @@
     </row>
     <row r="107">
       <c r="A107" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>15</v>
@@ -3629,10 +3575,10 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>7</v>
@@ -3650,13 +3596,13 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D109" s="6" t="s">
         <v>15</v>
@@ -3671,10 +3617,10 @@
     </row>
     <row r="110">
       <c r="A110" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110" s="6" t="s">
         <v>7</v>
@@ -3692,10 +3638,10 @@
     </row>
     <row r="111">
       <c r="A111" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>7</v>
@@ -3713,13 +3659,13 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -3734,10 +3680,10 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>7</v>
@@ -3755,7 +3701,7 @@
     </row>
     <row r="114">
       <c r="A114" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>7</v>
@@ -3776,10 +3722,10 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>7</v>
@@ -3797,19 +3743,19 @@
     </row>
     <row r="116">
       <c r="A116" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -3818,10 +3764,10 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
@@ -3839,7 +3785,7 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
         <v>8</v>
@@ -3860,7 +3806,7 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>7</v>
@@ -3881,7 +3827,7 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B120" s="6" t="s">
         <v>7</v>
@@ -3902,7 +3848,7 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>7</v>
@@ -3911,10 +3857,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -3923,7 +3869,7 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B122" s="6" t="s">
         <v>7</v>
@@ -3944,10 +3890,10 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
@@ -3965,13 +3911,13 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>15</v>
@@ -3986,7 +3932,7 @@
     </row>
     <row r="125">
       <c r="A125" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>7</v>
@@ -4007,7 +3953,7 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>7</v>
@@ -4028,7 +3974,7 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
@@ -4049,7 +3995,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
@@ -4070,13 +4016,13 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>15</v>
@@ -4091,13 +4037,13 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>15</v>
@@ -4112,13 +4058,13 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>15</v>
@@ -4133,7 +4079,7 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
@@ -4154,7 +4100,7 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
@@ -4175,7 +4121,7 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B134" s="6" t="s">
         <v>7</v>
@@ -4196,13 +4142,13 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>15</v>
@@ -4217,7 +4163,7 @@
     </row>
     <row r="136">
       <c r="A136" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B136" s="6" t="s">
         <v>7</v>
@@ -4238,7 +4184,7 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
@@ -4259,7 +4205,7 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>7</v>
@@ -4280,7 +4226,7 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>7</v>
@@ -4301,7 +4247,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>7</v>
@@ -4322,13 +4268,13 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D141" s="6" t="s">
         <v>15</v>
@@ -4343,7 +4289,7 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>7</v>
@@ -4364,13 +4310,13 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4385,7 +4331,7 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>7</v>
@@ -4406,7 +4352,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>7</v>
@@ -4427,7 +4373,7 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>7</v>
@@ -4448,7 +4394,7 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>7</v>
@@ -4469,13 +4415,13 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>15</v>
@@ -4490,10 +4436,10 @@
     </row>
     <row r="149">
       <c r="A149" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>7</v>
@@ -4511,7 +4457,7 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>7</v>
@@ -4532,10 +4478,10 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>7</v>
@@ -4553,13 +4499,13 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>15</v>
@@ -4574,7 +4520,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>7</v>
@@ -4595,13 +4541,13 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>15</v>
@@ -4616,10 +4562,10 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>7</v>
@@ -4637,10 +4583,10 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>7</v>
@@ -4658,13 +4604,13 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>15</v>
@@ -4679,13 +4625,13 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>15</v>
@@ -4700,13 +4646,13 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4721,10 +4667,10 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>7</v>
@@ -4742,13 +4688,13 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>15</v>
@@ -4763,10 +4709,10 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C162" s="6" t="s">
         <v>7</v>
@@ -4784,13 +4730,13 @@
     </row>
     <row r="163">
       <c r="A163" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B163" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>15</v>
@@ -4805,10 +4751,10 @@
     </row>
     <row r="164">
       <c r="A164" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B164" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C164" s="6" t="s">
         <v>7</v>
@@ -4826,7 +4772,7 @@
     </row>
     <row r="165">
       <c r="A165" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B165" s="6" t="s">
         <v>7</v>
@@ -4847,13 +4793,13 @@
     </row>
     <row r="166">
       <c r="A166" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D166" s="6" t="s">
         <v>15</v>
@@ -4868,7 +4814,7 @@
     </row>
     <row r="167">
       <c r="A167" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B167" s="6" t="s">
         <v>7</v>
@@ -4889,7 +4835,7 @@
     </row>
     <row r="168">
       <c r="A168" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B168" s="6" t="s">
         <v>7</v>
@@ -4910,13 +4856,13 @@
     </row>
     <row r="169">
       <c r="A169" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>15</v>
@@ -4931,13 +4877,13 @@
     </row>
     <row r="170">
       <c r="A170" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B170" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C170" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D170" s="6" t="s">
         <v>15</v>
@@ -4952,13 +4898,13 @@
     </row>
     <row r="171">
       <c r="A171" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B171" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C171" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D171" s="6" t="s">
         <v>15</v>
@@ -4973,13 +4919,13 @@
     </row>
     <row r="172">
       <c r="A172" s="5" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B172" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C172" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D172" s="6" t="s">
         <v>15</v>
@@ -4994,13 +4940,13 @@
     </row>
     <row r="173">
       <c r="A173" s="5" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C173" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D173" s="6" t="s">
         <v>15</v>
@@ -5015,10 +4961,10 @@
     </row>
     <row r="174">
       <c r="A174" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B174" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C174" s="6" t="s">
         <v>8</v>
@@ -5036,13 +4982,13 @@
     </row>
     <row r="175">
       <c r="A175" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B175" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>15</v>
@@ -5057,13 +5003,13 @@
     </row>
     <row r="176">
       <c r="A176" s="5" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B176" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C176" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D176" s="6" t="s">
         <v>15</v>
@@ -5078,13 +5024,13 @@
     </row>
     <row r="177">
       <c r="A177" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B177" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D177" s="6" t="s">
         <v>15</v>
@@ -5099,13 +5045,13 @@
     </row>
     <row r="178">
       <c r="A178" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B178" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D178" s="6" t="s">
         <v>15</v>
@@ -5120,10 +5066,10 @@
     </row>
     <row r="179">
       <c r="A179" s="5" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B179" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C179" s="6" t="s">
         <v>8</v>
@@ -5141,13 +5087,13 @@
     </row>
     <row r="180">
       <c r="A180" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B180" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C180" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D180" s="6" t="s">
         <v>15</v>
@@ -5162,10 +5108,10 @@
     </row>
     <row r="181">
       <c r="A181" s="5" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B181" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C181" s="6" t="s">
         <v>7</v>
@@ -5183,7 +5129,7 @@
     </row>
     <row r="182">
       <c r="A182" s="5" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B182" s="6" t="s">
         <v>8</v>
@@ -5204,7 +5150,7 @@
     </row>
     <row r="183">
       <c r="A183" s="5" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>8</v>
@@ -5225,19 +5171,19 @@
     </row>
     <row r="184">
       <c r="A184" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C184" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -5246,13 +5192,13 @@
     </row>
     <row r="185">
       <c r="A185" s="5" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C185" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D185" s="6" t="s">
         <v>15</v>
@@ -5267,10 +5213,10 @@
     </row>
     <row r="186">
       <c r="A186" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B186" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C186" s="6" t="s">
         <v>7</v>
@@ -5288,7 +5234,7 @@
     </row>
     <row r="187">
       <c r="A187" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B187" s="6" t="s">
         <v>8</v>
@@ -5309,13 +5255,13 @@
     </row>
     <row r="188">
       <c r="A188" s="5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B188" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5330,19 +5276,19 @@
     </row>
     <row r="189">
       <c r="A189" s="5" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B189" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D189" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E189" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
@@ -5351,7 +5297,7 @@
     </row>
     <row r="190">
       <c r="A190" s="5" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B190" s="6" t="s">
         <v>8</v>
@@ -5372,10 +5318,10 @@
     </row>
     <row r="191">
       <c r="A191" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>7</v>
@@ -5393,7 +5339,7 @@
     </row>
     <row r="192">
       <c r="A192" s="5" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B192" s="6" t="s">
         <v>8</v>
@@ -5402,10 +5348,10 @@
         <v>7</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -5414,19 +5360,19 @@
     </row>
     <row r="193">
       <c r="A193" s="5" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D193" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E193" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
@@ -5435,10 +5381,10 @@
     </row>
     <row r="194">
       <c r="A194" s="5" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B194" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C194" s="6" t="s">
         <v>7</v>
@@ -5456,7 +5402,7 @@
     </row>
     <row r="195">
       <c r="A195" s="5" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B195" s="6" t="s">
         <v>8</v>
@@ -5476,11 +5422,11 @@
       <c r="I195" s="2"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="s">
-        <v>211</v>
+      <c r="A196" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="B196" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>7</v>
@@ -5498,19 +5444,19 @@
     </row>
     <row r="197">
       <c r="A197" s="5" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D197" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E197" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
@@ -5519,7 +5465,7 @@
     </row>
     <row r="198">
       <c r="A198" s="5" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B198" s="6" t="s">
         <v>7</v>
@@ -5528,10 +5474,10 @@
         <v>7</v>
       </c>
       <c r="D198" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E198" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
@@ -5539,14 +5485,14 @@
       <c r="I198" s="2"/>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="s">
-        <v>214</v>
+      <c r="A199" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>15</v>
@@ -5561,10 +5507,10 @@
     </row>
     <row r="200">
       <c r="A200" s="5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C200" s="6" t="s">
         <v>7</v>
@@ -5581,11 +5527,11 @@
       <c r="I200" s="2"/>
     </row>
     <row r="201">
-      <c r="A201" s="14" t="s">
-        <v>216</v>
+      <c r="A201" s="5" t="s">
+        <v>215</v>
       </c>
       <c r="B201" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C201" s="6" t="s">
         <v>7</v>
@@ -5603,7 +5549,7 @@
     </row>
     <row r="202">
       <c r="A202" s="5" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B202" s="6" t="s">
         <v>7</v>
@@ -5623,14 +5569,14 @@
       <c r="I202" s="2"/>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="s">
-        <v>218</v>
+      <c r="A203" s="14" t="s">
+        <v>217</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>15</v>
@@ -5644,14 +5590,14 @@
       <c r="I203" s="2"/>
     </row>
     <row r="204">
-      <c r="A204" s="14" t="s">
-        <v>219</v>
+      <c r="A204" s="5" t="s">
+        <v>218</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>15</v>
@@ -5665,14 +5611,14 @@
       <c r="I204" s="2"/>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="s">
-        <v>220</v>
+      <c r="A205" s="14" t="s">
+        <v>219</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>15</v>
@@ -5687,10 +5633,10 @@
     </row>
     <row r="206">
       <c r="A206" s="5" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B206" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C206" s="6" t="s">
         <v>7</v>
@@ -5708,7 +5654,7 @@
     </row>
     <row r="207">
       <c r="A207" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B207" s="6" t="s">
         <v>7</v>
@@ -5717,10 +5663,10 @@
         <v>7</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
@@ -5728,14 +5674,14 @@
       <c r="I207" s="2"/>
     </row>
     <row r="208">
-      <c r="A208" s="14" t="s">
-        <v>223</v>
+      <c r="A208" s="5" t="s">
+        <v>222</v>
       </c>
       <c r="B208" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D208" s="6" t="s">
         <v>15</v>
@@ -5750,7 +5696,7 @@
     </row>
     <row r="209">
       <c r="A209" s="5" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B209" s="6" t="s">
         <v>7</v>
@@ -5770,14 +5716,14 @@
       <c r="I209" s="2"/>
     </row>
     <row r="210">
-      <c r="A210" s="14" t="s">
-        <v>225</v>
+      <c r="A210" s="5" t="s">
+        <v>224</v>
       </c>
       <c r="B210" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C210" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D210" s="6" t="s">
         <v>15</v>
@@ -5792,7 +5738,7 @@
     </row>
     <row r="211">
       <c r="A211" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>8</v>
@@ -5801,10 +5747,10 @@
         <v>7</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -5813,7 +5759,7 @@
     </row>
     <row r="212">
       <c r="A212" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B212" s="6" t="s">
         <v>7</v>
@@ -5833,14 +5779,14 @@
       <c r="I212" s="2"/>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="s">
-        <v>228</v>
+      <c r="A213" s="14" t="s">
+        <v>227</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D213" s="6" t="s">
         <v>15</v>
@@ -5855,7 +5801,7 @@
     </row>
     <row r="214">
       <c r="A214" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B214" s="6" t="s">
         <v>7</v>
@@ -5876,7 +5822,7 @@
     </row>
     <row r="215">
       <c r="A215" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B215" s="6" t="s">
         <v>7</v>
@@ -5896,8 +5842,8 @@
       <c r="I215" s="2"/>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="s">
-        <v>231</v>
+      <c r="A216" s="14" t="s">
+        <v>230</v>
       </c>
       <c r="B216" s="6" t="s">
         <v>8</v>
@@ -5917,20 +5863,20 @@
       <c r="I216" s="2"/>
     </row>
     <row r="217">
-      <c r="A217" s="5" t="s">
-        <v>232</v>
+      <c r="A217" s="14" t="s">
+        <v>231</v>
       </c>
       <c r="B217" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C217" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -5938,20 +5884,20 @@
       <c r="I217" s="2"/>
     </row>
     <row r="218">
-      <c r="A218" s="14" t="s">
-        <v>233</v>
+      <c r="A218" s="5" t="s">
+        <v>232</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -5959,11 +5905,11 @@
       <c r="I218" s="2"/>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="s">
-        <v>234</v>
+      <c r="A219" s="14" t="s">
+        <v>233</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
@@ -5981,7 +5927,7 @@
     </row>
     <row r="220">
       <c r="A220" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B220" s="6" t="s">
         <v>7</v>
@@ -5990,10 +5936,10 @@
         <v>7</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -6001,20 +5947,20 @@
       <c r="I220" s="2"/>
     </row>
     <row r="221">
-      <c r="A221" s="14" t="s">
-        <v>236</v>
+      <c r="A221" s="5" t="s">
+        <v>235</v>
       </c>
       <c r="B221" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C221" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -6022,20 +5968,20 @@
       <c r="I221" s="2"/>
     </row>
     <row r="222">
-      <c r="A222" s="14" t="s">
-        <v>237</v>
+      <c r="A222" s="15" t="s">
+        <v>236</v>
       </c>
       <c r="B222" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -6044,7 +5990,7 @@
     </row>
     <row r="223">
       <c r="A223" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>7</v>
@@ -6053,10 +5999,10 @@
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -6064,11 +6010,11 @@
       <c r="I223" s="2"/>
     </row>
     <row r="224">
-      <c r="A224" s="14" t="s">
-        <v>239</v>
+      <c r="A224" s="5" t="s">
+        <v>238</v>
       </c>
       <c r="B224" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C224" s="6" t="s">
         <v>7</v>
@@ -6086,7 +6032,7 @@
     </row>
     <row r="225">
       <c r="A225" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B225" s="6" t="s">
         <v>7</v>
@@ -6095,10 +6041,10 @@
         <v>7</v>
       </c>
       <c r="D225" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E225" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
@@ -6107,7 +6053,7 @@
     </row>
     <row r="226">
       <c r="A226" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B226" s="6" t="s">
         <v>7</v>
@@ -6127,8 +6073,8 @@
       <c r="I226" s="2"/>
     </row>
     <row r="227">
-      <c r="A227" s="15" t="s">
-        <v>242</v>
+      <c r="A227" s="5" t="s">
+        <v>241</v>
       </c>
       <c r="B227" s="6" t="s">
         <v>7</v>
@@ -6137,10 +6083,10 @@
         <v>7</v>
       </c>
       <c r="D227" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E227" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
@@ -6149,7 +6095,7 @@
     </row>
     <row r="228">
       <c r="A228" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B228" s="6" t="s">
         <v>7</v>
@@ -6170,7 +6116,7 @@
     </row>
     <row r="229">
       <c r="A229" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B229" s="6" t="s">
         <v>7</v>
@@ -6191,13 +6137,13 @@
     </row>
     <row r="230">
       <c r="A230" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>15</v>
@@ -6212,7 +6158,7 @@
     </row>
     <row r="231">
       <c r="A231" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>7</v>
@@ -6232,14 +6178,14 @@
       <c r="I231" s="2"/>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="s">
-        <v>247</v>
+      <c r="A232" s="14" t="s">
+        <v>246</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D232" s="6" t="s">
         <v>15</v>
@@ -6254,7 +6200,7 @@
     </row>
     <row r="233">
       <c r="A233" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>7</v>
@@ -6275,7 +6221,7 @@
     </row>
     <row r="234">
       <c r="A234" s="5" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B234" s="6" t="s">
         <v>7</v>
@@ -6296,13 +6242,13 @@
     </row>
     <row r="235">
       <c r="A235" s="5" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B235" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D235" s="6" t="s">
         <v>15</v>
@@ -6317,7 +6263,7 @@
     </row>
     <row r="236">
       <c r="A236" s="5" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B236" s="6" t="s">
         <v>7</v>
@@ -6337,14 +6283,14 @@
       <c r="I236" s="2"/>
     </row>
     <row r="237">
-      <c r="A237" s="14" t="s">
-        <v>252</v>
+      <c r="A237" s="5" t="s">
+        <v>251</v>
       </c>
       <c r="B237" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D237" s="6" t="s">
         <v>15</v>
@@ -6359,7 +6305,7 @@
     </row>
     <row r="238">
       <c r="A238" s="5" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B238" s="6" t="s">
         <v>7</v>
@@ -6380,7 +6326,7 @@
     </row>
     <row r="239">
       <c r="A239" s="5" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B239" s="6" t="s">
         <v>7</v>
@@ -6401,7 +6347,7 @@
     </row>
     <row r="240">
       <c r="A240" s="5" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B240" s="6" t="s">
         <v>7</v>
@@ -6422,7 +6368,7 @@
     </row>
     <row r="241">
       <c r="A241" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>7</v>
@@ -6443,7 +6389,7 @@
     </row>
     <row r="242">
       <c r="A242" s="5" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B242" s="6" t="s">
         <v>7</v>
@@ -6464,7 +6410,7 @@
     </row>
     <row r="243">
       <c r="A243" s="5" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>7</v>
@@ -6473,10 +6419,10 @@
         <v>7</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
@@ -6485,7 +6431,7 @@
     </row>
     <row r="244">
       <c r="A244" s="5" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B244" s="6" t="s">
         <v>7</v>
@@ -6506,7 +6452,7 @@
     </row>
     <row r="245">
       <c r="A245" s="5" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B245" s="6" t="s">
         <v>7</v>
@@ -6526,14 +6472,14 @@
       <c r="I245" s="2"/>
     </row>
     <row r="246">
-      <c r="A246" s="5" t="s">
-        <v>261</v>
+      <c r="A246" s="14" t="s">
+        <v>260</v>
       </c>
       <c r="B246" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D246" s="6" t="s">
         <v>15</v>
@@ -6548,7 +6494,7 @@
     </row>
     <row r="247">
       <c r="A247" s="5" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B247" s="6" t="s">
         <v>7</v>
@@ -6569,7 +6515,7 @@
     </row>
     <row r="248">
       <c r="A248" s="5" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B248" s="6" t="s">
         <v>7</v>
@@ -6578,10 +6524,10 @@
         <v>7</v>
       </c>
       <c r="D248" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E248" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
@@ -6590,7 +6536,7 @@
     </row>
     <row r="249">
       <c r="A249" s="5" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B249" s="6" t="s">
         <v>7</v>
@@ -6599,10 +6545,10 @@
         <v>7</v>
       </c>
       <c r="D249" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E249" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
@@ -6611,10 +6557,10 @@
     </row>
     <row r="250">
       <c r="A250" s="5" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B250" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C250" s="6" t="s">
         <v>7</v>
@@ -6631,14 +6577,14 @@
       <c r="I250" s="2"/>
     </row>
     <row r="251">
-      <c r="A251" s="14" t="s">
-        <v>266</v>
+      <c r="A251" s="5" t="s">
+        <v>265</v>
       </c>
       <c r="B251" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D251" s="6" t="s">
         <v>15</v>
@@ -6653,7 +6599,7 @@
     </row>
     <row r="252">
       <c r="A252" s="5" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B252" s="6" t="s">
         <v>7</v>
@@ -6674,7 +6620,7 @@
     </row>
     <row r="253">
       <c r="A253" s="5" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>7</v>
@@ -6695,13 +6641,13 @@
     </row>
     <row r="254">
       <c r="A254" s="5" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B254" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C254" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D254" s="6" t="s">
         <v>15</v>
@@ -6716,13 +6662,13 @@
     </row>
     <row r="255">
       <c r="A255" s="5" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B255" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D255" s="6" t="s">
         <v>15</v>
@@ -6737,19 +6683,19 @@
     </row>
     <row r="256">
       <c r="A256" s="5" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B256" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E256" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
@@ -6758,13 +6704,13 @@
     </row>
     <row r="257">
       <c r="A257" s="5" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B257" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C257" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D257" s="6" t="s">
         <v>15</v>
@@ -6779,13 +6725,13 @@
     </row>
     <row r="258">
       <c r="A258" s="5" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B258" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D258" s="6" t="s">
         <v>15</v>
@@ -6800,19 +6746,19 @@
     </row>
     <row r="259">
       <c r="A259" s="5" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B259" s="6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C259" s="6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E259" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
@@ -6820,147 +6766,77 @@
       <c r="I259" s="2"/>
     </row>
     <row r="260">
-      <c r="A260" s="5" t="s">
-        <v>275</v>
-      </c>
-      <c r="B260" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C260" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D260" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E260" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A260" s="16"/>
+      <c r="B260" s="17"/>
+      <c r="C260" s="17"/>
+      <c r="D260" s="17"/>
+      <c r="E260" s="17"/>
       <c r="F260" s="2"/>
       <c r="G260" s="2"/>
       <c r="H260" s="2"/>
       <c r="I260" s="2"/>
     </row>
     <row r="261">
-      <c r="A261" s="5" t="s">
-        <v>276</v>
-      </c>
-      <c r="B261" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C261" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D261" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E261" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A261" s="16"/>
+      <c r="B261" s="17"/>
+      <c r="C261" s="17"/>
+      <c r="D261" s="17"/>
+      <c r="E261" s="17"/>
       <c r="F261" s="2"/>
       <c r="G261" s="2"/>
       <c r="H261" s="2"/>
       <c r="I261" s="2"/>
     </row>
     <row r="262">
-      <c r="A262" s="5" t="s">
-        <v>277</v>
-      </c>
-      <c r="B262" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C262" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D262" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E262" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A262" s="16"/>
+      <c r="B262" s="17"/>
+      <c r="C262" s="17"/>
+      <c r="D262" s="17"/>
+      <c r="E262" s="17"/>
       <c r="F262" s="2"/>
       <c r="G262" s="2"/>
       <c r="H262" s="2"/>
       <c r="I262" s="2"/>
     </row>
     <row r="263">
-      <c r="A263" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B263" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C263" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D263" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E263" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A263" s="16"/>
+      <c r="B263" s="17"/>
+      <c r="C263" s="17"/>
+      <c r="D263" s="17"/>
+      <c r="E263" s="17"/>
       <c r="F263" s="2"/>
       <c r="G263" s="2"/>
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
     </row>
     <row r="264">
-      <c r="A264" s="5" t="s">
-        <v>279</v>
-      </c>
-      <c r="B264" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C264" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D264" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E264" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A264" s="16"/>
+      <c r="B264" s="17"/>
+      <c r="C264" s="17"/>
+      <c r="D264" s="17"/>
+      <c r="E264" s="17"/>
       <c r="F264" s="2"/>
       <c r="G264" s="2"/>
       <c r="H264" s="2"/>
       <c r="I264" s="2"/>
     </row>
     <row r="265">
-      <c r="A265" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="B265" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C265" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D265" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E265" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A265" s="16"/>
+      <c r="B265" s="17"/>
+      <c r="C265" s="17"/>
+      <c r="D265" s="17"/>
+      <c r="E265" s="17"/>
       <c r="F265" s="2"/>
       <c r="G265" s="2"/>
       <c r="H265" s="2"/>
       <c r="I265" s="2"/>
     </row>
     <row r="266">
-      <c r="A266" s="5" t="s">
-        <v>281</v>
-      </c>
-      <c r="B266" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="C266" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D266" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="E266" s="6" t="s">
-        <v>41</v>
-      </c>
+      <c r="A266" s="16"/>
+      <c r="B266" s="17"/>
+      <c r="C266" s="17"/>
+      <c r="D266" s="17"/>
+      <c r="E266" s="17"/>
       <c r="F266" s="2"/>
       <c r="G266" s="2"/>
       <c r="H266" s="2"/>
@@ -14600,104 +14476,27 @@
       <c r="H960" s="2"/>
       <c r="I960" s="2"/>
     </row>
-    <row r="961">
-      <c r="A961" s="16"/>
-      <c r="B961" s="17"/>
-      <c r="C961" s="17"/>
-      <c r="D961" s="17"/>
-      <c r="E961" s="17"/>
-      <c r="F961" s="2"/>
-      <c r="G961" s="2"/>
-      <c r="H961" s="2"/>
-      <c r="I961" s="2"/>
-    </row>
-    <row r="962">
-      <c r="A962" s="16"/>
-      <c r="B962" s="17"/>
-      <c r="C962" s="17"/>
-      <c r="D962" s="17"/>
-      <c r="E962" s="17"/>
-      <c r="F962" s="2"/>
-      <c r="G962" s="2"/>
-      <c r="H962" s="2"/>
-      <c r="I962" s="2"/>
-    </row>
-    <row r="963">
-      <c r="A963" s="16"/>
-      <c r="B963" s="17"/>
-      <c r="C963" s="17"/>
-      <c r="D963" s="17"/>
-      <c r="E963" s="17"/>
-      <c r="F963" s="2"/>
-      <c r="G963" s="2"/>
-      <c r="H963" s="2"/>
-      <c r="I963" s="2"/>
-    </row>
-    <row r="964">
-      <c r="A964" s="16"/>
-      <c r="B964" s="17"/>
-      <c r="C964" s="17"/>
-      <c r="D964" s="17"/>
-      <c r="E964" s="17"/>
-      <c r="F964" s="2"/>
-      <c r="G964" s="2"/>
-      <c r="H964" s="2"/>
-      <c r="I964" s="2"/>
-    </row>
-    <row r="965">
-      <c r="A965" s="16"/>
-      <c r="B965" s="17"/>
-      <c r="C965" s="17"/>
-      <c r="D965" s="17"/>
-      <c r="E965" s="17"/>
-      <c r="F965" s="2"/>
-      <c r="G965" s="2"/>
-      <c r="H965" s="2"/>
-      <c r="I965" s="2"/>
-    </row>
-    <row r="966">
-      <c r="A966" s="16"/>
-      <c r="B966" s="17"/>
-      <c r="C966" s="17"/>
-      <c r="D966" s="17"/>
-      <c r="E966" s="17"/>
-      <c r="F966" s="2"/>
-      <c r="G966" s="2"/>
-      <c r="H966" s="2"/>
-      <c r="I966" s="2"/>
-    </row>
-    <row r="967">
-      <c r="A967" s="16"/>
-      <c r="B967" s="17"/>
-      <c r="C967" s="17"/>
-      <c r="D967" s="17"/>
-      <c r="E967" s="17"/>
-      <c r="F967" s="2"/>
-      <c r="G967" s="2"/>
-      <c r="H967" s="2"/>
-      <c r="I967" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$967">
-    <sortState ref="A1:E967">
-      <sortCondition ref="A1:A967"/>
-      <sortCondition ref="D1:D967"/>
+  <autoFilter ref="$A$1:$E$960">
+    <sortState ref="A1:E960">
+      <sortCondition ref="A1:A960"/>
+      <sortCondition ref="D1:D960"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G13:I13"/>
+    <mergeCell ref="G11:I11"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C967">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C960">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D967">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D960">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E967">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E960">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14960,14 +14759,7 @@
     <hyperlink r:id="rId256" ref="A257"/>
     <hyperlink r:id="rId257" ref="A258"/>
     <hyperlink r:id="rId258" ref="A259"/>
-    <hyperlink r:id="rId259" ref="A260"/>
-    <hyperlink r:id="rId260" ref="A261"/>
-    <hyperlink r:id="rId261" ref="A262"/>
-    <hyperlink r:id="rId262" ref="A263"/>
-    <hyperlink r:id="rId263" ref="A264"/>
-    <hyperlink r:id="rId264" ref="A265"/>
-    <hyperlink r:id="rId265" ref="A266"/>
   </hyperlinks>
-  <drawing r:id="rId266"/>
+  <drawing r:id="rId259"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,7 +6,7 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$960</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$959</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
@@ -399,6 +399,9 @@
     <t>https://heatlabs.net/maps/project-phoenix</t>
   </si>
   <si>
+    <t>https://heatlabs.net/maps/railgun</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/maps/scarred-city</t>
   </si>
   <si>
@@ -763,9 +766,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/tanks/m60a3e2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/tanks/m60a3e2-bot</t>
   </si>
   <si>
     <t>https://heatlabs.net/tanks/m60e2</t>
@@ -1346,7 +1346,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1356,7 +1356,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
@@ -1450,7 +1450,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1460,7 +1460,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="8">
@@ -3704,10 +3704,10 @@
         <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>15</v>
@@ -3752,10 +3752,10 @@
         <v>7</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F116" s="2"/>
       <c r="G116" s="2"/>
@@ -3773,10 +3773,10 @@
         <v>7</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -3788,7 +3788,7 @@
         <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>7</v>
@@ -3809,7 +3809,7 @@
         <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
@@ -3917,7 +3917,7 @@
         <v>7</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D124" s="6" t="s">
         <v>15</v>
@@ -3938,7 +3938,7 @@
         <v>7</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>15</v>
@@ -4043,7 +4043,7 @@
         <v>7</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>15</v>
@@ -4085,7 +4085,7 @@
         <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>15</v>
@@ -4169,7 +4169,7 @@
         <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -4190,7 +4190,7 @@
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -4316,7 +4316,7 @@
         <v>7</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4337,7 +4337,7 @@
         <v>7</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>15</v>
@@ -4439,7 +4439,7 @@
         <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>7</v>
@@ -4460,7 +4460,7 @@
         <v>164</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>7</v>
@@ -4481,7 +4481,7 @@
         <v>165</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>7</v>
@@ -4502,10 +4502,10 @@
         <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>15</v>
@@ -4526,7 +4526,7 @@
         <v>7</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>15</v>
@@ -4547,7 +4547,7 @@
         <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>15</v>
@@ -4565,10 +4565,10 @@
         <v>169</v>
       </c>
       <c r="B155" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>15</v>
@@ -4586,7 +4586,7 @@
         <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>7</v>
@@ -4607,7 +4607,7 @@
         <v>171</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>7</v>
@@ -4631,7 +4631,7 @@
         <v>8</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>15</v>
@@ -4652,7 +4652,7 @@
         <v>8</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4670,7 +4670,7 @@
         <v>174</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>7</v>
@@ -4691,10 +4691,10 @@
         <v>175</v>
       </c>
       <c r="B161" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>15</v>
@@ -4712,10 +4712,10 @@
         <v>176</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D162" s="6" t="s">
         <v>15</v>
@@ -4859,10 +4859,10 @@
         <v>183</v>
       </c>
       <c r="B169" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C169" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D169" s="6" t="s">
         <v>15</v>
@@ -4943,7 +4943,7 @@
         <v>187</v>
       </c>
       <c r="B173" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C173" s="6" t="s">
         <v>8</v>
@@ -4988,7 +4988,7 @@
         <v>7</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D175" s="6" t="s">
         <v>15</v>
@@ -5006,7 +5006,7 @@
         <v>190</v>
       </c>
       <c r="B176" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C176" s="6" t="s">
         <v>7</v>
@@ -5072,7 +5072,7 @@
         <v>8</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D179" s="6" t="s">
         <v>15</v>
@@ -5090,7 +5090,7 @@
         <v>194</v>
       </c>
       <c r="B180" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C180" s="6" t="s">
         <v>8</v>
@@ -5114,7 +5114,7 @@
         <v>7</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D181" s="6" t="s">
         <v>15</v>
@@ -5132,7 +5132,7 @@
         <v>196</v>
       </c>
       <c r="B182" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C182" s="6" t="s">
         <v>7</v>
@@ -5174,16 +5174,16 @@
         <v>198</v>
       </c>
       <c r="B184" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D184" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E184" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
@@ -5195,16 +5195,16 @@
         <v>199</v>
       </c>
       <c r="B185" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C185" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D185" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E185" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
@@ -5261,7 +5261,7 @@
         <v>8</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D188" s="6" t="s">
         <v>15</v>
@@ -5282,7 +5282,7 @@
         <v>8</v>
       </c>
       <c r="C189" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D189" s="6" t="s">
         <v>15</v>
@@ -5321,7 +5321,7 @@
         <v>205</v>
       </c>
       <c r="B191" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C191" s="6" t="s">
         <v>7</v>
@@ -5342,16 +5342,16 @@
         <v>206</v>
       </c>
       <c r="B192" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C192" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D192" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E192" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
@@ -5363,7 +5363,7 @@
         <v>207</v>
       </c>
       <c r="B193" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C193" s="6" t="s">
         <v>7</v>
@@ -5390,10 +5390,10 @@
         <v>7</v>
       </c>
       <c r="D194" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E194" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
@@ -5405,7 +5405,7 @@
         <v>209</v>
       </c>
       <c r="B195" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C195" s="6" t="s">
         <v>7</v>
@@ -5422,7 +5422,7 @@
       <c r="I195" s="2"/>
     </row>
     <row r="196">
-      <c r="A196" s="14" t="s">
+      <c r="A196" s="5" t="s">
         <v>210</v>
       </c>
       <c r="B196" s="6" t="s">
@@ -5443,11 +5443,11 @@
       <c r="I196" s="2"/>
     </row>
     <row r="197">
-      <c r="A197" s="5" t="s">
+      <c r="A197" s="14" t="s">
         <v>211</v>
       </c>
       <c r="B197" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>7</v>
@@ -5485,14 +5485,14 @@
       <c r="I198" s="2"/>
     </row>
     <row r="199">
-      <c r="A199" s="14" t="s">
+      <c r="A199" s="5" t="s">
         <v>213</v>
       </c>
       <c r="B199" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D199" s="6" t="s">
         <v>15</v>
@@ -5506,14 +5506,14 @@
       <c r="I199" s="2"/>
     </row>
     <row r="200">
-      <c r="A200" s="5" t="s">
+      <c r="A200" s="14" t="s">
         <v>214</v>
       </c>
       <c r="B200" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C200" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D200" s="6" t="s">
         <v>15</v>
@@ -5569,14 +5569,14 @@
       <c r="I202" s="2"/>
     </row>
     <row r="203">
-      <c r="A203" s="14" t="s">
+      <c r="A203" s="5" t="s">
         <v>217</v>
       </c>
       <c r="B203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C203" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D203" s="6" t="s">
         <v>15</v>
@@ -5590,14 +5590,14 @@
       <c r="I203" s="2"/>
     </row>
     <row r="204">
-      <c r="A204" s="5" t="s">
+      <c r="A204" s="14" t="s">
         <v>218</v>
       </c>
       <c r="B204" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C204" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D204" s="6" t="s">
         <v>15</v>
@@ -5611,14 +5611,14 @@
       <c r="I204" s="2"/>
     </row>
     <row r="205">
-      <c r="A205" s="14" t="s">
+      <c r="A205" s="5" t="s">
         <v>219</v>
       </c>
       <c r="B205" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D205" s="6" t="s">
         <v>15</v>
@@ -5632,14 +5632,14 @@
       <c r="I205" s="2"/>
     </row>
     <row r="206">
-      <c r="A206" s="5" t="s">
+      <c r="A206" s="14" t="s">
         <v>220</v>
       </c>
       <c r="B206" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C206" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D206" s="6" t="s">
         <v>15</v>
@@ -5657,16 +5657,16 @@
         <v>221</v>
       </c>
       <c r="B207" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C207" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
@@ -5678,16 +5678,16 @@
         <v>222</v>
       </c>
       <c r="B208" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C208" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D208" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E208" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
@@ -5699,7 +5699,7 @@
         <v>223</v>
       </c>
       <c r="B209" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C209" s="6" t="s">
         <v>7</v>
@@ -5741,16 +5741,16 @@
         <v>225</v>
       </c>
       <c r="B211" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C211" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
@@ -5762,7 +5762,7 @@
         <v>226</v>
       </c>
       <c r="B212" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C212" s="6" t="s">
         <v>7</v>
@@ -5779,20 +5779,20 @@
       <c r="I212" s="2"/>
     </row>
     <row r="213">
-      <c r="A213" s="14" t="s">
+      <c r="A213" s="5" t="s">
         <v>227</v>
       </c>
       <c r="B213" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
@@ -5800,14 +5800,14 @@
       <c r="I213" s="2"/>
     </row>
     <row r="214">
-      <c r="A214" s="5" t="s">
+      <c r="A214" s="14" t="s">
         <v>228</v>
       </c>
       <c r="B214" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D214" s="6" t="s">
         <v>15</v>
@@ -5842,20 +5842,20 @@
       <c r="I215" s="2"/>
     </row>
     <row r="216">
-      <c r="A216" s="14" t="s">
+      <c r="A216" s="5" t="s">
         <v>230</v>
       </c>
       <c r="B216" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D216" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E216" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
@@ -5873,10 +5873,10 @@
         <v>7</v>
       </c>
       <c r="D217" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E217" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
@@ -5884,20 +5884,20 @@
       <c r="I217" s="2"/>
     </row>
     <row r="218">
-      <c r="A218" s="5" t="s">
+      <c r="A218" s="14" t="s">
         <v>232</v>
       </c>
       <c r="B218" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C218" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D218" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E218" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
@@ -5905,20 +5905,20 @@
       <c r="I218" s="2"/>
     </row>
     <row r="219">
-      <c r="A219" s="14" t="s">
+      <c r="A219" s="5" t="s">
         <v>233</v>
       </c>
       <c r="B219" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C219" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D219" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E219" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
@@ -5926,20 +5926,20 @@
       <c r="I219" s="2"/>
     </row>
     <row r="220">
-      <c r="A220" s="5" t="s">
+      <c r="A220" s="14" t="s">
         <v>234</v>
       </c>
       <c r="B220" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D220" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E220" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
@@ -5957,10 +5957,10 @@
         <v>7</v>
       </c>
       <c r="D221" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E221" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
@@ -5978,10 +5978,10 @@
         <v>7</v>
       </c>
       <c r="D222" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E222" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
@@ -5999,10 +5999,10 @@
         <v>7</v>
       </c>
       <c r="D223" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E223" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
@@ -6140,10 +6140,10 @@
         <v>244</v>
       </c>
       <c r="B230" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D230" s="6" t="s">
         <v>15</v>
@@ -6161,10 +6161,10 @@
         <v>245</v>
       </c>
       <c r="B231" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D231" s="6" t="s">
         <v>15</v>
@@ -6178,14 +6178,14 @@
       <c r="I231" s="2"/>
     </row>
     <row r="232">
-      <c r="A232" s="14" t="s">
+      <c r="A232" s="5" t="s">
         <v>246</v>
       </c>
       <c r="B232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D232" s="6" t="s">
         <v>15</v>
@@ -6199,14 +6199,14 @@
       <c r="I232" s="2"/>
     </row>
     <row r="233">
-      <c r="A233" s="5" t="s">
+      <c r="A233" s="14" t="s">
         <v>247</v>
       </c>
       <c r="B233" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C233" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D233" s="6" t="s">
         <v>15</v>
@@ -14465,22 +14465,11 @@
       <c r="H959" s="2"/>
       <c r="I959" s="2"/>
     </row>
-    <row r="960">
-      <c r="A960" s="16"/>
-      <c r="B960" s="17"/>
-      <c r="C960" s="17"/>
-      <c r="D960" s="17"/>
-      <c r="E960" s="17"/>
-      <c r="F960" s="2"/>
-      <c r="G960" s="2"/>
-      <c r="H960" s="2"/>
-      <c r="I960" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$960">
-    <sortState ref="A1:E960">
-      <sortCondition ref="A1:A960"/>
-      <sortCondition ref="D1:D960"/>
+  <autoFilter ref="$A$1:$E$959">
+    <sortState ref="A1:E959">
+      <sortCondition ref="A1:A959"/>
+      <sortCondition ref="D1:D959"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -14490,13 +14479,13 @@
     <mergeCell ref="G11:I11"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C959">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D959">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E960">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E959">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>

--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$959</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$866</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1308" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="181">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -123,39 +123,6 @@
     <t>NOT NEEDED</t>
   </si>
   <si>
-    <t>https://heatlabs.net/announcements/alpha-1-announcement-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/alpha-1-announcement-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/alpha-2-facts-figures</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/alpha-2-has-ended</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/alpha-2-livestream</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/alpha-2-tournament</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/game-name-released</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/jamess-introduction</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/last-day-of-alpha-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/voreksis-introduction</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/announcements/winter-wargames-tournament-1</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/asset-gallery</t>
   </si>
   <si>
@@ -411,231 +378,6 @@
     <t>https://heatlabs.net/news</t>
   </si>
   <si>
-    <t>https://heatlabs.net/news/agent-spotlight-akira</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/agent-spotlight-fantome</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/agent-spotlight-kent</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-1-day-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-2-days-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-3-days-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-facts-figures</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-10-tournament-preparation-improvements</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-11-post-tournament-qol-improvements</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-3-quick-match-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-4-quality-of-life</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-5-fantome-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-6-ray-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-7-raketa-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-8-akira-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-8-delayed</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-patch-9-hstvl-updates</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-1-valentines-day</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-1-day-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-2-days-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-3-days-to-go</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-1-first-patch</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-2-client-server-update</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-3-hounds-become-the-hunted</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-4-balance-improvements</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-5-small-improvements</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-6-important-changes</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-7-bradley-is-here</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-8-balancing-changes</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-patch-9-balancing-tweaks</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/alpha-2-valentines-day</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/balanced-and-reworked-maps</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/beirut-concept-art</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/blossom-crash-concept-art-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/blossom-crash-concept-art-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/community-managers-reintroduction</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/concept-art-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/concept-art-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/content-creator-impressions</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/desktop-mobile-backgrounds</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/dev-questions-answers-design</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/dev-questions-answers-narrative</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/friendship-dam-concept-art-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/friendship-dam-sneak-peek-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/friendship-dam-sneak-peek-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/gun-dispersion-changes</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/happy-tanksgiving</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/hitbox-monday-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/hitbox-monday-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/hitbox-monday-3</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/hitbox-monday-4</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/hitbox-monday-5</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/jager-wall-bug</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/map-monday-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/map-monday-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/map-monday-3</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/map-monday-4</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/map-monday-5</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/medals-explained</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/new-agents-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/new-agents-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/new-agents-3</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/nord-oko-concept-art-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/nord-oko-concept-art-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/nord-oko-concept-art-3</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/plant-defuse-mode</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/progression-and-social-changes</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/project-cw-debrief-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/project-cw-debrief-2</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/project-cw-debrief-3</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/project-cw-gamescom-2025</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/quest-progress</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/update-recap</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/who-are-they-1</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/news/who-are-they-2</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/players</t>
   </si>
   <si>
@@ -697,27 +439,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/resources/support-us</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/announcing-the-heat-creators-contest</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/announcing-world-of-tanks-heat</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/fair-play-and-clear-value</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/heat-wrapped-2025-in-review</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/human-machine-synergy</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/join-the-lodestar-program</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/steam-news/the-source-of-heat</t>
   </si>
   <si>
     <t>https://heatlabs.net/tanks</t>
@@ -1346,7 +1067,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>104</v>
+        <v>75</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1356,7 +1077,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>152</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
@@ -1450,7 +1171,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1460,7 +1181,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>191</v>
+        <v>118</v>
       </c>
     </row>
     <row r="8">
@@ -1751,16 +1472,16 @@
         <v>36</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1778,10 +1499,10 @@
         <v>7</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
@@ -1793,10 +1514,10 @@
         <v>38</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>15</v>
@@ -1814,10 +1535,10 @@
         <v>39</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>15</v>
@@ -1835,7 +1556,7 @@
         <v>40</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C25" s="6" t="s">
         <v>8</v>
@@ -1856,10 +1577,10 @@
         <v>41</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>15</v>
@@ -1877,7 +1598,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
         <v>7</v>
@@ -1894,7 +1615,7 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="14" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="6" t="s">
@@ -1940,10 +1661,10 @@
         <v>45</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>15</v>
@@ -1961,7 +1682,7 @@
         <v>46</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>7</v>
@@ -1982,16 +1703,16 @@
         <v>47</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F32" s="2"/>
       <c r="G32" s="2"/>
@@ -2003,7 +1724,7 @@
         <v>48</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>7</v>
@@ -2111,7 +1832,7 @@
         <v>8</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>15</v>
@@ -2125,14 +1846,14 @@
       <c r="I38" s="2"/>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="s">
+      <c r="A39" s="5" t="s">
         <v>54</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>15</v>
@@ -2150,7 +1871,7 @@
         <v>55</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
         <v>7</v>
@@ -2195,7 +1916,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>15</v>
@@ -2240,10 +1961,10 @@
         <v>7</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F44" s="2"/>
       <c r="G44" s="2"/>
@@ -2258,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>15</v>
@@ -2272,20 +1993,20 @@
       <c r="I45" s="2"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="14" t="s">
         <v>61</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2300,13 +2021,13 @@
         <v>8</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -2335,14 +2056,14 @@
       <c r="I48" s="2"/>
     </row>
     <row r="49">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="14" t="s">
         <v>64</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
@@ -2384,7 +2105,7 @@
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>15</v>
@@ -2402,10 +2123,10 @@
         <v>67</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>15</v>
@@ -2426,13 +2147,13 @@
         <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -2444,7 +2165,7 @@
         <v>69</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>7</v>
@@ -2503,20 +2224,20 @@
       <c r="I56" s="2"/>
     </row>
     <row r="57">
-      <c r="A57" s="14" t="s">
+      <c r="A57" s="5" t="s">
         <v>72</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F57" s="2"/>
       <c r="G57" s="2"/>
@@ -2531,13 +2252,13 @@
         <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F58" s="2"/>
       <c r="G58" s="2"/>
@@ -2549,10 +2270,10 @@
         <v>74</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>15</v>
@@ -2566,14 +2287,14 @@
       <c r="I59" s="2"/>
     </row>
     <row r="60">
-      <c r="A60" s="14" t="s">
+      <c r="A60" s="5" t="s">
         <v>75</v>
       </c>
       <c r="B60" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>15</v>
@@ -2594,7 +2315,7 @@
         <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>15</v>
@@ -2633,7 +2354,7 @@
         <v>78</v>
       </c>
       <c r="B63" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
         <v>7</v>
@@ -2654,16 +2375,16 @@
         <v>79</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F64" s="2"/>
       <c r="G64" s="2"/>
@@ -2675,7 +2396,7 @@
         <v>80</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>7</v>
@@ -2741,7 +2462,7 @@
         <v>8</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D68" s="6" t="s">
         <v>15</v>
@@ -2776,11 +2497,11 @@
       <c r="I69" s="2"/>
     </row>
     <row r="70">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="14" t="s">
         <v>85</v>
       </c>
       <c r="B70" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
         <v>7</v>
@@ -2801,16 +2522,16 @@
         <v>86</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -2822,16 +2543,16 @@
         <v>87</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -2843,16 +2564,16 @@
         <v>88</v>
       </c>
       <c r="B73" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F73" s="2"/>
       <c r="G73" s="2"/>
@@ -2864,7 +2585,7 @@
         <v>89</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>7</v>
@@ -2881,14 +2602,14 @@
       <c r="I74" s="2"/>
     </row>
     <row r="75">
-      <c r="A75" s="5" t="s">
+      <c r="A75" s="14" t="s">
         <v>90</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>15</v>
@@ -2902,14 +2623,14 @@
       <c r="I75" s="2"/>
     </row>
     <row r="76">
-      <c r="A76" s="5" t="s">
-        <v>91</v>
+      <c r="A76" s="14" t="s">
+        <v>90</v>
       </c>
       <c r="B76" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -2924,10 +2645,10 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B77" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C77" s="6" t="s">
         <v>7</v>
@@ -2945,10 +2666,10 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C78" s="6" t="s">
         <v>7</v>
@@ -2965,14 +2686,14 @@
       <c r="I78" s="2"/>
     </row>
     <row r="79">
-      <c r="A79" s="5" t="s">
-        <v>94</v>
+      <c r="A79" s="14" t="s">
+        <v>93</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>15</v>
@@ -2987,13 +2708,13 @@
     </row>
     <row r="80">
       <c r="A80" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D80" s="6" t="s">
         <v>15</v>
@@ -3007,11 +2728,11 @@
       <c r="I80" s="2"/>
     </row>
     <row r="81">
-      <c r="A81" s="14" t="s">
-        <v>96</v>
+      <c r="A81" s="5" t="s">
+        <v>95</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>7</v>
@@ -3029,7 +2750,7 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B82" s="6" t="s">
         <v>7</v>
@@ -3050,7 +2771,7 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>7</v>
@@ -3059,10 +2780,10 @@
         <v>7</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -3070,20 +2791,20 @@
       <c r="I83" s="2"/>
     </row>
     <row r="84">
-      <c r="A84" s="5" t="s">
-        <v>99</v>
+      <c r="A84" s="14" t="s">
+        <v>98</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -3092,7 +2813,7 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B85" s="6" t="s">
         <v>7</v>
@@ -3101,10 +2822,10 @@
         <v>7</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -3112,8 +2833,8 @@
       <c r="I85" s="2"/>
     </row>
     <row r="86">
-      <c r="A86" s="14" t="s">
-        <v>101</v>
+      <c r="A86" s="5" t="s">
+        <v>100</v>
       </c>
       <c r="B86" s="6" t="s">
         <v>8</v>
@@ -3133,20 +2854,20 @@
       <c r="I86" s="2"/>
     </row>
     <row r="87">
-      <c r="A87" s="14" t="s">
+      <c r="A87" s="5" t="s">
         <v>101</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -3161,7 +2882,7 @@
         <v>7</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>15</v>
@@ -3179,16 +2900,16 @@
         <v>103</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -3196,20 +2917,20 @@
       <c r="I89" s="2"/>
     </row>
     <row r="90">
-      <c r="A90" s="14" t="s">
+      <c r="A90" s="5" t="s">
         <v>104</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -3221,7 +2942,7 @@
         <v>105</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>7</v>
@@ -3242,7 +2963,7 @@
         <v>106</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>7</v>
@@ -3266,13 +2987,13 @@
         <v>7</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F93" s="2"/>
       <c r="G93" s="2"/>
@@ -3301,11 +3022,11 @@
       <c r="I94" s="2"/>
     </row>
     <row r="95">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="5" t="s">
         <v>109</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>7</v>
@@ -3326,16 +3047,16 @@
         <v>110</v>
       </c>
       <c r="B96" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
@@ -3347,10 +3068,10 @@
         <v>111</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D97" s="6" t="s">
         <v>15</v>
@@ -3374,10 +3095,10 @@
         <v>7</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F98" s="2"/>
       <c r="G98" s="2"/>
@@ -3389,10 +3110,10 @@
         <v>113</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3416,10 +3137,10 @@
         <v>7</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F100" s="2"/>
       <c r="G100" s="2"/>
@@ -3431,16 +3152,16 @@
         <v>115</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -3476,7 +3197,7 @@
         <v>8</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D103" s="6" t="s">
         <v>15</v>
@@ -3497,7 +3218,7 @@
         <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
         <v>15</v>
@@ -3542,10 +3263,10 @@
         <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -3560,13 +3281,13 @@
         <v>8</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -3584,10 +3305,10 @@
         <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -3637,7 +3358,7 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="14" t="s">
         <v>125</v>
       </c>
       <c r="B111" s="6" t="s">
@@ -3662,7 +3383,7 @@
         <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>7</v>
@@ -3683,7 +3404,7 @@
         <v>127</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>7</v>
@@ -3700,7 +3421,7 @@
       <c r="I113" s="2"/>
     </row>
     <row r="114">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="14" t="s">
         <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
@@ -3773,10 +3494,10 @@
         <v>7</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -3784,14 +3505,14 @@
       <c r="I117" s="2"/>
     </row>
     <row r="118">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="14" t="s">
         <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D118" s="6" t="s">
         <v>15</v>
@@ -3809,7 +3530,7 @@
         <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
@@ -3826,14 +3547,14 @@
       <c r="I119" s="2"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="14" t="s">
         <v>134</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>15</v>
@@ -3851,7 +3572,7 @@
         <v>135</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>7</v>
@@ -3878,10 +3599,10 @@
         <v>7</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3893,7 +3614,7 @@
         <v>137</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
@@ -3938,7 +3659,7 @@
         <v>7</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D125" s="6" t="s">
         <v>15</v>
@@ -3956,16 +3677,16 @@
         <v>140</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -3983,10 +3704,10 @@
         <v>7</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -4004,10 +3725,10 @@
         <v>7</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -4015,7 +3736,7 @@
       <c r="I128" s="2"/>
     </row>
     <row r="129">
-      <c r="A129" s="5" t="s">
+      <c r="A129" s="15" t="s">
         <v>143</v>
       </c>
       <c r="B129" s="6" t="s">
@@ -4046,10 +3767,10 @@
         <v>7</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -4064,7 +3785,7 @@
         <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>15</v>
@@ -4085,7 +3806,7 @@
         <v>7</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>15</v>
@@ -4190,7 +3911,7 @@
         <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -4208,10 +3929,10 @@
         <v>152</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>15</v>
@@ -4246,14 +3967,14 @@
       <c r="I139" s="2"/>
     </row>
     <row r="140">
-      <c r="A140" s="5" t="s">
+      <c r="A140" s="14" t="s">
         <v>154</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -4337,7 +4058,7 @@
         <v>7</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>15</v>
@@ -4460,16 +4181,16 @@
         <v>164</v>
       </c>
       <c r="B150" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C150" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
@@ -4502,7 +4223,7 @@
         <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>7</v>
@@ -4519,11 +4240,11 @@
       <c r="I152" s="2"/>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="14" t="s">
         <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>8</v>
@@ -4568,7 +4289,7 @@
         <v>7</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>15</v>
@@ -4586,16 +4307,16 @@
         <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -4607,7 +4328,7 @@
         <v>171</v>
       </c>
       <c r="B157" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C157" s="6" t="s">
         <v>7</v>
@@ -4628,7 +4349,7 @@
         <v>172</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>7</v>
@@ -4649,10 +4370,10 @@
         <v>173</v>
       </c>
       <c r="B159" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4670,7 +4391,7 @@
         <v>174</v>
       </c>
       <c r="B160" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C160" s="6" t="s">
         <v>7</v>
@@ -4694,7 +4415,7 @@
         <v>7</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D161" s="6" t="s">
         <v>15</v>
@@ -4736,7 +4457,7 @@
         <v>7</v>
       </c>
       <c r="C163" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D163" s="6" t="s">
         <v>15</v>
@@ -4757,7 +4478,7 @@
         <v>7</v>
       </c>
       <c r="C164" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D164" s="6" t="s">
         <v>15</v>
@@ -4778,7 +4499,7 @@
         <v>7</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>15</v>
@@ -4796,16 +4517,16 @@
         <v>180</v>
       </c>
       <c r="B166" s="6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="C166" s="6" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D166" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E166" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
@@ -4813,1953 +4534,1023 @@
       <c r="I166" s="2"/>
     </row>
     <row r="167">
-      <c r="A167" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="B167" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C167" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D167" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E167" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A167" s="16"/>
+      <c r="B167" s="17"/>
+      <c r="C167" s="17"/>
+      <c r="D167" s="17"/>
+      <c r="E167" s="17"/>
       <c r="F167" s="2"/>
       <c r="G167" s="2"/>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
     </row>
     <row r="168">
-      <c r="A168" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="B168" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C168" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D168" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E168" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A168" s="16"/>
+      <c r="B168" s="17"/>
+      <c r="C168" s="17"/>
+      <c r="D168" s="17"/>
+      <c r="E168" s="17"/>
       <c r="F168" s="2"/>
       <c r="G168" s="2"/>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
     </row>
     <row r="169">
-      <c r="A169" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="B169" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C169" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D169" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E169" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A169" s="16"/>
+      <c r="B169" s="17"/>
+      <c r="C169" s="17"/>
+      <c r="D169" s="17"/>
+      <c r="E169" s="17"/>
       <c r="F169" s="2"/>
       <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
     </row>
     <row r="170">
-      <c r="A170" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="B170" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C170" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D170" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E170" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A170" s="16"/>
+      <c r="B170" s="17"/>
+      <c r="C170" s="17"/>
+      <c r="D170" s="17"/>
+      <c r="E170" s="17"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
     </row>
     <row r="171">
-      <c r="A171" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="B171" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C171" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D171" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E171" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A171" s="16"/>
+      <c r="B171" s="17"/>
+      <c r="C171" s="17"/>
+      <c r="D171" s="17"/>
+      <c r="E171" s="17"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
     </row>
     <row r="172">
-      <c r="A172" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="B172" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C172" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D172" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E172" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A172" s="16"/>
+      <c r="B172" s="17"/>
+      <c r="C172" s="17"/>
+      <c r="D172" s="17"/>
+      <c r="E172" s="17"/>
       <c r="F172" s="2"/>
       <c r="G172" s="2"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
     </row>
     <row r="173">
-      <c r="A173" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="B173" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C173" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D173" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E173" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A173" s="16"/>
+      <c r="B173" s="17"/>
+      <c r="C173" s="17"/>
+      <c r="D173" s="17"/>
+      <c r="E173" s="17"/>
       <c r="F173" s="2"/>
       <c r="G173" s="2"/>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
     </row>
     <row r="174">
-      <c r="A174" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B174" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C174" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D174" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E174" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A174" s="16"/>
+      <c r="B174" s="17"/>
+      <c r="C174" s="17"/>
+      <c r="D174" s="17"/>
+      <c r="E174" s="17"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
     </row>
     <row r="175">
-      <c r="A175" s="5" t="s">
-        <v>189</v>
-      </c>
-      <c r="B175" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C175" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D175" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E175" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A175" s="16"/>
+      <c r="B175" s="17"/>
+      <c r="C175" s="17"/>
+      <c r="D175" s="17"/>
+      <c r="E175" s="17"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
     </row>
     <row r="176">
-      <c r="A176" s="5" t="s">
-        <v>190</v>
-      </c>
-      <c r="B176" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C176" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D176" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E176" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A176" s="16"/>
+      <c r="B176" s="17"/>
+      <c r="C176" s="17"/>
+      <c r="D176" s="17"/>
+      <c r="E176" s="17"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
     </row>
     <row r="177">
-      <c r="A177" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="B177" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C177" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D177" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E177" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A177" s="16"/>
+      <c r="B177" s="17"/>
+      <c r="C177" s="17"/>
+      <c r="D177" s="17"/>
+      <c r="E177" s="17"/>
       <c r="F177" s="2"/>
       <c r="G177" s="2"/>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
     </row>
     <row r="178">
-      <c r="A178" s="5" t="s">
-        <v>192</v>
-      </c>
-      <c r="B178" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C178" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D178" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E178" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A178" s="16"/>
+      <c r="B178" s="17"/>
+      <c r="C178" s="17"/>
+      <c r="D178" s="17"/>
+      <c r="E178" s="17"/>
       <c r="F178" s="2"/>
       <c r="G178" s="2"/>
       <c r="H178" s="2"/>
       <c r="I178" s="2"/>
     </row>
     <row r="179">
-      <c r="A179" s="5" t="s">
-        <v>193</v>
-      </c>
-      <c r="B179" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C179" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D179" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E179" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A179" s="16"/>
+      <c r="B179" s="17"/>
+      <c r="C179" s="17"/>
+      <c r="D179" s="17"/>
+      <c r="E179" s="17"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
     </row>
     <row r="180">
-      <c r="A180" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="B180" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C180" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D180" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E180" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A180" s="16"/>
+      <c r="B180" s="17"/>
+      <c r="C180" s="17"/>
+      <c r="D180" s="17"/>
+      <c r="E180" s="17"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
     </row>
     <row r="181">
-      <c r="A181" s="5" t="s">
-        <v>195</v>
-      </c>
-      <c r="B181" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C181" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D181" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E181" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A181" s="16"/>
+      <c r="B181" s="17"/>
+      <c r="C181" s="17"/>
+      <c r="D181" s="17"/>
+      <c r="E181" s="17"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
     </row>
     <row r="182">
-      <c r="A182" s="5" t="s">
-        <v>196</v>
-      </c>
-      <c r="B182" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C182" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D182" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E182" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A182" s="16"/>
+      <c r="B182" s="17"/>
+      <c r="C182" s="17"/>
+      <c r="D182" s="17"/>
+      <c r="E182" s="17"/>
       <c r="F182" s="2"/>
       <c r="G182" s="2"/>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
     </row>
     <row r="183">
-      <c r="A183" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="B183" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C183" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D183" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E183" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A183" s="16"/>
+      <c r="B183" s="17"/>
+      <c r="C183" s="17"/>
+      <c r="D183" s="17"/>
+      <c r="E183" s="17"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
     </row>
     <row r="184">
-      <c r="A184" s="5" t="s">
-        <v>198</v>
-      </c>
-      <c r="B184" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C184" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D184" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E184" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A184" s="16"/>
+      <c r="B184" s="17"/>
+      <c r="C184" s="17"/>
+      <c r="D184" s="17"/>
+      <c r="E184" s="17"/>
       <c r="F184" s="2"/>
       <c r="G184" s="2"/>
       <c r="H184" s="2"/>
       <c r="I184" s="2"/>
     </row>
     <row r="185">
-      <c r="A185" s="5" t="s">
-        <v>199</v>
-      </c>
-      <c r="B185" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D185" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E185" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A185" s="16"/>
+      <c r="B185" s="17"/>
+      <c r="C185" s="17"/>
+      <c r="D185" s="17"/>
+      <c r="E185" s="17"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
       <c r="H185" s="2"/>
       <c r="I185" s="2"/>
     </row>
     <row r="186">
-      <c r="A186" s="5" t="s">
-        <v>200</v>
-      </c>
-      <c r="B186" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C186" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D186" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E186" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A186" s="16"/>
+      <c r="B186" s="17"/>
+      <c r="C186" s="17"/>
+      <c r="D186" s="17"/>
+      <c r="E186" s="17"/>
       <c r="F186" s="2"/>
       <c r="G186" s="2"/>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
     </row>
     <row r="187">
-      <c r="A187" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="B187" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C187" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D187" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E187" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A187" s="16"/>
+      <c r="B187" s="17"/>
+      <c r="C187" s="17"/>
+      <c r="D187" s="17"/>
+      <c r="E187" s="17"/>
       <c r="F187" s="2"/>
       <c r="G187" s="2"/>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
     </row>
     <row r="188">
-      <c r="A188" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="B188" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C188" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D188" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E188" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A188" s="16"/>
+      <c r="B188" s="17"/>
+      <c r="C188" s="17"/>
+      <c r="D188" s="17"/>
+      <c r="E188" s="17"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
     </row>
     <row r="189">
-      <c r="A189" s="5" t="s">
-        <v>203</v>
-      </c>
-      <c r="B189" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C189" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D189" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E189" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A189" s="16"/>
+      <c r="B189" s="17"/>
+      <c r="C189" s="17"/>
+      <c r="D189" s="17"/>
+      <c r="E189" s="17"/>
       <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
     </row>
     <row r="190">
-      <c r="A190" s="5" t="s">
-        <v>204</v>
-      </c>
-      <c r="B190" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C190" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D190" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E190" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A190" s="16"/>
+      <c r="B190" s="17"/>
+      <c r="C190" s="17"/>
+      <c r="D190" s="17"/>
+      <c r="E190" s="17"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
     </row>
     <row r="191">
-      <c r="A191" s="5" t="s">
-        <v>205</v>
-      </c>
-      <c r="B191" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C191" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D191" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E191" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A191" s="16"/>
+      <c r="B191" s="17"/>
+      <c r="C191" s="17"/>
+      <c r="D191" s="17"/>
+      <c r="E191" s="17"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
     </row>
     <row r="192">
-      <c r="A192" s="5" t="s">
-        <v>206</v>
-      </c>
-      <c r="B192" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C192" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D192" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E192" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A192" s="16"/>
+      <c r="B192" s="17"/>
+      <c r="C192" s="17"/>
+      <c r="D192" s="17"/>
+      <c r="E192" s="17"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
     </row>
     <row r="193">
-      <c r="A193" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="B193" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C193" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D193" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E193" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A193" s="16"/>
+      <c r="B193" s="17"/>
+      <c r="C193" s="17"/>
+      <c r="D193" s="17"/>
+      <c r="E193" s="17"/>
       <c r="F193" s="2"/>
       <c r="G193" s="2"/>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
     </row>
     <row r="194">
-      <c r="A194" s="5" t="s">
-        <v>208</v>
-      </c>
-      <c r="B194" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C194" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D194" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E194" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A194" s="16"/>
+      <c r="B194" s="17"/>
+      <c r="C194" s="17"/>
+      <c r="D194" s="17"/>
+      <c r="E194" s="17"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
     </row>
     <row r="195">
-      <c r="A195" s="5" t="s">
-        <v>209</v>
-      </c>
-      <c r="B195" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C195" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D195" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E195" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A195" s="16"/>
+      <c r="B195" s="17"/>
+      <c r="C195" s="17"/>
+      <c r="D195" s="17"/>
+      <c r="E195" s="17"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
     </row>
     <row r="196">
-      <c r="A196" s="5" t="s">
-        <v>210</v>
-      </c>
-      <c r="B196" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C196" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D196" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E196" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A196" s="16"/>
+      <c r="B196" s="17"/>
+      <c r="C196" s="17"/>
+      <c r="D196" s="17"/>
+      <c r="E196" s="17"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
     </row>
     <row r="197">
-      <c r="A197" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="B197" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C197" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D197" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E197" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A197" s="16"/>
+      <c r="B197" s="17"/>
+      <c r="C197" s="17"/>
+      <c r="D197" s="17"/>
+      <c r="E197" s="17"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
       <c r="H197" s="2"/>
       <c r="I197" s="2"/>
     </row>
     <row r="198">
-      <c r="A198" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="B198" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C198" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D198" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E198" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A198" s="16"/>
+      <c r="B198" s="17"/>
+      <c r="C198" s="17"/>
+      <c r="D198" s="17"/>
+      <c r="E198" s="17"/>
       <c r="F198" s="2"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
     </row>
     <row r="199">
-      <c r="A199" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="B199" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C199" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D199" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E199" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A199" s="16"/>
+      <c r="B199" s="17"/>
+      <c r="C199" s="17"/>
+      <c r="D199" s="17"/>
+      <c r="E199" s="17"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
       <c r="H199" s="2"/>
       <c r="I199" s="2"/>
     </row>
     <row r="200">
-      <c r="A200" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="B200" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C200" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D200" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E200" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A200" s="16"/>
+      <c r="B200" s="17"/>
+      <c r="C200" s="17"/>
+      <c r="D200" s="17"/>
+      <c r="E200" s="17"/>
       <c r="F200" s="2"/>
       <c r="G200" s="2"/>
       <c r="H200" s="2"/>
       <c r="I200" s="2"/>
     </row>
     <row r="201">
-      <c r="A201" s="5" t="s">
-        <v>215</v>
-      </c>
-      <c r="B201" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C201" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D201" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E201" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A201" s="16"/>
+      <c r="B201" s="17"/>
+      <c r="C201" s="17"/>
+      <c r="D201" s="17"/>
+      <c r="E201" s="17"/>
       <c r="F201" s="2"/>
       <c r="G201" s="2"/>
       <c r="H201" s="2"/>
       <c r="I201" s="2"/>
     </row>
     <row r="202">
-      <c r="A202" s="5" t="s">
-        <v>216</v>
-      </c>
-      <c r="B202" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C202" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D202" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E202" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A202" s="16"/>
+      <c r="B202" s="17"/>
+      <c r="C202" s="17"/>
+      <c r="D202" s="17"/>
+      <c r="E202" s="17"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
       <c r="H202" s="2"/>
       <c r="I202" s="2"/>
     </row>
     <row r="203">
-      <c r="A203" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B203" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C203" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D203" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E203" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A203" s="16"/>
+      <c r="B203" s="17"/>
+      <c r="C203" s="17"/>
+      <c r="D203" s="17"/>
+      <c r="E203" s="17"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
       <c r="H203" s="2"/>
       <c r="I203" s="2"/>
     </row>
     <row r="204">
-      <c r="A204" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="B204" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C204" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D204" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E204" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A204" s="16"/>
+      <c r="B204" s="17"/>
+      <c r="C204" s="17"/>
+      <c r="D204" s="17"/>
+      <c r="E204" s="17"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
       <c r="H204" s="2"/>
       <c r="I204" s="2"/>
     </row>
     <row r="205">
-      <c r="A205" s="5" t="s">
-        <v>219</v>
-      </c>
-      <c r="B205" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C205" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D205" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E205" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A205" s="16"/>
+      <c r="B205" s="17"/>
+      <c r="C205" s="17"/>
+      <c r="D205" s="17"/>
+      <c r="E205" s="17"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
       <c r="H205" s="2"/>
       <c r="I205" s="2"/>
     </row>
     <row r="206">
-      <c r="A206" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="B206" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C206" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D206" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E206" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A206" s="16"/>
+      <c r="B206" s="17"/>
+      <c r="C206" s="17"/>
+      <c r="D206" s="17"/>
+      <c r="E206" s="17"/>
       <c r="F206" s="2"/>
       <c r="G206" s="2"/>
       <c r="H206" s="2"/>
       <c r="I206" s="2"/>
     </row>
     <row r="207">
-      <c r="A207" s="5" t="s">
-        <v>221</v>
-      </c>
-      <c r="B207" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C207" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D207" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E207" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A207" s="16"/>
+      <c r="B207" s="17"/>
+      <c r="C207" s="17"/>
+      <c r="D207" s="17"/>
+      <c r="E207" s="17"/>
       <c r="F207" s="2"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
     </row>
     <row r="208">
-      <c r="A208" s="5" t="s">
-        <v>222</v>
-      </c>
-      <c r="B208" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C208" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D208" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E208" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A208" s="16"/>
+      <c r="B208" s="17"/>
+      <c r="C208" s="17"/>
+      <c r="D208" s="17"/>
+      <c r="E208" s="17"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
       <c r="H208" s="2"/>
       <c r="I208" s="2"/>
     </row>
     <row r="209">
-      <c r="A209" s="5" t="s">
-        <v>223</v>
-      </c>
-      <c r="B209" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C209" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D209" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E209" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A209" s="16"/>
+      <c r="B209" s="17"/>
+      <c r="C209" s="17"/>
+      <c r="D209" s="17"/>
+      <c r="E209" s="17"/>
       <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
     </row>
     <row r="210">
-      <c r="A210" s="5" t="s">
-        <v>224</v>
-      </c>
-      <c r="B210" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C210" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D210" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E210" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A210" s="16"/>
+      <c r="B210" s="17"/>
+      <c r="C210" s="17"/>
+      <c r="D210" s="17"/>
+      <c r="E210" s="17"/>
       <c r="F210" s="2"/>
       <c r="G210" s="2"/>
       <c r="H210" s="2"/>
       <c r="I210" s="2"/>
     </row>
     <row r="211">
-      <c r="A211" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="B211" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C211" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D211" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E211" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A211" s="16"/>
+      <c r="B211" s="17"/>
+      <c r="C211" s="17"/>
+      <c r="D211" s="17"/>
+      <c r="E211" s="17"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
       <c r="H211" s="2"/>
       <c r="I211" s="2"/>
     </row>
     <row r="212">
-      <c r="A212" s="5" t="s">
-        <v>226</v>
-      </c>
-      <c r="B212" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C212" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D212" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E212" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A212" s="16"/>
+      <c r="B212" s="17"/>
+      <c r="C212" s="17"/>
+      <c r="D212" s="17"/>
+      <c r="E212" s="17"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
       <c r="H212" s="2"/>
       <c r="I212" s="2"/>
     </row>
     <row r="213">
-      <c r="A213" s="5" t="s">
-        <v>227</v>
-      </c>
-      <c r="B213" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C213" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D213" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E213" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A213" s="16"/>
+      <c r="B213" s="17"/>
+      <c r="C213" s="17"/>
+      <c r="D213" s="17"/>
+      <c r="E213" s="17"/>
       <c r="F213" s="2"/>
       <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
     </row>
     <row r="214">
-      <c r="A214" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B214" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C214" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D214" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E214" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A214" s="16"/>
+      <c r="B214" s="17"/>
+      <c r="C214" s="17"/>
+      <c r="D214" s="17"/>
+      <c r="E214" s="17"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
       <c r="H214" s="2"/>
       <c r="I214" s="2"/>
     </row>
     <row r="215">
-      <c r="A215" s="5" t="s">
-        <v>229</v>
-      </c>
-      <c r="B215" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C215" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D215" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E215" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A215" s="16"/>
+      <c r="B215" s="17"/>
+      <c r="C215" s="17"/>
+      <c r="D215" s="17"/>
+      <c r="E215" s="17"/>
       <c r="F215" s="2"/>
       <c r="G215" s="2"/>
       <c r="H215" s="2"/>
       <c r="I215" s="2"/>
     </row>
     <row r="216">
-      <c r="A216" s="5" t="s">
-        <v>230</v>
-      </c>
-      <c r="B216" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C216" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D216" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E216" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A216" s="16"/>
+      <c r="B216" s="17"/>
+      <c r="C216" s="17"/>
+      <c r="D216" s="17"/>
+      <c r="E216" s="17"/>
       <c r="F216" s="2"/>
       <c r="G216" s="2"/>
       <c r="H216" s="2"/>
       <c r="I216" s="2"/>
     </row>
     <row r="217">
-      <c r="A217" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="B217" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C217" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D217" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E217" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A217" s="16"/>
+      <c r="B217" s="17"/>
+      <c r="C217" s="17"/>
+      <c r="D217" s="17"/>
+      <c r="E217" s="17"/>
       <c r="F217" s="2"/>
       <c r="G217" s="2"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
     </row>
     <row r="218">
-      <c r="A218" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B218" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C218" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D218" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E218" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A218" s="16"/>
+      <c r="B218" s="17"/>
+      <c r="C218" s="17"/>
+      <c r="D218" s="17"/>
+      <c r="E218" s="17"/>
       <c r="F218" s="2"/>
       <c r="G218" s="2"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
     </row>
     <row r="219">
-      <c r="A219" s="5" t="s">
-        <v>233</v>
-      </c>
-      <c r="B219" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C219" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D219" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E219" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A219" s="16"/>
+      <c r="B219" s="17"/>
+      <c r="C219" s="17"/>
+      <c r="D219" s="17"/>
+      <c r="E219" s="17"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
     </row>
     <row r="220">
-      <c r="A220" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="B220" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C220" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D220" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E220" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A220" s="16"/>
+      <c r="B220" s="17"/>
+      <c r="C220" s="17"/>
+      <c r="D220" s="17"/>
+      <c r="E220" s="17"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
     </row>
     <row r="221">
-      <c r="A221" s="5" t="s">
-        <v>235</v>
-      </c>
-      <c r="B221" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C221" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D221" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E221" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A221" s="16"/>
+      <c r="B221" s="17"/>
+      <c r="C221" s="17"/>
+      <c r="D221" s="17"/>
+      <c r="E221" s="17"/>
       <c r="F221" s="2"/>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
     </row>
     <row r="222">
-      <c r="A222" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="B222" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C222" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D222" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E222" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A222" s="16"/>
+      <c r="B222" s="17"/>
+      <c r="C222" s="17"/>
+      <c r="D222" s="17"/>
+      <c r="E222" s="17"/>
       <c r="F222" s="2"/>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
     </row>
     <row r="223">
-      <c r="A223" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="B223" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C223" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D223" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E223" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A223" s="16"/>
+      <c r="B223" s="17"/>
+      <c r="C223" s="17"/>
+      <c r="D223" s="17"/>
+      <c r="E223" s="17"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
       <c r="H223" s="2"/>
       <c r="I223" s="2"/>
     </row>
     <row r="224">
-      <c r="A224" s="5" t="s">
-        <v>238</v>
-      </c>
-      <c r="B224" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C224" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D224" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E224" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A224" s="16"/>
+      <c r="B224" s="17"/>
+      <c r="C224" s="17"/>
+      <c r="D224" s="17"/>
+      <c r="E224" s="17"/>
       <c r="F224" s="2"/>
       <c r="G224" s="2"/>
       <c r="H224" s="2"/>
       <c r="I224" s="2"/>
     </row>
     <row r="225">
-      <c r="A225" s="5" t="s">
-        <v>239</v>
-      </c>
-      <c r="B225" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C225" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D225" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E225" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A225" s="16"/>
+      <c r="B225" s="17"/>
+      <c r="C225" s="17"/>
+      <c r="D225" s="17"/>
+      <c r="E225" s="17"/>
       <c r="F225" s="2"/>
       <c r="G225" s="2"/>
       <c r="H225" s="2"/>
       <c r="I225" s="2"/>
     </row>
     <row r="226">
-      <c r="A226" s="5" t="s">
-        <v>240</v>
-      </c>
-      <c r="B226" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C226" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D226" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E226" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A226" s="16"/>
+      <c r="B226" s="17"/>
+      <c r="C226" s="17"/>
+      <c r="D226" s="17"/>
+      <c r="E226" s="17"/>
       <c r="F226" s="2"/>
       <c r="G226" s="2"/>
       <c r="H226" s="2"/>
       <c r="I226" s="2"/>
     </row>
     <row r="227">
-      <c r="A227" s="5" t="s">
-        <v>241</v>
-      </c>
-      <c r="B227" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C227" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D227" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E227" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A227" s="16"/>
+      <c r="B227" s="17"/>
+      <c r="C227" s="17"/>
+      <c r="D227" s="17"/>
+      <c r="E227" s="17"/>
       <c r="F227" s="2"/>
       <c r="G227" s="2"/>
       <c r="H227" s="2"/>
       <c r="I227" s="2"/>
     </row>
     <row r="228">
-      <c r="A228" s="5" t="s">
-        <v>242</v>
-      </c>
-      <c r="B228" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C228" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D228" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E228" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A228" s="16"/>
+      <c r="B228" s="17"/>
+      <c r="C228" s="17"/>
+      <c r="D228" s="17"/>
+      <c r="E228" s="17"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
       <c r="H228" s="2"/>
       <c r="I228" s="2"/>
     </row>
     <row r="229">
-      <c r="A229" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="B229" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C229" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D229" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E229" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A229" s="16"/>
+      <c r="B229" s="17"/>
+      <c r="C229" s="17"/>
+      <c r="D229" s="17"/>
+      <c r="E229" s="17"/>
       <c r="F229" s="2"/>
       <c r="G229" s="2"/>
       <c r="H229" s="2"/>
       <c r="I229" s="2"/>
     </row>
     <row r="230">
-      <c r="A230" s="5" t="s">
-        <v>244</v>
-      </c>
-      <c r="B230" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C230" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D230" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E230" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A230" s="16"/>
+      <c r="B230" s="17"/>
+      <c r="C230" s="17"/>
+      <c r="D230" s="17"/>
+      <c r="E230" s="17"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
       <c r="H230" s="2"/>
       <c r="I230" s="2"/>
     </row>
     <row r="231">
-      <c r="A231" s="5" t="s">
-        <v>245</v>
-      </c>
-      <c r="B231" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C231" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D231" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E231" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A231" s="16"/>
+      <c r="B231" s="17"/>
+      <c r="C231" s="17"/>
+      <c r="D231" s="17"/>
+      <c r="E231" s="17"/>
       <c r="F231" s="2"/>
       <c r="G231" s="2"/>
       <c r="H231" s="2"/>
       <c r="I231" s="2"/>
     </row>
     <row r="232">
-      <c r="A232" s="5" t="s">
-        <v>246</v>
-      </c>
-      <c r="B232" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C232" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D232" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E232" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A232" s="16"/>
+      <c r="B232" s="17"/>
+      <c r="C232" s="17"/>
+      <c r="D232" s="17"/>
+      <c r="E232" s="17"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
       <c r="H232" s="2"/>
       <c r="I232" s="2"/>
     </row>
     <row r="233">
-      <c r="A233" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="B233" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C233" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D233" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E233" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A233" s="16"/>
+      <c r="B233" s="17"/>
+      <c r="C233" s="17"/>
+      <c r="D233" s="17"/>
+      <c r="E233" s="17"/>
       <c r="F233" s="2"/>
       <c r="G233" s="2"/>
       <c r="H233" s="2"/>
       <c r="I233" s="2"/>
     </row>
     <row r="234">
-      <c r="A234" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="B234" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C234" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D234" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E234" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A234" s="16"/>
+      <c r="B234" s="17"/>
+      <c r="C234" s="17"/>
+      <c r="D234" s="17"/>
+      <c r="E234" s="17"/>
       <c r="F234" s="2"/>
       <c r="G234" s="2"/>
       <c r="H234" s="2"/>
       <c r="I234" s="2"/>
     </row>
     <row r="235">
-      <c r="A235" s="5" t="s">
-        <v>249</v>
-      </c>
-      <c r="B235" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C235" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D235" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E235" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A235" s="16"/>
+      <c r="B235" s="17"/>
+      <c r="C235" s="17"/>
+      <c r="D235" s="17"/>
+      <c r="E235" s="17"/>
       <c r="F235" s="2"/>
       <c r="G235" s="2"/>
       <c r="H235" s="2"/>
       <c r="I235" s="2"/>
     </row>
     <row r="236">
-      <c r="A236" s="5" t="s">
-        <v>250</v>
-      </c>
-      <c r="B236" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C236" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D236" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E236" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A236" s="16"/>
+      <c r="B236" s="17"/>
+      <c r="C236" s="17"/>
+      <c r="D236" s="17"/>
+      <c r="E236" s="17"/>
       <c r="F236" s="2"/>
       <c r="G236" s="2"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
     </row>
     <row r="237">
-      <c r="A237" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="B237" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C237" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D237" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E237" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A237" s="16"/>
+      <c r="B237" s="17"/>
+      <c r="C237" s="17"/>
+      <c r="D237" s="17"/>
+      <c r="E237" s="17"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
       <c r="H237" s="2"/>
       <c r="I237" s="2"/>
     </row>
     <row r="238">
-      <c r="A238" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="B238" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C238" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D238" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E238" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A238" s="16"/>
+      <c r="B238" s="17"/>
+      <c r="C238" s="17"/>
+      <c r="D238" s="17"/>
+      <c r="E238" s="17"/>
       <c r="F238" s="2"/>
       <c r="G238" s="2"/>
       <c r="H238" s="2"/>
       <c r="I238" s="2"/>
     </row>
     <row r="239">
-      <c r="A239" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B239" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C239" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D239" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E239" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A239" s="16"/>
+      <c r="B239" s="17"/>
+      <c r="C239" s="17"/>
+      <c r="D239" s="17"/>
+      <c r="E239" s="17"/>
       <c r="F239" s="2"/>
       <c r="G239" s="2"/>
       <c r="H239" s="2"/>
       <c r="I239" s="2"/>
     </row>
     <row r="240">
-      <c r="A240" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="B240" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C240" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D240" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E240" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A240" s="16"/>
+      <c r="B240" s="17"/>
+      <c r="C240" s="17"/>
+      <c r="D240" s="17"/>
+      <c r="E240" s="17"/>
       <c r="F240" s="2"/>
       <c r="G240" s="2"/>
       <c r="H240" s="2"/>
       <c r="I240" s="2"/>
     </row>
     <row r="241">
-      <c r="A241" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B241" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C241" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D241" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E241" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A241" s="16"/>
+      <c r="B241" s="17"/>
+      <c r="C241" s="17"/>
+      <c r="D241" s="17"/>
+      <c r="E241" s="17"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
       <c r="H241" s="2"/>
       <c r="I241" s="2"/>
     </row>
     <row r="242">
-      <c r="A242" s="5" t="s">
-        <v>256</v>
-      </c>
-      <c r="B242" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C242" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D242" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E242" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A242" s="16"/>
+      <c r="B242" s="17"/>
+      <c r="C242" s="17"/>
+      <c r="D242" s="17"/>
+      <c r="E242" s="17"/>
       <c r="F242" s="2"/>
       <c r="G242" s="2"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
     </row>
     <row r="243">
-      <c r="A243" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="B243" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C243" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D243" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E243" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A243" s="16"/>
+      <c r="B243" s="17"/>
+      <c r="C243" s="17"/>
+      <c r="D243" s="17"/>
+      <c r="E243" s="17"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
       <c r="H243" s="2"/>
       <c r="I243" s="2"/>
     </row>
     <row r="244">
-      <c r="A244" s="5" t="s">
-        <v>258</v>
-      </c>
-      <c r="B244" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C244" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D244" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E244" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A244" s="16"/>
+      <c r="B244" s="17"/>
+      <c r="C244" s="17"/>
+      <c r="D244" s="17"/>
+      <c r="E244" s="17"/>
       <c r="F244" s="2"/>
       <c r="G244" s="2"/>
       <c r="H244" s="2"/>
       <c r="I244" s="2"/>
     </row>
     <row r="245">
-      <c r="A245" s="5" t="s">
-        <v>259</v>
-      </c>
-      <c r="B245" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C245" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D245" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E245" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A245" s="16"/>
+      <c r="B245" s="17"/>
+      <c r="C245" s="17"/>
+      <c r="D245" s="17"/>
+      <c r="E245" s="17"/>
       <c r="F245" s="2"/>
       <c r="G245" s="2"/>
       <c r="H245" s="2"/>
       <c r="I245" s="2"/>
     </row>
     <row r="246">
-      <c r="A246" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B246" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C246" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D246" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E246" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A246" s="16"/>
+      <c r="B246" s="17"/>
+      <c r="C246" s="17"/>
+      <c r="D246" s="17"/>
+      <c r="E246" s="17"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
       <c r="H246" s="2"/>
       <c r="I246" s="2"/>
     </row>
     <row r="247">
-      <c r="A247" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="B247" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C247" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D247" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E247" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A247" s="16"/>
+      <c r="B247" s="17"/>
+      <c r="C247" s="17"/>
+      <c r="D247" s="17"/>
+      <c r="E247" s="17"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
       <c r="H247" s="2"/>
       <c r="I247" s="2"/>
     </row>
     <row r="248">
-      <c r="A248" s="5" t="s">
-        <v>262</v>
-      </c>
-      <c r="B248" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C248" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D248" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E248" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A248" s="16"/>
+      <c r="B248" s="17"/>
+      <c r="C248" s="17"/>
+      <c r="D248" s="17"/>
+      <c r="E248" s="17"/>
       <c r="F248" s="2"/>
       <c r="G248" s="2"/>
       <c r="H248" s="2"/>
       <c r="I248" s="2"/>
     </row>
     <row r="249">
-      <c r="A249" s="5" t="s">
-        <v>263</v>
-      </c>
-      <c r="B249" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C249" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D249" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="E249" s="6" t="s">
-        <v>10</v>
-      </c>
+      <c r="A249" s="16"/>
+      <c r="B249" s="17"/>
+      <c r="C249" s="17"/>
+      <c r="D249" s="17"/>
+      <c r="E249" s="17"/>
       <c r="F249" s="2"/>
       <c r="G249" s="2"/>
       <c r="H249" s="2"/>
       <c r="I249" s="2"/>
     </row>
     <row r="250">
-      <c r="A250" s="5" t="s">
-        <v>264</v>
-      </c>
-      <c r="B250" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C250" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D250" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E250" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A250" s="16"/>
+      <c r="B250" s="17"/>
+      <c r="C250" s="17"/>
+      <c r="D250" s="17"/>
+      <c r="E250" s="17"/>
       <c r="F250" s="2"/>
       <c r="G250" s="2"/>
       <c r="H250" s="2"/>
       <c r="I250" s="2"/>
     </row>
     <row r="251">
-      <c r="A251" s="5" t="s">
-        <v>265</v>
-      </c>
-      <c r="B251" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C251" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D251" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E251" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A251" s="16"/>
+      <c r="B251" s="17"/>
+      <c r="C251" s="17"/>
+      <c r="D251" s="17"/>
+      <c r="E251" s="17"/>
       <c r="F251" s="2"/>
       <c r="G251" s="2"/>
       <c r="H251" s="2"/>
       <c r="I251" s="2"/>
     </row>
     <row r="252">
-      <c r="A252" s="5" t="s">
-        <v>266</v>
-      </c>
-      <c r="B252" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C252" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D252" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E252" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A252" s="16"/>
+      <c r="B252" s="17"/>
+      <c r="C252" s="17"/>
+      <c r="D252" s="17"/>
+      <c r="E252" s="17"/>
       <c r="F252" s="2"/>
       <c r="G252" s="2"/>
       <c r="H252" s="2"/>
       <c r="I252" s="2"/>
     </row>
     <row r="253">
-      <c r="A253" s="5" t="s">
-        <v>267</v>
-      </c>
-      <c r="B253" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C253" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D253" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E253" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A253" s="16"/>
+      <c r="B253" s="17"/>
+      <c r="C253" s="17"/>
+      <c r="D253" s="17"/>
+      <c r="E253" s="17"/>
       <c r="F253" s="2"/>
       <c r="G253" s="2"/>
       <c r="H253" s="2"/>
       <c r="I253" s="2"/>
     </row>
     <row r="254">
-      <c r="A254" s="5" t="s">
-        <v>268</v>
-      </c>
-      <c r="B254" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C254" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D254" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E254" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A254" s="16"/>
+      <c r="B254" s="17"/>
+      <c r="C254" s="17"/>
+      <c r="D254" s="17"/>
+      <c r="E254" s="17"/>
       <c r="F254" s="2"/>
       <c r="G254" s="2"/>
       <c r="H254" s="2"/>
       <c r="I254" s="2"/>
     </row>
     <row r="255">
-      <c r="A255" s="5" t="s">
-        <v>269</v>
-      </c>
-      <c r="B255" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C255" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D255" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E255" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A255" s="16"/>
+      <c r="B255" s="17"/>
+      <c r="C255" s="17"/>
+      <c r="D255" s="17"/>
+      <c r="E255" s="17"/>
       <c r="F255" s="2"/>
       <c r="G255" s="2"/>
       <c r="H255" s="2"/>
       <c r="I255" s="2"/>
     </row>
     <row r="256">
-      <c r="A256" s="5" t="s">
-        <v>270</v>
-      </c>
-      <c r="B256" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C256" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D256" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E256" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A256" s="16"/>
+      <c r="B256" s="17"/>
+      <c r="C256" s="17"/>
+      <c r="D256" s="17"/>
+      <c r="E256" s="17"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
       <c r="H256" s="2"/>
       <c r="I256" s="2"/>
     </row>
     <row r="257">
-      <c r="A257" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B257" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C257" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D257" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E257" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A257" s="16"/>
+      <c r="B257" s="17"/>
+      <c r="C257" s="17"/>
+      <c r="D257" s="17"/>
+      <c r="E257" s="17"/>
       <c r="F257" s="2"/>
       <c r="G257" s="2"/>
       <c r="H257" s="2"/>
       <c r="I257" s="2"/>
     </row>
     <row r="258">
-      <c r="A258" s="5" t="s">
-        <v>272</v>
-      </c>
-      <c r="B258" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C258" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D258" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E258" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A258" s="16"/>
+      <c r="B258" s="17"/>
+      <c r="C258" s="17"/>
+      <c r="D258" s="17"/>
+      <c r="E258" s="17"/>
       <c r="F258" s="2"/>
       <c r="G258" s="2"/>
       <c r="H258" s="2"/>
       <c r="I258" s="2"/>
     </row>
     <row r="259">
-      <c r="A259" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="B259" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C259" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D259" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E259" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="A259" s="16"/>
+      <c r="B259" s="17"/>
+      <c r="C259" s="17"/>
+      <c r="D259" s="17"/>
+      <c r="E259" s="17"/>
       <c r="F259" s="2"/>
       <c r="G259" s="2"/>
       <c r="H259" s="2"/>
@@ -13442,1034 +12233,11 @@
       <c r="H866" s="2"/>
       <c r="I866" s="2"/>
     </row>
-    <row r="867">
-      <c r="A867" s="16"/>
-      <c r="B867" s="17"/>
-      <c r="C867" s="17"/>
-      <c r="D867" s="17"/>
-      <c r="E867" s="17"/>
-      <c r="F867" s="2"/>
-      <c r="G867" s="2"/>
-      <c r="H867" s="2"/>
-      <c r="I867" s="2"/>
-    </row>
-    <row r="868">
-      <c r="A868" s="16"/>
-      <c r="B868" s="17"/>
-      <c r="C868" s="17"/>
-      <c r="D868" s="17"/>
-      <c r="E868" s="17"/>
-      <c r="F868" s="2"/>
-      <c r="G868" s="2"/>
-      <c r="H868" s="2"/>
-      <c r="I868" s="2"/>
-    </row>
-    <row r="869">
-      <c r="A869" s="16"/>
-      <c r="B869" s="17"/>
-      <c r="C869" s="17"/>
-      <c r="D869" s="17"/>
-      <c r="E869" s="17"/>
-      <c r="F869" s="2"/>
-      <c r="G869" s="2"/>
-      <c r="H869" s="2"/>
-      <c r="I869" s="2"/>
-    </row>
-    <row r="870">
-      <c r="A870" s="16"/>
-      <c r="B870" s="17"/>
-      <c r="C870" s="17"/>
-      <c r="D870" s="17"/>
-      <c r="E870" s="17"/>
-      <c r="F870" s="2"/>
-      <c r="G870" s="2"/>
-      <c r="H870" s="2"/>
-      <c r="I870" s="2"/>
-    </row>
-    <row r="871">
-      <c r="A871" s="16"/>
-      <c r="B871" s="17"/>
-      <c r="C871" s="17"/>
-      <c r="D871" s="17"/>
-      <c r="E871" s="17"/>
-      <c r="F871" s="2"/>
-      <c r="G871" s="2"/>
-      <c r="H871" s="2"/>
-      <c r="I871" s="2"/>
-    </row>
-    <row r="872">
-      <c r="A872" s="16"/>
-      <c r="B872" s="17"/>
-      <c r="C872" s="17"/>
-      <c r="D872" s="17"/>
-      <c r="E872" s="17"/>
-      <c r="F872" s="2"/>
-      <c r="G872" s="2"/>
-      <c r="H872" s="2"/>
-      <c r="I872" s="2"/>
-    </row>
-    <row r="873">
-      <c r="A873" s="16"/>
-      <c r="B873" s="17"/>
-      <c r="C873" s="17"/>
-      <c r="D873" s="17"/>
-      <c r="E873" s="17"/>
-      <c r="F873" s="2"/>
-      <c r="G873" s="2"/>
-      <c r="H873" s="2"/>
-      <c r="I873" s="2"/>
-    </row>
-    <row r="874">
-      <c r="A874" s="16"/>
-      <c r="B874" s="17"/>
-      <c r="C874" s="17"/>
-      <c r="D874" s="17"/>
-      <c r="E874" s="17"/>
-      <c r="F874" s="2"/>
-      <c r="G874" s="2"/>
-      <c r="H874" s="2"/>
-      <c r="I874" s="2"/>
-    </row>
-    <row r="875">
-      <c r="A875" s="16"/>
-      <c r="B875" s="17"/>
-      <c r="C875" s="17"/>
-      <c r="D875" s="17"/>
-      <c r="E875" s="17"/>
-      <c r="F875" s="2"/>
-      <c r="G875" s="2"/>
-      <c r="H875" s="2"/>
-      <c r="I875" s="2"/>
-    </row>
-    <row r="876">
-      <c r="A876" s="16"/>
-      <c r="B876" s="17"/>
-      <c r="C876" s="17"/>
-      <c r="D876" s="17"/>
-      <c r="E876" s="17"/>
-      <c r="F876" s="2"/>
-      <c r="G876" s="2"/>
-      <c r="H876" s="2"/>
-      <c r="I876" s="2"/>
-    </row>
-    <row r="877">
-      <c r="A877" s="16"/>
-      <c r="B877" s="17"/>
-      <c r="C877" s="17"/>
-      <c r="D877" s="17"/>
-      <c r="E877" s="17"/>
-      <c r="F877" s="2"/>
-      <c r="G877" s="2"/>
-      <c r="H877" s="2"/>
-      <c r="I877" s="2"/>
-    </row>
-    <row r="878">
-      <c r="A878" s="16"/>
-      <c r="B878" s="17"/>
-      <c r="C878" s="17"/>
-      <c r="D878" s="17"/>
-      <c r="E878" s="17"/>
-      <c r="F878" s="2"/>
-      <c r="G878" s="2"/>
-      <c r="H878" s="2"/>
-      <c r="I878" s="2"/>
-    </row>
-    <row r="879">
-      <c r="A879" s="16"/>
-      <c r="B879" s="17"/>
-      <c r="C879" s="17"/>
-      <c r="D879" s="17"/>
-      <c r="E879" s="17"/>
-      <c r="F879" s="2"/>
-      <c r="G879" s="2"/>
-      <c r="H879" s="2"/>
-      <c r="I879" s="2"/>
-    </row>
-    <row r="880">
-      <c r="A880" s="16"/>
-      <c r="B880" s="17"/>
-      <c r="C880" s="17"/>
-      <c r="D880" s="17"/>
-      <c r="E880" s="17"/>
-      <c r="F880" s="2"/>
-      <c r="G880" s="2"/>
-      <c r="H880" s="2"/>
-      <c r="I880" s="2"/>
-    </row>
-    <row r="881">
-      <c r="A881" s="16"/>
-      <c r="B881" s="17"/>
-      <c r="C881" s="17"/>
-      <c r="D881" s="17"/>
-      <c r="E881" s="17"/>
-      <c r="F881" s="2"/>
-      <c r="G881" s="2"/>
-      <c r="H881" s="2"/>
-      <c r="I881" s="2"/>
-    </row>
-    <row r="882">
-      <c r="A882" s="16"/>
-      <c r="B882" s="17"/>
-      <c r="C882" s="17"/>
-      <c r="D882" s="17"/>
-      <c r="E882" s="17"/>
-      <c r="F882" s="2"/>
-      <c r="G882" s="2"/>
-      <c r="H882" s="2"/>
-      <c r="I882" s="2"/>
-    </row>
-    <row r="883">
-      <c r="A883" s="16"/>
-      <c r="B883" s="17"/>
-      <c r="C883" s="17"/>
-      <c r="D883" s="17"/>
-      <c r="E883" s="17"/>
-      <c r="F883" s="2"/>
-      <c r="G883" s="2"/>
-      <c r="H883" s="2"/>
-      <c r="I883" s="2"/>
-    </row>
-    <row r="884">
-      <c r="A884" s="16"/>
-      <c r="B884" s="17"/>
-      <c r="C884" s="17"/>
-      <c r="D884" s="17"/>
-      <c r="E884" s="17"/>
-      <c r="F884" s="2"/>
-      <c r="G884" s="2"/>
-      <c r="H884" s="2"/>
-      <c r="I884" s="2"/>
-    </row>
-    <row r="885">
-      <c r="A885" s="16"/>
-      <c r="B885" s="17"/>
-      <c r="C885" s="17"/>
-      <c r="D885" s="17"/>
-      <c r="E885" s="17"/>
-      <c r="F885" s="2"/>
-      <c r="G885" s="2"/>
-      <c r="H885" s="2"/>
-      <c r="I885" s="2"/>
-    </row>
-    <row r="886">
-      <c r="A886" s="16"/>
-      <c r="B886" s="17"/>
-      <c r="C886" s="17"/>
-      <c r="D886" s="17"/>
-      <c r="E886" s="17"/>
-      <c r="F886" s="2"/>
-      <c r="G886" s="2"/>
-      <c r="H886" s="2"/>
-      <c r="I886" s="2"/>
-    </row>
-    <row r="887">
-      <c r="A887" s="16"/>
-      <c r="B887" s="17"/>
-      <c r="C887" s="17"/>
-      <c r="D887" s="17"/>
-      <c r="E887" s="17"/>
-      <c r="F887" s="2"/>
-      <c r="G887" s="2"/>
-      <c r="H887" s="2"/>
-      <c r="I887" s="2"/>
-    </row>
-    <row r="888">
-      <c r="A888" s="16"/>
-      <c r="B888" s="17"/>
-      <c r="C888" s="17"/>
-      <c r="D888" s="17"/>
-      <c r="E888" s="17"/>
-      <c r="F888" s="2"/>
-      <c r="G888" s="2"/>
-      <c r="H888" s="2"/>
-      <c r="I888" s="2"/>
-    </row>
-    <row r="889">
-      <c r="A889" s="16"/>
-      <c r="B889" s="17"/>
-      <c r="C889" s="17"/>
-      <c r="D889" s="17"/>
-      <c r="E889" s="17"/>
-      <c r="F889" s="2"/>
-      <c r="G889" s="2"/>
-      <c r="H889" s="2"/>
-      <c r="I889" s="2"/>
-    </row>
-    <row r="890">
-      <c r="A890" s="16"/>
-      <c r="B890" s="17"/>
-      <c r="C890" s="17"/>
-      <c r="D890" s="17"/>
-      <c r="E890" s="17"/>
-      <c r="F890" s="2"/>
-      <c r="G890" s="2"/>
-      <c r="H890" s="2"/>
-      <c r="I890" s="2"/>
-    </row>
-    <row r="891">
-      <c r="A891" s="16"/>
-      <c r="B891" s="17"/>
-      <c r="C891" s="17"/>
-      <c r="D891" s="17"/>
-      <c r="E891" s="17"/>
-      <c r="F891" s="2"/>
-      <c r="G891" s="2"/>
-      <c r="H891" s="2"/>
-      <c r="I891" s="2"/>
-    </row>
-    <row r="892">
-      <c r="A892" s="16"/>
-      <c r="B892" s="17"/>
-      <c r="C892" s="17"/>
-      <c r="D892" s="17"/>
-      <c r="E892" s="17"/>
-      <c r="F892" s="2"/>
-      <c r="G892" s="2"/>
-      <c r="H892" s="2"/>
-      <c r="I892" s="2"/>
-    </row>
-    <row r="893">
-      <c r="A893" s="16"/>
-      <c r="B893" s="17"/>
-      <c r="C893" s="17"/>
-      <c r="D893" s="17"/>
-      <c r="E893" s="17"/>
-      <c r="F893" s="2"/>
-      <c r="G893" s="2"/>
-      <c r="H893" s="2"/>
-      <c r="I893" s="2"/>
-    </row>
-    <row r="894">
-      <c r="A894" s="16"/>
-      <c r="B894" s="17"/>
-      <c r="C894" s="17"/>
-      <c r="D894" s="17"/>
-      <c r="E894" s="17"/>
-      <c r="F894" s="2"/>
-      <c r="G894" s="2"/>
-      <c r="H894" s="2"/>
-      <c r="I894" s="2"/>
-    </row>
-    <row r="895">
-      <c r="A895" s="16"/>
-      <c r="B895" s="17"/>
-      <c r="C895" s="17"/>
-      <c r="D895" s="17"/>
-      <c r="E895" s="17"/>
-      <c r="F895" s="2"/>
-      <c r="G895" s="2"/>
-      <c r="H895" s="2"/>
-      <c r="I895" s="2"/>
-    </row>
-    <row r="896">
-      <c r="A896" s="16"/>
-      <c r="B896" s="17"/>
-      <c r="C896" s="17"/>
-      <c r="D896" s="17"/>
-      <c r="E896" s="17"/>
-      <c r="F896" s="2"/>
-      <c r="G896" s="2"/>
-      <c r="H896" s="2"/>
-      <c r="I896" s="2"/>
-    </row>
-    <row r="897">
-      <c r="A897" s="16"/>
-      <c r="B897" s="17"/>
-      <c r="C897" s="17"/>
-      <c r="D897" s="17"/>
-      <c r="E897" s="17"/>
-      <c r="F897" s="2"/>
-      <c r="G897" s="2"/>
-      <c r="H897" s="2"/>
-      <c r="I897" s="2"/>
-    </row>
-    <row r="898">
-      <c r="A898" s="16"/>
-      <c r="B898" s="17"/>
-      <c r="C898" s="17"/>
-      <c r="D898" s="17"/>
-      <c r="E898" s="17"/>
-      <c r="F898" s="2"/>
-      <c r="G898" s="2"/>
-      <c r="H898" s="2"/>
-      <c r="I898" s="2"/>
-    </row>
-    <row r="899">
-      <c r="A899" s="16"/>
-      <c r="B899" s="17"/>
-      <c r="C899" s="17"/>
-      <c r="D899" s="17"/>
-      <c r="E899" s="17"/>
-      <c r="F899" s="2"/>
-      <c r="G899" s="2"/>
-      <c r="H899" s="2"/>
-      <c r="I899" s="2"/>
-    </row>
-    <row r="900">
-      <c r="A900" s="16"/>
-      <c r="B900" s="17"/>
-      <c r="C900" s="17"/>
-      <c r="D900" s="17"/>
-      <c r="E900" s="17"/>
-      <c r="F900" s="2"/>
-      <c r="G900" s="2"/>
-      <c r="H900" s="2"/>
-      <c r="I900" s="2"/>
-    </row>
-    <row r="901">
-      <c r="A901" s="16"/>
-      <c r="B901" s="17"/>
-      <c r="C901" s="17"/>
-      <c r="D901" s="17"/>
-      <c r="E901" s="17"/>
-      <c r="F901" s="2"/>
-      <c r="G901" s="2"/>
-      <c r="H901" s="2"/>
-      <c r="I901" s="2"/>
-    </row>
-    <row r="902">
-      <c r="A902" s="16"/>
-      <c r="B902" s="17"/>
-      <c r="C902" s="17"/>
-      <c r="D902" s="17"/>
-      <c r="E902" s="17"/>
-      <c r="F902" s="2"/>
-      <c r="G902" s="2"/>
-      <c r="H902" s="2"/>
-      <c r="I902" s="2"/>
-    </row>
-    <row r="903">
-      <c r="A903" s="16"/>
-      <c r="B903" s="17"/>
-      <c r="C903" s="17"/>
-      <c r="D903" s="17"/>
-      <c r="E903" s="17"/>
-      <c r="F903" s="2"/>
-      <c r="G903" s="2"/>
-      <c r="H903" s="2"/>
-      <c r="I903" s="2"/>
-    </row>
-    <row r="904">
-      <c r="A904" s="16"/>
-      <c r="B904" s="17"/>
-      <c r="C904" s="17"/>
-      <c r="D904" s="17"/>
-      <c r="E904" s="17"/>
-      <c r="F904" s="2"/>
-      <c r="G904" s="2"/>
-      <c r="H904" s="2"/>
-      <c r="I904" s="2"/>
-    </row>
-    <row r="905">
-      <c r="A905" s="16"/>
-      <c r="B905" s="17"/>
-      <c r="C905" s="17"/>
-      <c r="D905" s="17"/>
-      <c r="E905" s="17"/>
-      <c r="F905" s="2"/>
-      <c r="G905" s="2"/>
-      <c r="H905" s="2"/>
-      <c r="I905" s="2"/>
-    </row>
-    <row r="906">
-      <c r="A906" s="16"/>
-      <c r="B906" s="17"/>
-      <c r="C906" s="17"/>
-      <c r="D906" s="17"/>
-      <c r="E906" s="17"/>
-      <c r="F906" s="2"/>
-      <c r="G906" s="2"/>
-      <c r="H906" s="2"/>
-      <c r="I906" s="2"/>
-    </row>
-    <row r="907">
-      <c r="A907" s="16"/>
-      <c r="B907" s="17"/>
-      <c r="C907" s="17"/>
-      <c r="D907" s="17"/>
-      <c r="E907" s="17"/>
-      <c r="F907" s="2"/>
-      <c r="G907" s="2"/>
-      <c r="H907" s="2"/>
-      <c r="I907" s="2"/>
-    </row>
-    <row r="908">
-      <c r="A908" s="16"/>
-      <c r="B908" s="17"/>
-      <c r="C908" s="17"/>
-      <c r="D908" s="17"/>
-      <c r="E908" s="17"/>
-      <c r="F908" s="2"/>
-      <c r="G908" s="2"/>
-      <c r="H908" s="2"/>
-      <c r="I908" s="2"/>
-    </row>
-    <row r="909">
-      <c r="A909" s="16"/>
-      <c r="B909" s="17"/>
-      <c r="C909" s="17"/>
-      <c r="D909" s="17"/>
-      <c r="E909" s="17"/>
-      <c r="F909" s="2"/>
-      <c r="G909" s="2"/>
-      <c r="H909" s="2"/>
-      <c r="I909" s="2"/>
-    </row>
-    <row r="910">
-      <c r="A910" s="16"/>
-      <c r="B910" s="17"/>
-      <c r="C910" s="17"/>
-      <c r="D910" s="17"/>
-      <c r="E910" s="17"/>
-      <c r="F910" s="2"/>
-      <c r="G910" s="2"/>
-      <c r="H910" s="2"/>
-      <c r="I910" s="2"/>
-    </row>
-    <row r="911">
-      <c r="A911" s="16"/>
-      <c r="B911" s="17"/>
-      <c r="C911" s="17"/>
-      <c r="D911" s="17"/>
-      <c r="E911" s="17"/>
-      <c r="F911" s="2"/>
-      <c r="G911" s="2"/>
-      <c r="H911" s="2"/>
-      <c r="I911" s="2"/>
-    </row>
-    <row r="912">
-      <c r="A912" s="16"/>
-      <c r="B912" s="17"/>
-      <c r="C912" s="17"/>
-      <c r="D912" s="17"/>
-      <c r="E912" s="17"/>
-      <c r="F912" s="2"/>
-      <c r="G912" s="2"/>
-      <c r="H912" s="2"/>
-      <c r="I912" s="2"/>
-    </row>
-    <row r="913">
-      <c r="A913" s="16"/>
-      <c r="B913" s="17"/>
-      <c r="C913" s="17"/>
-      <c r="D913" s="17"/>
-      <c r="E913" s="17"/>
-      <c r="F913" s="2"/>
-      <c r="G913" s="2"/>
-      <c r="H913" s="2"/>
-      <c r="I913" s="2"/>
-    </row>
-    <row r="914">
-      <c r="A914" s="16"/>
-      <c r="B914" s="17"/>
-      <c r="C914" s="17"/>
-      <c r="D914" s="17"/>
-      <c r="E914" s="17"/>
-      <c r="F914" s="2"/>
-      <c r="G914" s="2"/>
-      <c r="H914" s="2"/>
-      <c r="I914" s="2"/>
-    </row>
-    <row r="915">
-      <c r="A915" s="16"/>
-      <c r="B915" s="17"/>
-      <c r="C915" s="17"/>
-      <c r="D915" s="17"/>
-      <c r="E915" s="17"/>
-      <c r="F915" s="2"/>
-      <c r="G915" s="2"/>
-      <c r="H915" s="2"/>
-      <c r="I915" s="2"/>
-    </row>
-    <row r="916">
-      <c r="A916" s="16"/>
-      <c r="B916" s="17"/>
-      <c r="C916" s="17"/>
-      <c r="D916" s="17"/>
-      <c r="E916" s="17"/>
-      <c r="F916" s="2"/>
-      <c r="G916" s="2"/>
-      <c r="H916" s="2"/>
-      <c r="I916" s="2"/>
-    </row>
-    <row r="917">
-      <c r="A917" s="16"/>
-      <c r="B917" s="17"/>
-      <c r="C917" s="17"/>
-      <c r="D917" s="17"/>
-      <c r="E917" s="17"/>
-      <c r="F917" s="2"/>
-      <c r="G917" s="2"/>
-      <c r="H917" s="2"/>
-      <c r="I917" s="2"/>
-    </row>
-    <row r="918">
-      <c r="A918" s="16"/>
-      <c r="B918" s="17"/>
-      <c r="C918" s="17"/>
-      <c r="D918" s="17"/>
-      <c r="E918" s="17"/>
-      <c r="F918" s="2"/>
-      <c r="G918" s="2"/>
-      <c r="H918" s="2"/>
-      <c r="I918" s="2"/>
-    </row>
-    <row r="919">
-      <c r="A919" s="16"/>
-      <c r="B919" s="17"/>
-      <c r="C919" s="17"/>
-      <c r="D919" s="17"/>
-      <c r="E919" s="17"/>
-      <c r="F919" s="2"/>
-      <c r="G919" s="2"/>
-      <c r="H919" s="2"/>
-      <c r="I919" s="2"/>
-    </row>
-    <row r="920">
-      <c r="A920" s="16"/>
-      <c r="B920" s="17"/>
-      <c r="C920" s="17"/>
-      <c r="D920" s="17"/>
-      <c r="E920" s="17"/>
-      <c r="F920" s="2"/>
-      <c r="G920" s="2"/>
-      <c r="H920" s="2"/>
-      <c r="I920" s="2"/>
-    </row>
-    <row r="921">
-      <c r="A921" s="16"/>
-      <c r="B921" s="17"/>
-      <c r="C921" s="17"/>
-      <c r="D921" s="17"/>
-      <c r="E921" s="17"/>
-      <c r="F921" s="2"/>
-      <c r="G921" s="2"/>
-      <c r="H921" s="2"/>
-      <c r="I921" s="2"/>
-    </row>
-    <row r="922">
-      <c r="A922" s="16"/>
-      <c r="B922" s="17"/>
-      <c r="C922" s="17"/>
-      <c r="D922" s="17"/>
-      <c r="E922" s="17"/>
-      <c r="F922" s="2"/>
-      <c r="G922" s="2"/>
-      <c r="H922" s="2"/>
-      <c r="I922" s="2"/>
-    </row>
-    <row r="923">
-      <c r="A923" s="16"/>
-      <c r="B923" s="17"/>
-      <c r="C923" s="17"/>
-      <c r="D923" s="17"/>
-      <c r="E923" s="17"/>
-      <c r="F923" s="2"/>
-      <c r="G923" s="2"/>
-      <c r="H923" s="2"/>
-      <c r="I923" s="2"/>
-    </row>
-    <row r="924">
-      <c r="A924" s="16"/>
-      <c r="B924" s="17"/>
-      <c r="C924" s="17"/>
-      <c r="D924" s="17"/>
-      <c r="E924" s="17"/>
-      <c r="F924" s="2"/>
-      <c r="G924" s="2"/>
-      <c r="H924" s="2"/>
-      <c r="I924" s="2"/>
-    </row>
-    <row r="925">
-      <c r="A925" s="16"/>
-      <c r="B925" s="17"/>
-      <c r="C925" s="17"/>
-      <c r="D925" s="17"/>
-      <c r="E925" s="17"/>
-      <c r="F925" s="2"/>
-      <c r="G925" s="2"/>
-      <c r="H925" s="2"/>
-      <c r="I925" s="2"/>
-    </row>
-    <row r="926">
-      <c r="A926" s="16"/>
-      <c r="B926" s="17"/>
-      <c r="C926" s="17"/>
-      <c r="D926" s="17"/>
-      <c r="E926" s="17"/>
-      <c r="F926" s="2"/>
-      <c r="G926" s="2"/>
-      <c r="H926" s="2"/>
-      <c r="I926" s="2"/>
-    </row>
-    <row r="927">
-      <c r="A927" s="16"/>
-      <c r="B927" s="17"/>
-      <c r="C927" s="17"/>
-      <c r="D927" s="17"/>
-      <c r="E927" s="17"/>
-      <c r="F927" s="2"/>
-      <c r="G927" s="2"/>
-      <c r="H927" s="2"/>
-      <c r="I927" s="2"/>
-    </row>
-    <row r="928">
-      <c r="A928" s="16"/>
-      <c r="B928" s="17"/>
-      <c r="C928" s="17"/>
-      <c r="D928" s="17"/>
-      <c r="E928" s="17"/>
-      <c r="F928" s="2"/>
-      <c r="G928" s="2"/>
-      <c r="H928" s="2"/>
-      <c r="I928" s="2"/>
-    </row>
-    <row r="929">
-      <c r="A929" s="16"/>
-      <c r="B929" s="17"/>
-      <c r="C929" s="17"/>
-      <c r="D929" s="17"/>
-      <c r="E929" s="17"/>
-      <c r="F929" s="2"/>
-      <c r="G929" s="2"/>
-      <c r="H929" s="2"/>
-      <c r="I929" s="2"/>
-    </row>
-    <row r="930">
-      <c r="A930" s="16"/>
-      <c r="B930" s="17"/>
-      <c r="C930" s="17"/>
-      <c r="D930" s="17"/>
-      <c r="E930" s="17"/>
-      <c r="F930" s="2"/>
-      <c r="G930" s="2"/>
-      <c r="H930" s="2"/>
-      <c r="I930" s="2"/>
-    </row>
-    <row r="931">
-      <c r="A931" s="16"/>
-      <c r="B931" s="17"/>
-      <c r="C931" s="17"/>
-      <c r="D931" s="17"/>
-      <c r="E931" s="17"/>
-      <c r="F931" s="2"/>
-      <c r="G931" s="2"/>
-      <c r="H931" s="2"/>
-      <c r="I931" s="2"/>
-    </row>
-    <row r="932">
-      <c r="A932" s="16"/>
-      <c r="B932" s="17"/>
-      <c r="C932" s="17"/>
-      <c r="D932" s="17"/>
-      <c r="E932" s="17"/>
-      <c r="F932" s="2"/>
-      <c r="G932" s="2"/>
-      <c r="H932" s="2"/>
-      <c r="I932" s="2"/>
-    </row>
-    <row r="933">
-      <c r="A933" s="16"/>
-      <c r="B933" s="17"/>
-      <c r="C933" s="17"/>
-      <c r="D933" s="17"/>
-      <c r="E933" s="17"/>
-      <c r="F933" s="2"/>
-      <c r="G933" s="2"/>
-      <c r="H933" s="2"/>
-      <c r="I933" s="2"/>
-    </row>
-    <row r="934">
-      <c r="A934" s="16"/>
-      <c r="B934" s="17"/>
-      <c r="C934" s="17"/>
-      <c r="D934" s="17"/>
-      <c r="E934" s="17"/>
-      <c r="F934" s="2"/>
-      <c r="G934" s="2"/>
-      <c r="H934" s="2"/>
-      <c r="I934" s="2"/>
-    </row>
-    <row r="935">
-      <c r="A935" s="16"/>
-      <c r="B935" s="17"/>
-      <c r="C935" s="17"/>
-      <c r="D935" s="17"/>
-      <c r="E935" s="17"/>
-      <c r="F935" s="2"/>
-      <c r="G935" s="2"/>
-      <c r="H935" s="2"/>
-      <c r="I935" s="2"/>
-    </row>
-    <row r="936">
-      <c r="A936" s="16"/>
-      <c r="B936" s="17"/>
-      <c r="C936" s="17"/>
-      <c r="D936" s="17"/>
-      <c r="E936" s="17"/>
-      <c r="F936" s="2"/>
-      <c r="G936" s="2"/>
-      <c r="H936" s="2"/>
-      <c r="I936" s="2"/>
-    </row>
-    <row r="937">
-      <c r="A937" s="16"/>
-      <c r="B937" s="17"/>
-      <c r="C937" s="17"/>
-      <c r="D937" s="17"/>
-      <c r="E937" s="17"/>
-      <c r="F937" s="2"/>
-      <c r="G937" s="2"/>
-      <c r="H937" s="2"/>
-      <c r="I937" s="2"/>
-    </row>
-    <row r="938">
-      <c r="A938" s="16"/>
-      <c r="B938" s="17"/>
-      <c r="C938" s="17"/>
-      <c r="D938" s="17"/>
-      <c r="E938" s="17"/>
-      <c r="F938" s="2"/>
-      <c r="G938" s="2"/>
-      <c r="H938" s="2"/>
-      <c r="I938" s="2"/>
-    </row>
-    <row r="939">
-      <c r="A939" s="16"/>
-      <c r="B939" s="17"/>
-      <c r="C939" s="17"/>
-      <c r="D939" s="17"/>
-      <c r="E939" s="17"/>
-      <c r="F939" s="2"/>
-      <c r="G939" s="2"/>
-      <c r="H939" s="2"/>
-      <c r="I939" s="2"/>
-    </row>
-    <row r="940">
-      <c r="A940" s="16"/>
-      <c r="B940" s="17"/>
-      <c r="C940" s="17"/>
-      <c r="D940" s="17"/>
-      <c r="E940" s="17"/>
-      <c r="F940" s="2"/>
-      <c r="G940" s="2"/>
-      <c r="H940" s="2"/>
-      <c r="I940" s="2"/>
-    </row>
-    <row r="941">
-      <c r="A941" s="16"/>
-      <c r="B941" s="17"/>
-      <c r="C941" s="17"/>
-      <c r="D941" s="17"/>
-      <c r="E941" s="17"/>
-      <c r="F941" s="2"/>
-      <c r="G941" s="2"/>
-      <c r="H941" s="2"/>
-      <c r="I941" s="2"/>
-    </row>
-    <row r="942">
-      <c r="A942" s="16"/>
-      <c r="B942" s="17"/>
-      <c r="C942" s="17"/>
-      <c r="D942" s="17"/>
-      <c r="E942" s="17"/>
-      <c r="F942" s="2"/>
-      <c r="G942" s="2"/>
-      <c r="H942" s="2"/>
-      <c r="I942" s="2"/>
-    </row>
-    <row r="943">
-      <c r="A943" s="16"/>
-      <c r="B943" s="17"/>
-      <c r="C943" s="17"/>
-      <c r="D943" s="17"/>
-      <c r="E943" s="17"/>
-      <c r="F943" s="2"/>
-      <c r="G943" s="2"/>
-      <c r="H943" s="2"/>
-      <c r="I943" s="2"/>
-    </row>
-    <row r="944">
-      <c r="A944" s="16"/>
-      <c r="B944" s="17"/>
-      <c r="C944" s="17"/>
-      <c r="D944" s="17"/>
-      <c r="E944" s="17"/>
-      <c r="F944" s="2"/>
-      <c r="G944" s="2"/>
-      <c r="H944" s="2"/>
-      <c r="I944" s="2"/>
-    </row>
-    <row r="945">
-      <c r="A945" s="16"/>
-      <c r="B945" s="17"/>
-      <c r="C945" s="17"/>
-      <c r="D945" s="17"/>
-      <c r="E945" s="17"/>
-      <c r="F945" s="2"/>
-      <c r="G945" s="2"/>
-      <c r="H945" s="2"/>
-      <c r="I945" s="2"/>
-    </row>
-    <row r="946">
-      <c r="A946" s="16"/>
-      <c r="B946" s="17"/>
-      <c r="C946" s="17"/>
-      <c r="D946" s="17"/>
-      <c r="E946" s="17"/>
-      <c r="F946" s="2"/>
-      <c r="G946" s="2"/>
-      <c r="H946" s="2"/>
-      <c r="I946" s="2"/>
-    </row>
-    <row r="947">
-      <c r="A947" s="16"/>
-      <c r="B947" s="17"/>
-      <c r="C947" s="17"/>
-      <c r="D947" s="17"/>
-      <c r="E947" s="17"/>
-      <c r="F947" s="2"/>
-      <c r="G947" s="2"/>
-      <c r="H947" s="2"/>
-      <c r="I947" s="2"/>
-    </row>
-    <row r="948">
-      <c r="A948" s="16"/>
-      <c r="B948" s="17"/>
-      <c r="C948" s="17"/>
-      <c r="D948" s="17"/>
-      <c r="E948" s="17"/>
-      <c r="F948" s="2"/>
-      <c r="G948" s="2"/>
-      <c r="H948" s="2"/>
-      <c r="I948" s="2"/>
-    </row>
-    <row r="949">
-      <c r="A949" s="16"/>
-      <c r="B949" s="17"/>
-      <c r="C949" s="17"/>
-      <c r="D949" s="17"/>
-      <c r="E949" s="17"/>
-      <c r="F949" s="2"/>
-      <c r="G949" s="2"/>
-      <c r="H949" s="2"/>
-      <c r="I949" s="2"/>
-    </row>
-    <row r="950">
-      <c r="A950" s="16"/>
-      <c r="B950" s="17"/>
-      <c r="C950" s="17"/>
-      <c r="D950" s="17"/>
-      <c r="E950" s="17"/>
-      <c r="F950" s="2"/>
-      <c r="G950" s="2"/>
-      <c r="H950" s="2"/>
-      <c r="I950" s="2"/>
-    </row>
-    <row r="951">
-      <c r="A951" s="16"/>
-      <c r="B951" s="17"/>
-      <c r="C951" s="17"/>
-      <c r="D951" s="17"/>
-      <c r="E951" s="17"/>
-      <c r="F951" s="2"/>
-      <c r="G951" s="2"/>
-      <c r="H951" s="2"/>
-      <c r="I951" s="2"/>
-    </row>
-    <row r="952">
-      <c r="A952" s="16"/>
-      <c r="B952" s="17"/>
-      <c r="C952" s="17"/>
-      <c r="D952" s="17"/>
-      <c r="E952" s="17"/>
-      <c r="F952" s="2"/>
-      <c r="G952" s="2"/>
-      <c r="H952" s="2"/>
-      <c r="I952" s="2"/>
-    </row>
-    <row r="953">
-      <c r="A953" s="16"/>
-      <c r="B953" s="17"/>
-      <c r="C953" s="17"/>
-      <c r="D953" s="17"/>
-      <c r="E953" s="17"/>
-      <c r="F953" s="2"/>
-      <c r="G953" s="2"/>
-      <c r="H953" s="2"/>
-      <c r="I953" s="2"/>
-    </row>
-    <row r="954">
-      <c r="A954" s="16"/>
-      <c r="B954" s="17"/>
-      <c r="C954" s="17"/>
-      <c r="D954" s="17"/>
-      <c r="E954" s="17"/>
-      <c r="F954" s="2"/>
-      <c r="G954" s="2"/>
-      <c r="H954" s="2"/>
-      <c r="I954" s="2"/>
-    </row>
-    <row r="955">
-      <c r="A955" s="16"/>
-      <c r="B955" s="17"/>
-      <c r="C955" s="17"/>
-      <c r="D955" s="17"/>
-      <c r="E955" s="17"/>
-      <c r="F955" s="2"/>
-      <c r="G955" s="2"/>
-      <c r="H955" s="2"/>
-      <c r="I955" s="2"/>
-    </row>
-    <row r="956">
-      <c r="A956" s="16"/>
-      <c r="B956" s="17"/>
-      <c r="C956" s="17"/>
-      <c r="D956" s="17"/>
-      <c r="E956" s="17"/>
-      <c r="F956" s="2"/>
-      <c r="G956" s="2"/>
-      <c r="H956" s="2"/>
-      <c r="I956" s="2"/>
-    </row>
-    <row r="957">
-      <c r="A957" s="16"/>
-      <c r="B957" s="17"/>
-      <c r="C957" s="17"/>
-      <c r="D957" s="17"/>
-      <c r="E957" s="17"/>
-      <c r="F957" s="2"/>
-      <c r="G957" s="2"/>
-      <c r="H957" s="2"/>
-      <c r="I957" s="2"/>
-    </row>
-    <row r="958">
-      <c r="A958" s="16"/>
-      <c r="B958" s="17"/>
-      <c r="C958" s="17"/>
-      <c r="D958" s="17"/>
-      <c r="E958" s="17"/>
-      <c r="F958" s="2"/>
-      <c r="G958" s="2"/>
-      <c r="H958" s="2"/>
-      <c r="I958" s="2"/>
-    </row>
-    <row r="959">
-      <c r="A959" s="16"/>
-      <c r="B959" s="17"/>
-      <c r="C959" s="17"/>
-      <c r="D959" s="17"/>
-      <c r="E959" s="17"/>
-      <c r="F959" s="2"/>
-      <c r="G959" s="2"/>
-      <c r="H959" s="2"/>
-      <c r="I959" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$959">
-    <sortState ref="A1:E959">
-      <sortCondition ref="A1:A959"/>
-      <sortCondition ref="D1:D959"/>
+  <autoFilter ref="$A$1:$E$866">
+    <sortState ref="A1:E866">
+      <sortCondition ref="A1:A866"/>
+      <sortCondition ref="D1:D866"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -14479,13 +12247,13 @@
     <mergeCell ref="G11:I11"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C959">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C866">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D959">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D866">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E959">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E866">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14655,100 +12423,7 @@
     <hyperlink r:id="rId163" ref="A164"/>
     <hyperlink r:id="rId164" ref="A165"/>
     <hyperlink r:id="rId165" ref="A166"/>
-    <hyperlink r:id="rId166" ref="A167"/>
-    <hyperlink r:id="rId167" ref="A168"/>
-    <hyperlink r:id="rId168" ref="A169"/>
-    <hyperlink r:id="rId169" ref="A170"/>
-    <hyperlink r:id="rId170" ref="A171"/>
-    <hyperlink r:id="rId171" ref="A172"/>
-    <hyperlink r:id="rId172" ref="A173"/>
-    <hyperlink r:id="rId173" ref="A174"/>
-    <hyperlink r:id="rId174" ref="A175"/>
-    <hyperlink r:id="rId175" ref="A176"/>
-    <hyperlink r:id="rId176" ref="A177"/>
-    <hyperlink r:id="rId177" ref="A178"/>
-    <hyperlink r:id="rId178" ref="A179"/>
-    <hyperlink r:id="rId179" ref="A180"/>
-    <hyperlink r:id="rId180" ref="A181"/>
-    <hyperlink r:id="rId181" ref="A182"/>
-    <hyperlink r:id="rId182" ref="A183"/>
-    <hyperlink r:id="rId183" ref="A184"/>
-    <hyperlink r:id="rId184" ref="A185"/>
-    <hyperlink r:id="rId185" ref="A186"/>
-    <hyperlink r:id="rId186" ref="A187"/>
-    <hyperlink r:id="rId187" ref="A188"/>
-    <hyperlink r:id="rId188" ref="A189"/>
-    <hyperlink r:id="rId189" ref="A190"/>
-    <hyperlink r:id="rId190" ref="A191"/>
-    <hyperlink r:id="rId191" ref="A192"/>
-    <hyperlink r:id="rId192" ref="A193"/>
-    <hyperlink r:id="rId193" ref="A194"/>
-    <hyperlink r:id="rId194" ref="A195"/>
-    <hyperlink r:id="rId195" ref="A196"/>
-    <hyperlink r:id="rId196" ref="A197"/>
-    <hyperlink r:id="rId197" ref="A198"/>
-    <hyperlink r:id="rId198" ref="A199"/>
-    <hyperlink r:id="rId199" ref="A200"/>
-    <hyperlink r:id="rId200" ref="A201"/>
-    <hyperlink r:id="rId201" ref="A202"/>
-    <hyperlink r:id="rId202" ref="A203"/>
-    <hyperlink r:id="rId203" ref="A204"/>
-    <hyperlink r:id="rId204" ref="A205"/>
-    <hyperlink r:id="rId205" ref="A206"/>
-    <hyperlink r:id="rId206" ref="A207"/>
-    <hyperlink r:id="rId207" ref="A208"/>
-    <hyperlink r:id="rId208" ref="A209"/>
-    <hyperlink r:id="rId209" ref="A210"/>
-    <hyperlink r:id="rId210" ref="A211"/>
-    <hyperlink r:id="rId211" ref="A212"/>
-    <hyperlink r:id="rId212" ref="A213"/>
-    <hyperlink r:id="rId213" ref="A214"/>
-    <hyperlink r:id="rId214" ref="A215"/>
-    <hyperlink r:id="rId215" ref="A216"/>
-    <hyperlink r:id="rId216" ref="A217"/>
-    <hyperlink r:id="rId217" ref="A218"/>
-    <hyperlink r:id="rId218" ref="A219"/>
-    <hyperlink r:id="rId219" ref="A220"/>
-    <hyperlink r:id="rId220" ref="A221"/>
-    <hyperlink r:id="rId221" ref="A222"/>
-    <hyperlink r:id="rId222" ref="A223"/>
-    <hyperlink r:id="rId223" ref="A224"/>
-    <hyperlink r:id="rId224" ref="A225"/>
-    <hyperlink r:id="rId225" ref="A226"/>
-    <hyperlink r:id="rId226" ref="A227"/>
-    <hyperlink r:id="rId227" ref="A228"/>
-    <hyperlink r:id="rId228" ref="A229"/>
-    <hyperlink r:id="rId229" ref="A230"/>
-    <hyperlink r:id="rId230" ref="A231"/>
-    <hyperlink r:id="rId231" ref="A232"/>
-    <hyperlink r:id="rId232" ref="A233"/>
-    <hyperlink r:id="rId233" ref="A234"/>
-    <hyperlink r:id="rId234" ref="A235"/>
-    <hyperlink r:id="rId235" ref="A236"/>
-    <hyperlink r:id="rId236" ref="A237"/>
-    <hyperlink r:id="rId237" ref="A238"/>
-    <hyperlink r:id="rId238" ref="A239"/>
-    <hyperlink r:id="rId239" ref="A240"/>
-    <hyperlink r:id="rId240" ref="A241"/>
-    <hyperlink r:id="rId241" ref="A242"/>
-    <hyperlink r:id="rId242" ref="A243"/>
-    <hyperlink r:id="rId243" ref="A244"/>
-    <hyperlink r:id="rId244" ref="A245"/>
-    <hyperlink r:id="rId245" ref="A246"/>
-    <hyperlink r:id="rId246" ref="A247"/>
-    <hyperlink r:id="rId247" ref="A248"/>
-    <hyperlink r:id="rId248" ref="A249"/>
-    <hyperlink r:id="rId249" ref="A250"/>
-    <hyperlink r:id="rId250" ref="A251"/>
-    <hyperlink r:id="rId251" ref="A252"/>
-    <hyperlink r:id="rId252" ref="A253"/>
-    <hyperlink r:id="rId253" ref="A254"/>
-    <hyperlink r:id="rId254" ref="A255"/>
-    <hyperlink r:id="rId255" ref="A256"/>
-    <hyperlink r:id="rId256" ref="A257"/>
-    <hyperlink r:id="rId257" ref="A258"/>
-    <hyperlink r:id="rId258" ref="A259"/>
   </hyperlinks>
-  <drawing r:id="rId259"/>
+  <drawing r:id="rId166"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$866</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$862</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="178">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -282,25 +282,16 @@
     <t>https://heatlabs.net/guides</t>
   </si>
   <si>
-    <t>https://heatlabs.net/guides/general-guides</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/general-guides/shell-crit-cone-mechanic</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/map-guides</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/tank-guides</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/tank-guides/alvt-players-guide</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/tank-guides/bat-4m-basic-guide</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/tank-guides/xm1-v-build-guide</t>
+    <t>https://heatlabs.net/guides/shell-crit-cone-mechanic</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/guides/alvt-players-guide</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/guides/bat-4m-basic-guide</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/guides/xm1-v-build-guide</t>
   </si>
   <si>
     <t>https://heatlabs.net/legal</t>
@@ -1067,7 +1058,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1077,7 +1068,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4">
@@ -1171,7 +1162,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1181,7 +1172,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -2585,10 +2576,10 @@
         <v>89</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D74" s="6" t="s">
         <v>15</v>
@@ -2602,7 +2593,7 @@
       <c r="I74" s="2"/>
     </row>
     <row r="75">
-      <c r="A75" s="14" t="s">
+      <c r="A75" s="5" t="s">
         <v>90</v>
       </c>
       <c r="B75" s="6" t="s">
@@ -2623,14 +2614,14 @@
       <c r="I75" s="2"/>
     </row>
     <row r="76">
-      <c r="A76" s="14" t="s">
-        <v>90</v>
+      <c r="A76" s="5" t="s">
+        <v>91</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -2645,7 +2636,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>7</v>
@@ -2666,7 +2657,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>7</v>
@@ -2675,10 +2666,10 @@
         <v>7</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -2686,14 +2677,14 @@
       <c r="I78" s="2"/>
     </row>
     <row r="79">
-      <c r="A79" s="14" t="s">
-        <v>93</v>
+      <c r="A79" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B79" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D79" s="6" t="s">
         <v>15</v>
@@ -2707,11 +2698,11 @@
       <c r="I79" s="2"/>
     </row>
     <row r="80">
-      <c r="A80" s="5" t="s">
-        <v>94</v>
+      <c r="A80" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>7</v>
@@ -2729,7 +2720,7 @@
     </row>
     <row r="81">
       <c r="A81" s="5" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>7</v>
@@ -2738,10 +2729,10 @@
         <v>7</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -2750,19 +2741,19 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -2771,7 +2762,7 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>7</v>
@@ -2780,10 +2771,10 @@
         <v>7</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -2791,14 +2782,14 @@
       <c r="I83" s="2"/>
     </row>
     <row r="84">
-      <c r="A84" s="14" t="s">
-        <v>98</v>
+      <c r="A84" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="B84" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="D84" s="6" t="s">
         <v>15</v>
@@ -2813,10 +2804,10 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C85" s="6" t="s">
         <v>7</v>
@@ -2834,19 +2825,19 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -2855,19 +2846,19 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -2876,13 +2867,13 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D88" s="6" t="s">
         <v>15</v>
@@ -2897,19 +2888,19 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B89" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C89" s="6" t="s">
-        <v>7</v>
-      </c>
       <c r="D89" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F89" s="2"/>
       <c r="G89" s="2"/>
@@ -2918,7 +2909,7 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>7</v>
@@ -2927,10 +2918,10 @@
         <v>7</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F90" s="2"/>
       <c r="G90" s="2"/>
@@ -2939,10 +2930,10 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B91" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>7</v>
@@ -2960,13 +2951,13 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B92" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -2981,13 +2972,13 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>15</v>
@@ -3002,7 +2993,7 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
@@ -3023,10 +3014,10 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>7</v>
@@ -3044,13 +3035,13 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D96" s="6" t="s">
         <v>15</v>
@@ -3065,10 +3056,10 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B97" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>7</v>
@@ -3086,10 +3077,10 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B98" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
         <v>7</v>
@@ -3107,13 +3098,13 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3128,10 +3119,10 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>7</v>
@@ -3149,10 +3140,10 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B101" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>7</v>
@@ -3170,19 +3161,19 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3191,19 +3182,19 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F103" s="2"/>
       <c r="G103" s="2"/>
@@ -3212,7 +3203,7 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B104" s="6" t="s">
         <v>7</v>
@@ -3221,10 +3212,10 @@
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3233,7 +3224,7 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -3254,19 +3245,19 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F106" s="2"/>
       <c r="G106" s="2"/>
@@ -3274,8 +3265,8 @@
       <c r="I106" s="2"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="s">
-        <v>121</v>
+      <c r="A107" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>8</v>
@@ -3284,10 +3275,10 @@
         <v>7</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F107" s="2"/>
       <c r="G107" s="2"/>
@@ -3296,7 +3287,7 @@
     </row>
     <row r="108">
       <c r="A108" s="5" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B108" s="6" t="s">
         <v>7</v>
@@ -3305,10 +3296,10 @@
         <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F108" s="2"/>
       <c r="G108" s="2"/>
@@ -3317,7 +3308,7 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -3337,14 +3328,14 @@
       <c r="I109" s="2"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="s">
-        <v>124</v>
+      <c r="A110" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B110" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>15</v>
@@ -3358,11 +3349,11 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="14" t="s">
-        <v>125</v>
+      <c r="A111" s="5" t="s">
+        <v>126</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
         <v>7</v>
@@ -3380,7 +3371,7 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>7</v>
@@ -3401,7 +3392,7 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>7</v>
@@ -3422,7 +3413,7 @@
     </row>
     <row r="114">
       <c r="A114" s="14" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B114" s="6" t="s">
         <v>8</v>
@@ -3443,7 +3434,7 @@
     </row>
     <row r="115">
       <c r="A115" s="5" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B115" s="6" t="s">
         <v>7</v>
@@ -3463,14 +3454,14 @@
       <c r="I115" s="2"/>
     </row>
     <row r="116">
-      <c r="A116" s="5" t="s">
-        <v>130</v>
+      <c r="A116" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>15</v>
@@ -3485,10 +3476,10 @@
     </row>
     <row r="117">
       <c r="A117" s="5" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
@@ -3505,20 +3496,20 @@
       <c r="I117" s="2"/>
     </row>
     <row r="118">
-      <c r="A118" s="14" t="s">
-        <v>132</v>
+      <c r="A118" s="5" t="s">
+        <v>133</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -3527,10 +3518,10 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
@@ -3547,14 +3538,14 @@
       <c r="I119" s="2"/>
     </row>
     <row r="120">
-      <c r="A120" s="14" t="s">
-        <v>134</v>
+      <c r="A120" s="5" t="s">
+        <v>135</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D120" s="6" t="s">
         <v>15</v>
@@ -3569,10 +3560,10 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B121" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>7</v>
@@ -3590,10 +3581,10 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>7</v>
@@ -3611,19 +3602,19 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -3632,7 +3623,7 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>7</v>
@@ -3641,10 +3632,10 @@
         <v>7</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -3652,8 +3643,8 @@
       <c r="I124" s="2"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="s">
-        <v>139</v>
+      <c r="A125" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>7</v>
@@ -3674,10 +3665,10 @@
     </row>
     <row r="126">
       <c r="A126" s="5" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B126" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C126" s="6" t="s">
         <v>7</v>
@@ -3695,7 +3686,7 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
@@ -3704,10 +3695,10 @@
         <v>7</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -3716,7 +3707,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
@@ -3725,10 +3716,10 @@
         <v>7</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F128" s="2"/>
       <c r="G128" s="2"/>
@@ -3736,8 +3727,8 @@
       <c r="I128" s="2"/>
     </row>
     <row r="129">
-      <c r="A129" s="15" t="s">
-        <v>143</v>
+      <c r="A129" s="5" t="s">
+        <v>144</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
@@ -3758,7 +3749,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
@@ -3767,10 +3758,10 @@
         <v>7</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
@@ -3779,7 +3770,7 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
@@ -3800,7 +3791,7 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
@@ -3821,7 +3812,7 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
@@ -3842,13 +3833,13 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>15</v>
@@ -3863,7 +3854,7 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B135" s="6" t="s">
         <v>7</v>
@@ -3883,14 +3874,14 @@
       <c r="I135" s="2"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="s">
-        <v>150</v>
+      <c r="A136" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -3905,7 +3896,7 @@
     </row>
     <row r="137">
       <c r="A137" s="5" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B137" s="6" t="s">
         <v>7</v>
@@ -3926,13 +3917,13 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D138" s="6" t="s">
         <v>15</v>
@@ -3947,7 +3938,7 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>7</v>
@@ -3967,14 +3958,14 @@
       <c r="I139" s="2"/>
     </row>
     <row r="140">
-      <c r="A140" s="14" t="s">
-        <v>154</v>
+      <c r="A140" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="B140" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D140" s="6" t="s">
         <v>15</v>
@@ -3989,7 +3980,7 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>7</v>
@@ -4010,7 +4001,7 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>7</v>
@@ -4031,7 +4022,7 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>7</v>
@@ -4052,7 +4043,7 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>7</v>
@@ -4073,7 +4064,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>7</v>
@@ -4094,7 +4085,7 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>7</v>
@@ -4103,10 +4094,10 @@
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4115,7 +4106,7 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>7</v>
@@ -4136,7 +4127,7 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>7</v>
@@ -4156,14 +4147,14 @@
       <c r="I148" s="2"/>
     </row>
     <row r="149">
-      <c r="A149" s="5" t="s">
-        <v>163</v>
+      <c r="A149" s="14" t="s">
+        <v>164</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>15</v>
@@ -4178,7 +4169,7 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>7</v>
@@ -4187,10 +4178,10 @@
         <v>7</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F150" s="2"/>
       <c r="G150" s="2"/>
@@ -4199,7 +4190,7 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>7</v>
@@ -4220,7 +4211,7 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>7</v>
@@ -4229,10 +4220,10 @@
         <v>7</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
@@ -4240,14 +4231,14 @@
       <c r="I152" s="2"/>
     </row>
     <row r="153">
-      <c r="A153" s="14" t="s">
-        <v>167</v>
+      <c r="A153" s="5" t="s">
+        <v>168</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>15</v>
@@ -4262,7 +4253,7 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>7</v>
@@ -4283,7 +4274,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>7</v>
@@ -4304,7 +4295,7 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>7</v>
@@ -4313,10 +4304,10 @@
         <v>7</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
@@ -4325,13 +4316,13 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B157" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="D157" s="6" t="s">
         <v>15</v>
@@ -4346,13 +4337,13 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D158" s="6" t="s">
         <v>15</v>
@@ -4367,13 +4358,13 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D159" s="6" t="s">
         <v>15</v>
@@ -4388,13 +4379,13 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D160" s="6" t="s">
         <v>15</v>
@@ -4409,7 +4400,7 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>7</v>
@@ -4430,19 +4421,19 @@
     </row>
     <row r="162">
       <c r="A162" s="5" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B162" s="6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="C162" s="6" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="D162" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E162" s="6" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
@@ -4450,84 +4441,44 @@
       <c r="I162" s="2"/>
     </row>
     <row r="163">
-      <c r="A163" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B163" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D163" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E163" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A163" s="16"/>
+      <c r="B163" s="17"/>
+      <c r="C163" s="17"/>
+      <c r="D163" s="17"/>
+      <c r="E163" s="17"/>
       <c r="F163" s="2"/>
       <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
     </row>
     <row r="164">
-      <c r="A164" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="B164" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C164" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D164" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E164" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A164" s="16"/>
+      <c r="B164" s="17"/>
+      <c r="C164" s="17"/>
+      <c r="D164" s="17"/>
+      <c r="E164" s="17"/>
       <c r="F164" s="2"/>
       <c r="G164" s="2"/>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
     </row>
     <row r="165">
-      <c r="A165" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="B165" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C165" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D165" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E165" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A165" s="16"/>
+      <c r="B165" s="17"/>
+      <c r="C165" s="17"/>
+      <c r="D165" s="17"/>
+      <c r="E165" s="17"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
     </row>
     <row r="166">
-      <c r="A166" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="B166" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C166" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D166" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E166" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="A166" s="16"/>
+      <c r="B166" s="17"/>
+      <c r="C166" s="17"/>
+      <c r="D166" s="17"/>
+      <c r="E166" s="17"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
       <c r="H166" s="2"/>
@@ -12189,55 +12140,11 @@
       <c r="H862" s="2"/>
       <c r="I862" s="2"/>
     </row>
-    <row r="863">
-      <c r="A863" s="16"/>
-      <c r="B863" s="17"/>
-      <c r="C863" s="17"/>
-      <c r="D863" s="17"/>
-      <c r="E863" s="17"/>
-      <c r="F863" s="2"/>
-      <c r="G863" s="2"/>
-      <c r="H863" s="2"/>
-      <c r="I863" s="2"/>
-    </row>
-    <row r="864">
-      <c r="A864" s="16"/>
-      <c r="B864" s="17"/>
-      <c r="C864" s="17"/>
-      <c r="D864" s="17"/>
-      <c r="E864" s="17"/>
-      <c r="F864" s="2"/>
-      <c r="G864" s="2"/>
-      <c r="H864" s="2"/>
-      <c r="I864" s="2"/>
-    </row>
-    <row r="865">
-      <c r="A865" s="16"/>
-      <c r="B865" s="17"/>
-      <c r="C865" s="17"/>
-      <c r="D865" s="17"/>
-      <c r="E865" s="17"/>
-      <c r="F865" s="2"/>
-      <c r="G865" s="2"/>
-      <c r="H865" s="2"/>
-      <c r="I865" s="2"/>
-    </row>
-    <row r="866">
-      <c r="A866" s="16"/>
-      <c r="B866" s="17"/>
-      <c r="C866" s="17"/>
-      <c r="D866" s="17"/>
-      <c r="E866" s="17"/>
-      <c r="F866" s="2"/>
-      <c r="G866" s="2"/>
-      <c r="H866" s="2"/>
-      <c r="I866" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$866">
-    <sortState ref="A1:E866">
-      <sortCondition ref="A1:A866"/>
-      <sortCondition ref="D1:D866"/>
+  <autoFilter ref="$A$1:$E$862">
+    <sortState ref="A1:E862">
+      <sortCondition ref="A1:A862"/>
+      <sortCondition ref="D1:D862"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -12247,13 +12154,13 @@
     <mergeCell ref="G11:I11"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C866">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C862">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D866">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D862">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E866">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E862">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12419,11 +12326,7 @@
     <hyperlink r:id="rId159" ref="A160"/>
     <hyperlink r:id="rId160" ref="A161"/>
     <hyperlink r:id="rId161" ref="A162"/>
-    <hyperlink r:id="rId162" ref="A163"/>
-    <hyperlink r:id="rId163" ref="A164"/>
-    <hyperlink r:id="rId164" ref="A165"/>
-    <hyperlink r:id="rId165" ref="A166"/>
   </hyperlinks>
-  <drawing r:id="rId166"/>
+  <drawing r:id="rId162"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$862</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$861</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="823" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="176">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -72,9 +72,6 @@
     <t>https://heatlabs.net/agents</t>
   </si>
   <si>
-    <t>https://heatlabs.net/agents/akira</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/agents/anansi</t>
   </si>
   <si>
@@ -99,6 +96,12 @@
     <t>https://heatlabs.net/agents/flair</t>
   </si>
   <si>
+    <t>https://heatlabs.net/agents/fuzzer</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/agents/gambit</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/agents/hound</t>
   </si>
   <si>
@@ -114,15 +117,12 @@
     <t>https://heatlabs.net/agents/reaper</t>
   </si>
   <si>
+    <t>https://heatlabs.net/agents/twister</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/agents/udarnik</t>
   </si>
   <si>
-    <t>https://heatlabs.net/ai</t>
-  </si>
-  <si>
-    <t>NOT NEEDED</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/asset-gallery</t>
   </si>
   <si>
@@ -492,9 +492,6 @@
     <t>https://heatlabs.net/tanks/ptz89c</t>
   </si>
   <si>
-    <t>https://heatlabs.net/tanks/t-55-enigma</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/tanks/t-62av</t>
   </si>
   <si>
@@ -544,9 +541,6 @@
   </si>
   <si>
     <t>https://status.heatlabs.net</t>
-  </si>
-  <si>
-    <t>https://store.heatlabs.net</t>
   </si>
 </sst>
 </file>
@@ -1058,7 +1052,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1068,7 +1062,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4">
@@ -1162,7 +1156,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1172,7 +1166,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -1192,13 +1186,15 @@
         <v>15</v>
       </c>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
+      <c r="G8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>7</v>
@@ -1213,11 +1209,9 @@
         <v>15</v>
       </c>
       <c r="F9" s="2"/>
-      <c r="G9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H9" s="4"/>
-      <c r="I9" s="4"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
@@ -1236,13 +1230,15 @@
         <v>15</v>
       </c>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
+      <c r="G10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>7</v>
@@ -1257,21 +1253,25 @@
         <v>15</v>
       </c>
       <c r="F11" s="2"/>
-      <c r="G11" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="4"/>
-      <c r="I11" s="4"/>
+      <c r="G11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I11" s="13" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>15</v>
@@ -1280,15 +1280,9 @@
         <v>15</v>
       </c>
       <c r="F12" s="2"/>
-      <c r="G12" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="H12" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>10</v>
-      </c>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
@@ -1319,7 +1313,7 @@
         <v>8</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>15</v>
@@ -1379,7 +1373,7 @@
         <v>31</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>7</v>
@@ -1442,16 +1436,16 @@
         <v>34</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="2"/>
       <c r="G20" s="2"/>
@@ -1460,7 +1454,7 @@
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>7</v>
@@ -1469,10 +1463,10 @@
         <v>7</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
@@ -1481,7 +1475,7 @@
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>7</v>
@@ -1502,19 +1496,19 @@
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F23" s="2"/>
       <c r="G23" s="2"/>
@@ -1523,7 +1517,7 @@
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>8</v>
@@ -1544,7 +1538,7 @@
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>8</v>
@@ -1565,7 +1559,7 @@
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>8</v>
@@ -1586,13 +1580,13 @@
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>15</v>
@@ -1606,11 +1600,11 @@
       <c r="I27" s="2"/>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="s">
-        <v>43</v>
+      <c r="A28" s="5" t="s">
+        <v>42</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>7</v>
@@ -1627,8 +1621,8 @@
       <c r="I28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="s">
-        <v>44</v>
+      <c r="A29" s="14" t="s">
+        <v>43</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>7</v>
@@ -1649,13 +1643,13 @@
     </row>
     <row r="30">
       <c r="A30" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>15</v>
@@ -1670,13 +1664,13 @@
     </row>
     <row r="31">
       <c r="A31" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>15</v>
@@ -1691,7 +1685,7 @@
     </row>
     <row r="32">
       <c r="A32" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>8</v>
@@ -1712,7 +1706,7 @@
     </row>
     <row r="33">
       <c r="A33" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>8</v>
@@ -1721,10 +1715,10 @@
         <v>7</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1733,19 +1727,19 @@
     </row>
     <row r="34">
       <c r="A34" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -1754,7 +1748,7 @@
     </row>
     <row r="35">
       <c r="A35" s="5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>8</v>
@@ -1775,7 +1769,7 @@
     </row>
     <row r="36">
       <c r="A36" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>8</v>
@@ -1796,7 +1790,7 @@
     </row>
     <row r="37">
       <c r="A37" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>8</v>
@@ -1817,7 +1811,7 @@
     </row>
     <row r="38">
       <c r="A38" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B38" s="6" t="s">
         <v>8</v>
@@ -1838,7 +1832,7 @@
     </row>
     <row r="39">
       <c r="A39" s="5" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>8</v>
@@ -1859,13 +1853,13 @@
     </row>
     <row r="40">
       <c r="A40" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>15</v>
@@ -1880,13 +1874,13 @@
     </row>
     <row r="41">
       <c r="A41" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>15</v>
@@ -1901,7 +1895,7 @@
     </row>
     <row r="42">
       <c r="A42" s="5" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>8</v>
@@ -1922,13 +1916,13 @@
     </row>
     <row r="43">
       <c r="A43" s="5" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>15</v>
@@ -1943,7 +1937,7 @@
     </row>
     <row r="44">
       <c r="A44" s="5" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>8</v>
@@ -1964,7 +1958,7 @@
     </row>
     <row r="45">
       <c r="A45" s="5" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>8</v>
@@ -1984,8 +1978,8 @@
       <c r="I45" s="2"/>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="s">
-        <v>61</v>
+      <c r="A46" s="5" t="s">
+        <v>60</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>8</v>
@@ -1994,10 +1988,10 @@
         <v>7</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
@@ -2005,8 +1999,8 @@
       <c r="I46" s="2"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="s">
-        <v>62</v>
+      <c r="A47" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>8</v>
@@ -2027,19 +2021,19 @@
     </row>
     <row r="48">
       <c r="A48" s="5" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B48" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -2047,14 +2041,14 @@
       <c r="I48" s="2"/>
     </row>
     <row r="49">
-      <c r="A49" s="14" t="s">
-        <v>64</v>
+      <c r="A49" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="B49" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>15</v>
@@ -2068,14 +2062,14 @@
       <c r="I49" s="2"/>
     </row>
     <row r="50">
-      <c r="A50" s="5" t="s">
-        <v>65</v>
+      <c r="A50" s="14" t="s">
+        <v>64</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>15</v>
@@ -2090,7 +2084,7 @@
     </row>
     <row r="51">
       <c r="A51" s="5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
@@ -2111,13 +2105,13 @@
     </row>
     <row r="52">
       <c r="A52" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B52" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>15</v>
@@ -2132,19 +2126,19 @@
     </row>
     <row r="53">
       <c r="A53" s="5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C53" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
@@ -2153,19 +2147,19 @@
     </row>
     <row r="54">
       <c r="A54" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -2174,10 +2168,10 @@
     </row>
     <row r="55">
       <c r="A55" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>7</v>
@@ -2195,7 +2189,7 @@
     </row>
     <row r="56">
       <c r="A56" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B56" s="6" t="s">
         <v>8</v>
@@ -2216,13 +2210,13 @@
     </row>
     <row r="57">
       <c r="A57" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B57" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D57" s="6" t="s">
         <v>15</v>
@@ -2237,7 +2231,7 @@
     </row>
     <row r="58">
       <c r="A58" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B58" s="6" t="s">
         <v>8</v>
@@ -2258,13 +2252,13 @@
     </row>
     <row r="59">
       <c r="A59" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B59" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" s="6" t="s">
         <v>15</v>
@@ -2279,13 +2273,13 @@
     </row>
     <row r="60">
       <c r="A60" s="5" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>15</v>
@@ -2300,13 +2294,13 @@
     </row>
     <row r="61">
       <c r="A61" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>15</v>
@@ -2321,13 +2315,13 @@
     </row>
     <row r="62">
       <c r="A62" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B62" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>15</v>
@@ -2342,13 +2336,13 @@
     </row>
     <row r="63">
       <c r="A63" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>15</v>
@@ -2363,10 +2357,10 @@
     </row>
     <row r="64">
       <c r="A64" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B64" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
         <v>7</v>
@@ -2384,10 +2378,10 @@
     </row>
     <row r="65">
       <c r="A65" s="5" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>7</v>
@@ -2405,7 +2399,7 @@
     </row>
     <row r="66">
       <c r="A66" s="5" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B66" s="6" t="s">
         <v>8</v>
@@ -2426,7 +2420,7 @@
     </row>
     <row r="67">
       <c r="A67" s="5" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B67" s="6" t="s">
         <v>8</v>
@@ -2447,7 +2441,7 @@
     </row>
     <row r="68">
       <c r="A68" s="5" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B68" s="6" t="s">
         <v>8</v>
@@ -2468,13 +2462,13 @@
     </row>
     <row r="69">
       <c r="A69" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B69" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D69" s="6" t="s">
         <v>15</v>
@@ -2488,14 +2482,14 @@
       <c r="I69" s="2"/>
     </row>
     <row r="70">
-      <c r="A70" s="14" t="s">
-        <v>85</v>
+      <c r="A70" s="5" t="s">
+        <v>84</v>
       </c>
       <c r="B70" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>15</v>
@@ -2509,20 +2503,20 @@
       <c r="I70" s="2"/>
     </row>
     <row r="71">
-      <c r="A71" s="5" t="s">
-        <v>86</v>
+      <c r="A71" s="14" t="s">
+        <v>85</v>
       </c>
       <c r="B71" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F71" s="2"/>
       <c r="G71" s="2"/>
@@ -2531,7 +2525,7 @@
     </row>
     <row r="72">
       <c r="A72" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B72" s="6" t="s">
         <v>7</v>
@@ -2552,7 +2546,7 @@
     </row>
     <row r="73">
       <c r="A73" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>7</v>
@@ -2573,19 +2567,19 @@
     </row>
     <row r="74">
       <c r="A74" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F74" s="2"/>
       <c r="G74" s="2"/>
@@ -2594,7 +2588,7 @@
     </row>
     <row r="75">
       <c r="A75" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B75" s="6" t="s">
         <v>8</v>
@@ -2615,13 +2609,13 @@
     </row>
     <row r="76">
       <c r="A76" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B76" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D76" s="6" t="s">
         <v>15</v>
@@ -2636,7 +2630,7 @@
     </row>
     <row r="77">
       <c r="A77" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B77" s="6" t="s">
         <v>7</v>
@@ -2657,7 +2651,7 @@
     </row>
     <row r="78">
       <c r="A78" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B78" s="6" t="s">
         <v>7</v>
@@ -2666,10 +2660,10 @@
         <v>7</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F78" s="2"/>
       <c r="G78" s="2"/>
@@ -2678,7 +2672,7 @@
     </row>
     <row r="79">
       <c r="A79" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B79" s="6" t="s">
         <v>7</v>
@@ -2687,10 +2681,10 @@
         <v>7</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -2698,11 +2692,11 @@
       <c r="I79" s="2"/>
     </row>
     <row r="80">
-      <c r="A80" s="14" t="s">
-        <v>95</v>
+      <c r="A80" s="5" t="s">
+        <v>94</v>
       </c>
       <c r="B80" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C80" s="6" t="s">
         <v>7</v>
@@ -2719,20 +2713,20 @@
       <c r="I80" s="2"/>
     </row>
     <row r="81">
-      <c r="A81" s="5" t="s">
-        <v>96</v>
+      <c r="A81" s="14" t="s">
+        <v>95</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F81" s="2"/>
       <c r="G81" s="2"/>
@@ -2741,19 +2735,19 @@
     </row>
     <row r="82">
       <c r="A82" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -2762,19 +2756,19 @@
     </row>
     <row r="83">
       <c r="A83" s="5" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -2783,19 +2777,19 @@
     </row>
     <row r="84">
       <c r="A84" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B84" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -2804,19 +2798,19 @@
     </row>
     <row r="85">
       <c r="A85" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -2825,10 +2819,10 @@
     </row>
     <row r="86">
       <c r="A86" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C86" s="6" t="s">
         <v>7</v>
@@ -2846,19 +2840,19 @@
     </row>
     <row r="87">
       <c r="A87" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F87" s="2"/>
       <c r="G87" s="2"/>
@@ -2867,7 +2861,7 @@
     </row>
     <row r="88">
       <c r="A88" s="5" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B88" s="6" t="s">
         <v>8</v>
@@ -2888,13 +2882,13 @@
     </row>
     <row r="89">
       <c r="A89" s="5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B89" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D89" s="6" t="s">
         <v>15</v>
@@ -2909,13 +2903,13 @@
     </row>
     <row r="90">
       <c r="A90" s="5" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B90" s="6" t="s">
         <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>15</v>
@@ -2930,7 +2924,7 @@
     </row>
     <row r="91">
       <c r="A91" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>7</v>
@@ -2951,13 +2945,13 @@
     </row>
     <row r="92">
       <c r="A92" s="5" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -2972,13 +2966,13 @@
     </row>
     <row r="93">
       <c r="A93" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>15</v>
@@ -2993,7 +2987,7 @@
     </row>
     <row r="94">
       <c r="A94" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B94" s="6" t="s">
         <v>7</v>
@@ -3014,10 +3008,10 @@
     </row>
     <row r="95">
       <c r="A95" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>7</v>
@@ -3035,7 +3029,7 @@
     </row>
     <row r="96">
       <c r="A96" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B96" s="6" t="s">
         <v>8</v>
@@ -3056,7 +3050,7 @@
     </row>
     <row r="97">
       <c r="A97" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B97" s="6" t="s">
         <v>8</v>
@@ -3077,7 +3071,7 @@
     </row>
     <row r="98">
       <c r="A98" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B98" s="6" t="s">
         <v>8</v>
@@ -3098,13 +3092,13 @@
     </row>
     <row r="99">
       <c r="A99" s="5" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B99" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3119,13 +3113,13 @@
     </row>
     <row r="100">
       <c r="A100" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>15</v>
@@ -3140,7 +3134,7 @@
     </row>
     <row r="101">
       <c r="A101" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>7</v>
@@ -3161,7 +3155,7 @@
     </row>
     <row r="102">
       <c r="A102" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B102" s="6" t="s">
         <v>7</v>
@@ -3170,10 +3164,10 @@
         <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3182,10 +3176,10 @@
     </row>
     <row r="103">
       <c r="A103" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>7</v>
@@ -3203,10 +3197,10 @@
     </row>
     <row r="104">
       <c r="A104" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>7</v>
@@ -3224,7 +3218,7 @@
     </row>
     <row r="105">
       <c r="A105" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B105" s="6" t="s">
         <v>7</v>
@@ -3233,10 +3227,10 @@
         <v>7</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -3245,10 +3239,10 @@
     </row>
     <row r="106">
       <c r="A106" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6" t="s">
         <v>7</v>
@@ -3265,8 +3259,8 @@
       <c r="I106" s="2"/>
     </row>
     <row r="107">
-      <c r="A107" s="14" t="s">
-        <v>122</v>
+      <c r="A107" s="5" t="s">
+        <v>121</v>
       </c>
       <c r="B107" s="6" t="s">
         <v>8</v>
@@ -3286,11 +3280,11 @@
       <c r="I107" s="2"/>
     </row>
     <row r="108">
-      <c r="A108" s="5" t="s">
-        <v>123</v>
+      <c r="A108" s="14" t="s">
+        <v>122</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C108" s="6" t="s">
         <v>7</v>
@@ -3308,7 +3302,7 @@
     </row>
     <row r="109">
       <c r="A109" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B109" s="6" t="s">
         <v>7</v>
@@ -3328,14 +3322,14 @@
       <c r="I109" s="2"/>
     </row>
     <row r="110">
-      <c r="A110" s="14" t="s">
-        <v>125</v>
+      <c r="A110" s="5" t="s">
+        <v>124</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>15</v>
@@ -3349,14 +3343,14 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="s">
-        <v>126</v>
+      <c r="A111" s="14" t="s">
+        <v>125</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3371,7 +3365,7 @@
     </row>
     <row r="112">
       <c r="A112" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>7</v>
@@ -3392,7 +3386,7 @@
     </row>
     <row r="113">
       <c r="A113" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>7</v>
@@ -3412,14 +3406,14 @@
       <c r="I113" s="2"/>
     </row>
     <row r="114">
-      <c r="A114" s="14" t="s">
-        <v>129</v>
+      <c r="A114" s="5" t="s">
+        <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D114" s="6" t="s">
         <v>15</v>
@@ -3433,14 +3427,14 @@
       <c r="I114" s="2"/>
     </row>
     <row r="115">
-      <c r="A115" s="5" t="s">
-        <v>130</v>
+      <c r="A115" s="14" t="s">
+        <v>129</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D115" s="6" t="s">
         <v>15</v>
@@ -3454,14 +3448,14 @@
       <c r="I115" s="2"/>
     </row>
     <row r="116">
-      <c r="A116" s="14" t="s">
-        <v>131</v>
+      <c r="A116" s="5" t="s">
+        <v>130</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D116" s="6" t="s">
         <v>15</v>
@@ -3475,14 +3469,14 @@
       <c r="I116" s="2"/>
     </row>
     <row r="117">
-      <c r="A117" s="5" t="s">
-        <v>132</v>
+      <c r="A117" s="14" t="s">
+        <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>15</v>
@@ -3497,19 +3491,19 @@
     </row>
     <row r="118">
       <c r="A118" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -3518,19 +3512,19 @@
     </row>
     <row r="119">
       <c r="A119" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -3539,10 +3533,10 @@
     </row>
     <row r="120">
       <c r="A120" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>7</v>
@@ -3560,7 +3554,7 @@
     </row>
     <row r="121">
       <c r="A121" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>7</v>
@@ -3581,19 +3575,19 @@
     </row>
     <row r="122">
       <c r="A122" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3602,10 +3596,10 @@
     </row>
     <row r="123">
       <c r="A123" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
@@ -3623,7 +3617,7 @@
     </row>
     <row r="124">
       <c r="A124" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B124" s="6" t="s">
         <v>7</v>
@@ -3643,8 +3637,8 @@
       <c r="I124" s="2"/>
     </row>
     <row r="125">
-      <c r="A125" s="15" t="s">
-        <v>140</v>
+      <c r="A125" s="5" t="s">
+        <v>139</v>
       </c>
       <c r="B125" s="6" t="s">
         <v>7</v>
@@ -3653,10 +3647,10 @@
         <v>7</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -3664,8 +3658,8 @@
       <c r="I125" s="2"/>
     </row>
     <row r="126">
-      <c r="A126" s="5" t="s">
-        <v>141</v>
+      <c r="A126" s="15" t="s">
+        <v>140</v>
       </c>
       <c r="B126" s="6" t="s">
         <v>7</v>
@@ -3674,10 +3668,10 @@
         <v>7</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -3686,7 +3680,7 @@
     </row>
     <row r="127">
       <c r="A127" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B127" s="6" t="s">
         <v>7</v>
@@ -3695,10 +3689,10 @@
         <v>7</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -3707,7 +3701,7 @@
     </row>
     <row r="128">
       <c r="A128" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B128" s="6" t="s">
         <v>7</v>
@@ -3728,7 +3722,7 @@
     </row>
     <row r="129">
       <c r="A129" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B129" s="6" t="s">
         <v>7</v>
@@ -3749,7 +3743,7 @@
     </row>
     <row r="130">
       <c r="A130" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B130" s="6" t="s">
         <v>7</v>
@@ -3770,7 +3764,7 @@
     </row>
     <row r="131">
       <c r="A131" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>7</v>
@@ -3791,7 +3785,7 @@
     </row>
     <row r="132">
       <c r="A132" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B132" s="6" t="s">
         <v>7</v>
@@ -3812,7 +3806,7 @@
     </row>
     <row r="133">
       <c r="A133" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>7</v>
@@ -3833,13 +3827,13 @@
     </row>
     <row r="134">
       <c r="A134" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>15</v>
@@ -3854,13 +3848,13 @@
     </row>
     <row r="135">
       <c r="A135" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>15</v>
@@ -3874,14 +3868,14 @@
       <c r="I135" s="2"/>
     </row>
     <row r="136">
-      <c r="A136" s="14" t="s">
-        <v>151</v>
+      <c r="A136" s="5" t="s">
+        <v>150</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -3895,14 +3889,14 @@
       <c r="I136" s="2"/>
     </row>
     <row r="137">
-      <c r="A137" s="5" t="s">
-        <v>152</v>
+      <c r="A137" s="14" t="s">
+        <v>151</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -3917,7 +3911,7 @@
     </row>
     <row r="138">
       <c r="A138" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B138" s="6" t="s">
         <v>7</v>
@@ -3938,7 +3932,7 @@
     </row>
     <row r="139">
       <c r="A139" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B139" s="6" t="s">
         <v>7</v>
@@ -3959,7 +3953,7 @@
     </row>
     <row r="140">
       <c r="A140" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B140" s="6" t="s">
         <v>7</v>
@@ -3980,7 +3974,7 @@
     </row>
     <row r="141">
       <c r="A141" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>7</v>
@@ -4001,7 +3995,7 @@
     </row>
     <row r="142">
       <c r="A142" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B142" s="6" t="s">
         <v>7</v>
@@ -4022,7 +4016,7 @@
     </row>
     <row r="143">
       <c r="A143" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>7</v>
@@ -4043,7 +4037,7 @@
     </row>
     <row r="144">
       <c r="A144" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B144" s="6" t="s">
         <v>7</v>
@@ -4064,7 +4058,7 @@
     </row>
     <row r="145">
       <c r="A145" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B145" s="6" t="s">
         <v>7</v>
@@ -4085,7 +4079,7 @@
     </row>
     <row r="146">
       <c r="A146" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B146" s="6" t="s">
         <v>7</v>
@@ -4106,7 +4100,7 @@
     </row>
     <row r="147">
       <c r="A147" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B147" s="6" t="s">
         <v>7</v>
@@ -4127,7 +4121,7 @@
     </row>
     <row r="148">
       <c r="A148" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B148" s="6" t="s">
         <v>7</v>
@@ -4148,7 +4142,7 @@
     </row>
     <row r="149">
       <c r="A149" s="14" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
         <v>8</v>
@@ -4169,7 +4163,7 @@
     </row>
     <row r="150">
       <c r="A150" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B150" s="6" t="s">
         <v>7</v>
@@ -4190,7 +4184,7 @@
     </row>
     <row r="151">
       <c r="A151" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>7</v>
@@ -4211,7 +4205,7 @@
     </row>
     <row r="152">
       <c r="A152" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
         <v>7</v>
@@ -4232,7 +4226,7 @@
     </row>
     <row r="153">
       <c r="A153" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>8</v>
@@ -4253,7 +4247,7 @@
     </row>
     <row r="154">
       <c r="A154" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B154" s="6" t="s">
         <v>7</v>
@@ -4274,7 +4268,7 @@
     </row>
     <row r="155">
       <c r="A155" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B155" s="6" t="s">
         <v>7</v>
@@ -4295,7 +4289,7 @@
     </row>
     <row r="156">
       <c r="A156" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
         <v>7</v>
@@ -4316,7 +4310,7 @@
     </row>
     <row r="157">
       <c r="A157" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B157" s="6" t="s">
         <v>7</v>
@@ -4337,7 +4331,7 @@
     </row>
     <row r="158">
       <c r="A158" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B158" s="6" t="s">
         <v>8</v>
@@ -4358,7 +4352,7 @@
     </row>
     <row r="159">
       <c r="A159" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B159" s="6" t="s">
         <v>7</v>
@@ -4379,7 +4373,7 @@
     </row>
     <row r="160">
       <c r="A160" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B160" s="6" t="s">
         <v>7</v>
@@ -4400,7 +4394,7 @@
     </row>
     <row r="161">
       <c r="A161" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>7</v>
@@ -4420,21 +4414,11 @@
       <c r="I161" s="2"/>
     </row>
     <row r="162">
-      <c r="A162" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="B162" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="C162" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D162" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="A162" s="16"/>
+      <c r="B162" s="17"/>
+      <c r="C162" s="17"/>
+      <c r="D162" s="17"/>
+      <c r="E162" s="17"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -12129,38 +12113,27 @@
       <c r="H861" s="2"/>
       <c r="I861" s="2"/>
     </row>
-    <row r="862">
-      <c r="A862" s="16"/>
-      <c r="B862" s="17"/>
-      <c r="C862" s="17"/>
-      <c r="D862" s="17"/>
-      <c r="E862" s="17"/>
-      <c r="F862" s="2"/>
-      <c r="G862" s="2"/>
-      <c r="H862" s="2"/>
-      <c r="I862" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$862">
-    <sortState ref="A1:E862">
-      <sortCondition ref="A1:A862"/>
-      <sortCondition ref="D1:D862"/>
+  <autoFilter ref="$A$1:$E$861">
+    <sortState ref="A1:E861">
+      <sortCondition ref="A1:A861"/>
+      <sortCondition ref="D1:D861"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
     <mergeCell ref="G1:I1"/>
     <mergeCell ref="G5:I5"/>
-    <mergeCell ref="G9:I9"/>
-    <mergeCell ref="G11:I11"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="G10:I10"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C862">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C861">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D862">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D861">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E862">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E861">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12325,8 +12298,7 @@
     <hyperlink r:id="rId158" ref="A159"/>
     <hyperlink r:id="rId159" ref="A160"/>
     <hyperlink r:id="rId160" ref="A161"/>
-    <hyperlink r:id="rId161" ref="A162"/>
   </hyperlinks>
-  <drawing r:id="rId162"/>
+  <drawing r:id="rId161"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$861</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$859</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="176">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="174">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -408,9 +408,6 @@
     <t>https://heatlabs.net/playground/tierlist</t>
   </si>
   <si>
-    <t>https://heatlabs.net/playground/weekend-chase-stats</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/playground/wordle</t>
   </si>
   <si>
@@ -523,9 +520,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/tournaments/open-alpha-2-tournament</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/video-showcase</t>
   </si>
   <si>
     <t>https://mods.heatlabs.net</t>
@@ -1052,7 +1046,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1062,7 +1056,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -1156,7 +1150,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1166,7 +1160,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
@@ -3469,14 +3463,14 @@
       <c r="I116" s="2"/>
     </row>
     <row r="117">
-      <c r="A117" s="14" t="s">
+      <c r="A117" s="5" t="s">
         <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D117" s="6" t="s">
         <v>15</v>
@@ -3494,16 +3488,16 @@
         <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -3515,16 +3509,16 @@
         <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -3536,7 +3530,7 @@
         <v>134</v>
       </c>
       <c r="B120" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C120" s="6" t="s">
         <v>7</v>
@@ -3578,16 +3572,16 @@
         <v>136</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3599,7 +3593,7 @@
         <v>137</v>
       </c>
       <c r="B123" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>7</v>
@@ -3637,7 +3631,7 @@
       <c r="I124" s="2"/>
     </row>
     <row r="125">
-      <c r="A125" s="5" t="s">
+      <c r="A125" s="15" t="s">
         <v>139</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -3647,10 +3641,10 @@
         <v>7</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F125" s="2"/>
       <c r="G125" s="2"/>
@@ -3658,7 +3652,7 @@
       <c r="I125" s="2"/>
     </row>
     <row r="126">
-      <c r="A126" s="15" t="s">
+      <c r="A126" s="5" t="s">
         <v>140</v>
       </c>
       <c r="B126" s="6" t="s">
@@ -3668,10 +3662,10 @@
         <v>7</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -3689,10 +3683,10 @@
         <v>7</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F127" s="2"/>
       <c r="G127" s="2"/>
@@ -3830,10 +3824,10 @@
         <v>148</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>15</v>
@@ -3851,10 +3845,10 @@
         <v>149</v>
       </c>
       <c r="B135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>15</v>
@@ -3868,14 +3862,14 @@
       <c r="I135" s="2"/>
     </row>
     <row r="136">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="14" t="s">
         <v>150</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -3889,14 +3883,14 @@
       <c r="I136" s="2"/>
     </row>
     <row r="137">
-      <c r="A137" s="14" t="s">
+      <c r="A137" s="5" t="s">
         <v>151</v>
       </c>
       <c r="B137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D137" s="6" t="s">
         <v>15</v>
@@ -4067,10 +4061,10 @@
         <v>7</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -4088,10 +4082,10 @@
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4120,14 +4114,14 @@
       <c r="I147" s="2"/>
     </row>
     <row r="148">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="14" t="s">
         <v>162</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D148" s="6" t="s">
         <v>15</v>
@@ -4141,14 +4135,14 @@
       <c r="I148" s="2"/>
     </row>
     <row r="149">
-      <c r="A149" s="14" t="s">
+      <c r="A149" s="5" t="s">
         <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D149" s="6" t="s">
         <v>15</v>
@@ -4193,10 +4187,10 @@
         <v>7</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
@@ -4208,16 +4202,16 @@
         <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
@@ -4229,7 +4223,7 @@
         <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>7</v>
@@ -4274,7 +4268,7 @@
         <v>7</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D155" s="6" t="s">
         <v>15</v>
@@ -4292,10 +4286,10 @@
         <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D156" s="6" t="s">
         <v>15</v>
@@ -4334,7 +4328,7 @@
         <v>172</v>
       </c>
       <c r="B158" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C158" s="6" t="s">
         <v>8</v>
@@ -4372,42 +4366,22 @@
       <c r="I159" s="2"/>
     </row>
     <row r="160">
-      <c r="A160" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="B160" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C160" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D160" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E160" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A160" s="16"/>
+      <c r="B160" s="17"/>
+      <c r="C160" s="17"/>
+      <c r="D160" s="17"/>
+      <c r="E160" s="17"/>
       <c r="F160" s="2"/>
       <c r="G160" s="2"/>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
     </row>
     <row r="161">
-      <c r="A161" s="5" t="s">
-        <v>175</v>
-      </c>
-      <c r="B161" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C161" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D161" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E161" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A161" s="16"/>
+      <c r="B161" s="17"/>
+      <c r="C161" s="17"/>
+      <c r="D161" s="17"/>
+      <c r="E161" s="17"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
       <c r="H161" s="2"/>
@@ -12091,33 +12065,11 @@
       <c r="H859" s="2"/>
       <c r="I859" s="2"/>
     </row>
-    <row r="860">
-      <c r="A860" s="16"/>
-      <c r="B860" s="17"/>
-      <c r="C860" s="17"/>
-      <c r="D860" s="17"/>
-      <c r="E860" s="17"/>
-      <c r="F860" s="2"/>
-      <c r="G860" s="2"/>
-      <c r="H860" s="2"/>
-      <c r="I860" s="2"/>
-    </row>
-    <row r="861">
-      <c r="A861" s="16"/>
-      <c r="B861" s="17"/>
-      <c r="C861" s="17"/>
-      <c r="D861" s="17"/>
-      <c r="E861" s="17"/>
-      <c r="F861" s="2"/>
-      <c r="G861" s="2"/>
-      <c r="H861" s="2"/>
-      <c r="I861" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$861">
-    <sortState ref="A1:E861">
-      <sortCondition ref="A1:A861"/>
-      <sortCondition ref="D1:D861"/>
+  <autoFilter ref="$A$1:$E$859">
+    <sortState ref="A1:E859">
+      <sortCondition ref="A1:A859"/>
+      <sortCondition ref="D1:D859"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -12127,13 +12079,13 @@
     <mergeCell ref="G10:I10"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C861">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C859">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D861">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D859">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E861">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E859">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12296,9 +12248,7 @@
     <hyperlink r:id="rId156" ref="A157"/>
     <hyperlink r:id="rId157" ref="A158"/>
     <hyperlink r:id="rId158" ref="A159"/>
-    <hyperlink r:id="rId159" ref="A160"/>
-    <hyperlink r:id="rId160" ref="A161"/>
   </hyperlinks>
-  <drawing r:id="rId161"/>
+  <drawing r:id="rId159"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$859</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$856</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="808" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="171">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -376,15 +376,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/playground/configurator</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/playground/countdown</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/playground/game-data</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/playground/game-servers</t>
   </si>
   <si>
     <t>https://heatlabs.net/playground/heat-labs-app</t>
@@ -1046,7 +1037,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1056,7 +1047,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -1160,7 +1151,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8">
@@ -3257,7 +3248,7 @@
         <v>121</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C107" s="6" t="s">
         <v>7</v>
@@ -3281,7 +3272,7 @@
         <v>8</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>15</v>
@@ -3337,14 +3328,14 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="14" t="s">
+      <c r="A111" s="5" t="s">
         <v>125</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3358,14 +3349,14 @@
       <c r="I111" s="2"/>
     </row>
     <row r="112">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="14" t="s">
         <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -3404,7 +3395,7 @@
         <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>7</v>
@@ -3421,20 +3412,20 @@
       <c r="I114" s="2"/>
     </row>
     <row r="115">
-      <c r="A115" s="14" t="s">
+      <c r="A115" s="5" t="s">
         <v>129</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -3446,7 +3437,7 @@
         <v>130</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>7</v>
@@ -3467,7 +3458,7 @@
         <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
@@ -3494,10 +3485,10 @@
         <v>7</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -3515,10 +3506,10 @@
         <v>7</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F119" s="2"/>
       <c r="G119" s="2"/>
@@ -3536,10 +3527,10 @@
         <v>7</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -3557,10 +3548,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -3568,20 +3559,20 @@
       <c r="I121" s="2"/>
     </row>
     <row r="122">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="15" t="s">
         <v>136</v>
       </c>
       <c r="B122" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C122" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3620,10 +3611,10 @@
         <v>7</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F124" s="2"/>
       <c r="G124" s="2"/>
@@ -3631,7 +3622,7 @@
       <c r="I124" s="2"/>
     </row>
     <row r="125">
-      <c r="A125" s="15" t="s">
+      <c r="A125" s="5" t="s">
         <v>139</v>
       </c>
       <c r="B125" s="6" t="s">
@@ -3662,10 +3653,10 @@
         <v>7</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F126" s="2"/>
       <c r="G126" s="2"/>
@@ -3761,10 +3752,10 @@
         <v>145</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>15</v>
@@ -3799,14 +3790,14 @@
       <c r="I132" s="2"/>
     </row>
     <row r="133">
-      <c r="A133" s="5" t="s">
+      <c r="A133" s="14" t="s">
         <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>15</v>
@@ -3824,10 +3815,10 @@
         <v>148</v>
       </c>
       <c r="B134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D134" s="6" t="s">
         <v>15</v>
@@ -3862,14 +3853,14 @@
       <c r="I135" s="2"/>
     </row>
     <row r="136">
-      <c r="A136" s="14" t="s">
+      <c r="A136" s="5" t="s">
         <v>150</v>
       </c>
       <c r="B136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D136" s="6" t="s">
         <v>15</v>
@@ -3998,10 +3989,10 @@
         <v>7</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -4051,20 +4042,20 @@
       <c r="I144" s="2"/>
     </row>
     <row r="145">
-      <c r="A145" s="5" t="s">
+      <c r="A145" s="14" t="s">
         <v>159</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
@@ -4114,20 +4105,20 @@
       <c r="I147" s="2"/>
     </row>
     <row r="148">
-      <c r="A148" s="14" t="s">
+      <c r="A148" s="5" t="s">
         <v>162</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -4139,7 +4130,7 @@
         <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>7</v>
@@ -4187,10 +4178,10 @@
         <v>7</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F151" s="2"/>
       <c r="G151" s="2"/>
@@ -4202,10 +4193,10 @@
         <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C152" s="6" t="s">
         <v>8</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>7</v>
       </c>
       <c r="D152" s="6" t="s">
         <v>15</v>
@@ -4223,10 +4214,10 @@
         <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D153" s="6" t="s">
         <v>15</v>
@@ -4247,7 +4238,7 @@
         <v>7</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D154" s="6" t="s">
         <v>15</v>
@@ -4286,7 +4277,7 @@
         <v>170</v>
       </c>
       <c r="B156" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C156" s="6" t="s">
         <v>8</v>
@@ -4303,63 +4294,33 @@
       <c r="I156" s="2"/>
     </row>
     <row r="157">
-      <c r="A157" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="B157" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C157" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D157" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E157" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A157" s="16"/>
+      <c r="B157" s="17"/>
+      <c r="C157" s="17"/>
+      <c r="D157" s="17"/>
+      <c r="E157" s="17"/>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
     </row>
     <row r="158">
-      <c r="A158" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="B158" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C158" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E158" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A158" s="16"/>
+      <c r="B158" s="17"/>
+      <c r="C158" s="17"/>
+      <c r="D158" s="17"/>
+      <c r="E158" s="17"/>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
     </row>
     <row r="159">
-      <c r="A159" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="B159" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C159" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D159" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E159" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A159" s="16"/>
+      <c r="B159" s="17"/>
+      <c r="C159" s="17"/>
+      <c r="D159" s="17"/>
+      <c r="E159" s="17"/>
       <c r="F159" s="2"/>
       <c r="G159" s="2"/>
       <c r="H159" s="2"/>
@@ -12032,44 +11993,11 @@
       <c r="H856" s="2"/>
       <c r="I856" s="2"/>
     </row>
-    <row r="857">
-      <c r="A857" s="16"/>
-      <c r="B857" s="17"/>
-      <c r="C857" s="17"/>
-      <c r="D857" s="17"/>
-      <c r="E857" s="17"/>
-      <c r="F857" s="2"/>
-      <c r="G857" s="2"/>
-      <c r="H857" s="2"/>
-      <c r="I857" s="2"/>
-    </row>
-    <row r="858">
-      <c r="A858" s="16"/>
-      <c r="B858" s="17"/>
-      <c r="C858" s="17"/>
-      <c r="D858" s="17"/>
-      <c r="E858" s="17"/>
-      <c r="F858" s="2"/>
-      <c r="G858" s="2"/>
-      <c r="H858" s="2"/>
-      <c r="I858" s="2"/>
-    </row>
-    <row r="859">
-      <c r="A859" s="16"/>
-      <c r="B859" s="17"/>
-      <c r="C859" s="17"/>
-      <c r="D859" s="17"/>
-      <c r="E859" s="17"/>
-      <c r="F859" s="2"/>
-      <c r="G859" s="2"/>
-      <c r="H859" s="2"/>
-      <c r="I859" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$859">
-    <sortState ref="A1:E859">
-      <sortCondition ref="A1:A859"/>
-      <sortCondition ref="D1:D859"/>
+  <autoFilter ref="$A$1:$E$856">
+    <sortState ref="A1:E856">
+      <sortCondition ref="A1:A856"/>
+      <sortCondition ref="D1:D856"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -12079,13 +12007,13 @@
     <mergeCell ref="G10:I10"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C859">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C856">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D859">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D856">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E859">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E856">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12245,10 +12173,7 @@
     <hyperlink r:id="rId153" ref="A154"/>
     <hyperlink r:id="rId154" ref="A155"/>
     <hyperlink r:id="rId155" ref="A156"/>
-    <hyperlink r:id="rId156" ref="A157"/>
-    <hyperlink r:id="rId157" ref="A158"/>
-    <hyperlink r:id="rId158" ref="A159"/>
   </hyperlinks>
-  <drawing r:id="rId159"/>
+  <drawing r:id="rId156"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -6,14 +6,14 @@
     <sheet state="visible" name="pages" sheetId="1" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$856</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">pages!$A$1:$E$854</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="169">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -327,9 +327,6 @@
     <t>https://heatlabs.net/maps/baikonur</t>
   </si>
   <si>
-    <t>https://heatlabs.net/maps/ballistic-range</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/maps/blossom-crash</t>
   </si>
   <si>
@@ -340,9 +337,6 @@
   </si>
   <si>
     <t>https://heatlabs.net/maps/inferno</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/maps/military-training</t>
   </si>
   <si>
     <t>https://heatlabs.net/maps/moonshot</t>
@@ -1047,7 +1041,7 @@
       <c r="I3" s="10">
         <f>COUNTIF(B:B,"INDEXED")
 </f>
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -1141,7 +1135,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1151,7 +1145,7 @@
       <c r="I7" s="10">
         <f>COUNTIF(C:C,"INDEXED")
 </f>
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="8">
@@ -2894,7 +2888,7 @@
         <v>7</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D90" s="6" t="s">
         <v>15</v>
@@ -2933,10 +2927,10 @@
         <v>106</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -2954,10 +2948,10 @@
         <v>107</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>15</v>
@@ -2975,7 +2969,7 @@
         <v>108</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>7</v>
@@ -2996,7 +2990,7 @@
         <v>109</v>
       </c>
       <c r="B95" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>7</v>
@@ -3062,7 +3056,7 @@
         <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>15</v>
@@ -3080,7 +3074,7 @@
         <v>113</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>7</v>
@@ -3101,10 +3095,10 @@
         <v>114</v>
       </c>
       <c r="B100" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>15</v>
@@ -3128,10 +3122,10 @@
         <v>7</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -3143,16 +3137,16 @@
         <v>116</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
@@ -3185,16 +3179,16 @@
         <v>118</v>
       </c>
       <c r="B104" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C104" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3212,10 +3206,10 @@
         <v>7</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F105" s="2"/>
       <c r="G105" s="2"/>
@@ -3223,14 +3217,14 @@
       <c r="I105" s="2"/>
     </row>
     <row r="106">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="14" t="s">
         <v>120</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>15</v>
@@ -3265,14 +3259,14 @@
       <c r="I107" s="2"/>
     </row>
     <row r="108">
-      <c r="A108" s="14" t="s">
+      <c r="A108" s="5" t="s">
         <v>122</v>
       </c>
       <c r="B108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D108" s="6" t="s">
         <v>15</v>
@@ -3307,14 +3301,14 @@
       <c r="I109" s="2"/>
     </row>
     <row r="110">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="14" t="s">
         <v>124</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>15</v>
@@ -3349,14 +3343,14 @@
       <c r="I111" s="2"/>
     </row>
     <row r="112">
-      <c r="A112" s="14" t="s">
+      <c r="A112" s="5" t="s">
         <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D112" s="6" t="s">
         <v>15</v>
@@ -3380,10 +3374,10 @@
         <v>7</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -3422,10 +3416,10 @@
         <v>7</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F115" s="2"/>
       <c r="G115" s="2"/>
@@ -3437,7 +3431,7 @@
         <v>130</v>
       </c>
       <c r="B116" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C116" s="6" t="s">
         <v>7</v>
@@ -3458,16 +3452,16 @@
         <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -3485,10 +3479,10 @@
         <v>7</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F118" s="2"/>
       <c r="G118" s="2"/>
@@ -3500,7 +3494,7 @@
         <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C119" s="6" t="s">
         <v>7</v>
@@ -3517,7 +3511,7 @@
       <c r="I119" s="2"/>
     </row>
     <row r="120">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="15" t="s">
         <v>134</v>
       </c>
       <c r="B120" s="6" t="s">
@@ -3527,10 +3521,10 @@
         <v>7</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -3559,7 +3553,7 @@
       <c r="I121" s="2"/>
     </row>
     <row r="122">
-      <c r="A122" s="15" t="s">
+      <c r="A122" s="5" t="s">
         <v>136</v>
       </c>
       <c r="B122" s="6" t="s">
@@ -3590,10 +3584,10 @@
         <v>7</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F123" s="2"/>
       <c r="G123" s="2"/>
@@ -3710,10 +3704,10 @@
         <v>143</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>15</v>
@@ -3748,7 +3742,7 @@
       <c r="I130" s="2"/>
     </row>
     <row r="131">
-      <c r="A131" s="5" t="s">
+      <c r="A131" s="14" t="s">
         <v>145</v>
       </c>
       <c r="B131" s="6" t="s">
@@ -3790,14 +3784,14 @@
       <c r="I132" s="2"/>
     </row>
     <row r="133">
-      <c r="A133" s="14" t="s">
+      <c r="A133" s="5" t="s">
         <v>147</v>
       </c>
       <c r="B133" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D133" s="6" t="s">
         <v>15</v>
@@ -3947,10 +3941,10 @@
         <v>7</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -3989,10 +3983,10 @@
         <v>7</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F142" s="2"/>
       <c r="G142" s="2"/>
@@ -4000,14 +3994,14 @@
       <c r="I142" s="2"/>
     </row>
     <row r="143">
-      <c r="A143" s="5" t="s">
+      <c r="A143" s="14" t="s">
         <v>157</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4042,14 +4036,14 @@
       <c r="I144" s="2"/>
     </row>
     <row r="145">
-      <c r="A145" s="14" t="s">
+      <c r="A145" s="5" t="s">
         <v>159</v>
       </c>
       <c r="B145" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D145" s="6" t="s">
         <v>15</v>
@@ -4073,10 +4067,10 @@
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4088,7 +4082,7 @@
         <v>161</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>7</v>
@@ -4115,10 +4109,10 @@
         <v>7</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F148" s="2"/>
       <c r="G148" s="2"/>
@@ -4130,7 +4124,7 @@
         <v>163</v>
       </c>
       <c r="B149" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C149" s="6" t="s">
         <v>7</v>
@@ -4154,7 +4148,7 @@
         <v>7</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>15</v>
@@ -4172,10 +4166,10 @@
         <v>165</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D151" s="6" t="s">
         <v>15</v>
@@ -4214,7 +4208,7 @@
         <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>8</v>
@@ -4252,42 +4246,22 @@
       <c r="I154" s="2"/>
     </row>
     <row r="155">
-      <c r="A155" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B155" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C155" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D155" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E155" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A155" s="16"/>
+      <c r="B155" s="17"/>
+      <c r="C155" s="17"/>
+      <c r="D155" s="17"/>
+      <c r="E155" s="17"/>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
     </row>
     <row r="156">
-      <c r="A156" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="B156" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C156" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D156" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="E156" s="6" t="s">
-        <v>15</v>
-      </c>
+      <c r="A156" s="16"/>
+      <c r="B156" s="17"/>
+      <c r="C156" s="17"/>
+      <c r="D156" s="17"/>
+      <c r="E156" s="17"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
@@ -11971,33 +11945,11 @@
       <c r="H854" s="2"/>
       <c r="I854" s="2"/>
     </row>
-    <row r="855">
-      <c r="A855" s="16"/>
-      <c r="B855" s="17"/>
-      <c r="C855" s="17"/>
-      <c r="D855" s="17"/>
-      <c r="E855" s="17"/>
-      <c r="F855" s="2"/>
-      <c r="G855" s="2"/>
-      <c r="H855" s="2"/>
-      <c r="I855" s="2"/>
-    </row>
-    <row r="856">
-      <c r="A856" s="16"/>
-      <c r="B856" s="17"/>
-      <c r="C856" s="17"/>
-      <c r="D856" s="17"/>
-      <c r="E856" s="17"/>
-      <c r="F856" s="2"/>
-      <c r="G856" s="2"/>
-      <c r="H856" s="2"/>
-      <c r="I856" s="2"/>
-    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$E$856">
-    <sortState ref="A1:E856">
-      <sortCondition ref="A1:A856"/>
-      <sortCondition ref="D1:D856"/>
+  <autoFilter ref="$A$1:$E$854">
+    <sortState ref="A1:E854">
+      <sortCondition ref="A1:A854"/>
+      <sortCondition ref="D1:D854"/>
     </sortState>
   </autoFilter>
   <mergeCells count="4">
@@ -12007,13 +11959,13 @@
     <mergeCell ref="G10:I10"/>
   </mergeCells>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C856">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:C854">
       <formula1>"NOT INDEXED,NOT NEEDED,PENDING,INDEXED"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D856">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="D2:D854">
       <formula1>"NOT NEEDED,NOT HTTPS,UNKNOWN,HTTPS"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E856">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="E2:E854">
       <formula1>"NOT NEEDED,INVALID,UNKNOWN,VALID"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12171,9 +12123,7 @@
     <hyperlink r:id="rId151" ref="A152"/>
     <hyperlink r:id="rId152" ref="A153"/>
     <hyperlink r:id="rId153" ref="A154"/>
-    <hyperlink r:id="rId154" ref="A155"/>
-    <hyperlink r:id="rId155" ref="A156"/>
   </hyperlinks>
-  <drawing r:id="rId156"/>
+  <drawing r:id="rId154"/>
 </worksheet>
 </file>
--- a/page-data.xlsx
+++ b/page-data.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="783" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="803" uniqueCount="173">
   <si>
     <t>-PAGE-</t>
   </si>
@@ -138,6 +138,9 @@
     <t>https://heatlabs.net/blog/damage-calculation</t>
   </si>
   <si>
+    <t>https://heatlabs.net/blog/dev-stream-questions-and-answers</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/blog/developer-guide-images</t>
   </si>
   <si>
@@ -282,15 +285,15 @@
     <t>https://heatlabs.net/guides</t>
   </si>
   <si>
+    <t>https://heatlabs.net/guides/alvt-players-guide</t>
+  </si>
+  <si>
+    <t>https://heatlabs.net/guides/bat-4m-basic-guide</t>
+  </si>
+  <si>
     <t>https://heatlabs.net/guides/shell-crit-cone-mechanic</t>
   </si>
   <si>
-    <t>https://heatlabs.net/guides/alvt-players-guide</t>
-  </si>
-  <si>
-    <t>https://heatlabs.net/guides/bat-4m-basic-guide</t>
-  </si>
-  <si>
     <t>https://heatlabs.net/guides/xm1-v-build-guide</t>
   </si>
   <si>
@@ -508,6 +511,15 @@
   </si>
   <si>
     <t>https://mods.heatlabs.net</t>
+  </si>
+  <si>
+    <t>https://mods.heatlabs.net/details/configurator</t>
+  </si>
+  <si>
+    <t>https://mods.heatlabs.net/details/fuse</t>
+  </si>
+  <si>
+    <t>https://mods.heatlabs.net/details/sentinel</t>
   </si>
   <si>
     <t>https://search.heatlabs.net</t>
@@ -692,7 +704,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
@@ -714,13 +726,13 @@
     <xf borderId="1" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="4" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="6" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="6" fillId="5" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -1031,7 +1043,7 @@
       <c r="G3" s="10">
         <f>COUNTIF(B:B,"PENDING")
 </f>
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H3" s="10">
         <f>COUNTIF(B:B,"NOT INDEXED")
@@ -1135,7 +1147,7 @@
       <c r="G7" s="10">
         <f>COUNTIF(C:C,"PENDING")
 </f>
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H7" s="10">
         <f>COUNTIF(C:C,"NOT INDEXED")
@@ -1558,7 +1570,7 @@
       <c r="I26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="14" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="6" t="s">
@@ -1586,7 +1598,7 @@
         <v>8</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>15</v>
@@ -1600,11 +1612,11 @@
       <c r="I28" s="2"/>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="s">
+      <c r="A29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C29" s="6" t="s">
         <v>7</v>
@@ -1621,7 +1633,7 @@
       <c r="I29" s="2"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B30" s="6" t="s">
@@ -1646,10 +1658,10 @@
         <v>45</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>15</v>
@@ -1670,7 +1682,7 @@
         <v>8</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>15</v>
@@ -1715,10 +1727,10 @@
         <v>7</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -1733,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>
@@ -1859,7 +1871,7 @@
         <v>8</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D41" s="6" t="s">
         <v>15</v>
@@ -1880,7 +1892,7 @@
         <v>8</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>15</v>
@@ -1922,7 +1934,7 @@
         <v>8</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>15</v>
@@ -1978,7 +1990,7 @@
       <c r="I46" s="2"/>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="s">
+      <c r="A47" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B47" s="6" t="s">
@@ -1988,10 +2000,10 @@
         <v>7</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F47" s="2"/>
       <c r="G47" s="2"/>
@@ -1999,7 +2011,7 @@
       <c r="I47" s="2"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="14" t="s">
         <v>62</v>
       </c>
       <c r="B48" s="6" t="s">
@@ -2027,13 +2039,13 @@
         <v>8</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
@@ -2041,14 +2053,14 @@
       <c r="I49" s="2"/>
     </row>
     <row r="50">
-      <c r="A50" s="14" t="s">
+      <c r="A50" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B50" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>15</v>
@@ -2062,14 +2074,14 @@
       <c r="I50" s="2"/>
     </row>
     <row r="51">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="14" t="s">
         <v>65</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>15</v>
@@ -2108,10 +2120,10 @@
         <v>67</v>
       </c>
       <c r="B53" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>15</v>
@@ -2129,16 +2141,16 @@
         <v>68</v>
       </c>
       <c r="B54" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C54" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F54" s="2"/>
       <c r="G54" s="2"/>
@@ -2150,16 +2162,16 @@
         <v>69</v>
       </c>
       <c r="B55" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C55" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F55" s="2"/>
       <c r="G55" s="2"/>
@@ -2171,7 +2183,7 @@
         <v>70</v>
       </c>
       <c r="B56" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>7</v>
@@ -2216,7 +2228,7 @@
         <v>8</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D58" s="6" t="s">
         <v>15</v>
@@ -2255,10 +2267,10 @@
         <v>74</v>
       </c>
       <c r="B60" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" s="6" t="s">
         <v>15</v>
@@ -2276,10 +2288,10 @@
         <v>75</v>
       </c>
       <c r="B61" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D61" s="6" t="s">
         <v>15</v>
@@ -2300,7 +2312,7 @@
         <v>8</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>15</v>
@@ -2321,7 +2333,7 @@
         <v>8</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>15</v>
@@ -2342,7 +2354,7 @@
         <v>8</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>15</v>
@@ -2360,7 +2372,7 @@
         <v>79</v>
       </c>
       <c r="B65" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C65" s="6" t="s">
         <v>7</v>
@@ -2381,7 +2393,7 @@
         <v>80</v>
       </c>
       <c r="B66" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C66" s="6" t="s">
         <v>7</v>
@@ -2468,7 +2480,7 @@
         <v>8</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>15</v>
@@ -2482,14 +2494,14 @@
       <c r="I70" s="2"/>
     </row>
     <row r="71">
-      <c r="A71" s="14" t="s">
+      <c r="A71" s="5" t="s">
         <v>85</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>15</v>
@@ -2503,20 +2515,20 @@
       <c r="I71" s="2"/>
     </row>
     <row r="72">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="14" t="s">
         <v>86</v>
       </c>
       <c r="B72" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C72" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F72" s="2"/>
       <c r="G72" s="2"/>
@@ -2570,16 +2582,16 @@
         <v>89</v>
       </c>
       <c r="B75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F75" s="2"/>
       <c r="G75" s="2"/>
@@ -2633,10 +2645,10 @@
         <v>92</v>
       </c>
       <c r="B78" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D78" s="6" t="s">
         <v>15</v>
@@ -2660,10 +2672,10 @@
         <v>7</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F79" s="2"/>
       <c r="G79" s="2"/>
@@ -2681,10 +2693,10 @@
         <v>7</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F80" s="2"/>
       <c r="G80" s="2"/>
@@ -2692,11 +2704,11 @@
       <c r="I80" s="2"/>
     </row>
     <row r="81">
-      <c r="A81" s="14" t="s">
+      <c r="A81" s="5" t="s">
         <v>95</v>
       </c>
       <c r="B81" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>7</v>
@@ -2713,20 +2725,20 @@
       <c r="I81" s="2"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="14" t="s">
         <v>96</v>
       </c>
       <c r="B82" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C82" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
@@ -2738,16 +2750,16 @@
         <v>97</v>
       </c>
       <c r="B83" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2"/>
       <c r="G83" s="2"/>
@@ -2759,16 +2771,16 @@
         <v>98</v>
       </c>
       <c r="B84" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F84" s="2"/>
       <c r="G84" s="2"/>
@@ -2783,13 +2795,13 @@
         <v>7</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F85" s="2"/>
       <c r="G85" s="2"/>
@@ -2801,16 +2813,16 @@
         <v>100</v>
       </c>
       <c r="B86" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F86" s="2"/>
       <c r="G86" s="2"/>
@@ -2822,7 +2834,7 @@
         <v>101</v>
       </c>
       <c r="B87" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C87" s="6" t="s">
         <v>7</v>
@@ -2843,16 +2855,16 @@
         <v>102</v>
       </c>
       <c r="B88" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C88" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F88" s="2"/>
       <c r="G88" s="2"/>
@@ -2885,7 +2897,7 @@
         <v>104</v>
       </c>
       <c r="B90" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C90" s="6" t="s">
         <v>7</v>
@@ -2927,10 +2939,10 @@
         <v>106</v>
       </c>
       <c r="B92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D92" s="6" t="s">
         <v>15</v>
@@ -2948,10 +2960,10 @@
         <v>107</v>
       </c>
       <c r="B93" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D93" s="6" t="s">
         <v>15</v>
@@ -2969,7 +2981,7 @@
         <v>108</v>
       </c>
       <c r="B94" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C94" s="6" t="s">
         <v>7</v>
@@ -3056,7 +3068,7 @@
         <v>8</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D98" s="6" t="s">
         <v>15</v>
@@ -3074,10 +3086,10 @@
         <v>113</v>
       </c>
       <c r="B99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>15</v>
@@ -3122,10 +3134,10 @@
         <v>7</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F101" s="2"/>
       <c r="G101" s="2"/>
@@ -3137,7 +3149,7 @@
         <v>116</v>
       </c>
       <c r="B102" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>7</v>
@@ -3158,7 +3170,7 @@
         <v>117</v>
       </c>
       <c r="B103" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C103" s="6" t="s">
         <v>7</v>
@@ -3185,10 +3197,10 @@
         <v>7</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F104" s="2"/>
       <c r="G104" s="2"/>
@@ -3217,14 +3229,14 @@
       <c r="I105" s="2"/>
     </row>
     <row r="106">
-      <c r="A106" s="14" t="s">
+      <c r="A106" s="5" t="s">
         <v>120</v>
       </c>
       <c r="B106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D106" s="6" t="s">
         <v>15</v>
@@ -3238,14 +3250,14 @@
       <c r="I106" s="2"/>
     </row>
     <row r="107">
-      <c r="A107" s="5" t="s">
+      <c r="A107" s="14" t="s">
         <v>121</v>
       </c>
       <c r="B107" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D107" s="6" t="s">
         <v>15</v>
@@ -3301,14 +3313,14 @@
       <c r="I109" s="2"/>
     </row>
     <row r="110">
-      <c r="A110" s="14" t="s">
+      <c r="A110" s="5" t="s">
         <v>124</v>
       </c>
       <c r="B110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D110" s="6" t="s">
         <v>15</v>
@@ -3322,14 +3334,14 @@
       <c r="I110" s="2"/>
     </row>
     <row r="111">
-      <c r="A111" s="5" t="s">
+      <c r="A111" s="14" t="s">
         <v>125</v>
       </c>
       <c r="B111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D111" s="6" t="s">
         <v>15</v>
@@ -3347,7 +3359,7 @@
         <v>126</v>
       </c>
       <c r="B112" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>7</v>
@@ -3368,16 +3380,16 @@
         <v>127</v>
       </c>
       <c r="B113" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
@@ -3389,16 +3401,16 @@
         <v>128</v>
       </c>
       <c r="B114" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C114" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F114" s="2"/>
       <c r="G114" s="2"/>
@@ -3410,7 +3422,7 @@
         <v>129</v>
       </c>
       <c r="B115" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C115" s="6" t="s">
         <v>7</v>
@@ -3452,16 +3464,16 @@
         <v>131</v>
       </c>
       <c r="B117" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F117" s="2"/>
       <c r="G117" s="2"/>
@@ -3473,7 +3485,7 @@
         <v>132</v>
       </c>
       <c r="B118" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>7</v>
@@ -3521,10 +3533,10 @@
         <v>7</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F120" s="2"/>
       <c r="G120" s="2"/>
@@ -3542,10 +3554,10 @@
         <v>7</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
@@ -3563,10 +3575,10 @@
         <v>7</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
@@ -3704,10 +3716,10 @@
         <v>143</v>
       </c>
       <c r="B129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D129" s="6" t="s">
         <v>15</v>
@@ -3725,10 +3737,10 @@
         <v>144</v>
       </c>
       <c r="B130" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D130" s="6" t="s">
         <v>15</v>
@@ -3742,14 +3754,14 @@
       <c r="I130" s="2"/>
     </row>
     <row r="131">
-      <c r="A131" s="14" t="s">
+      <c r="A131" s="5" t="s">
         <v>145</v>
       </c>
       <c r="B131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D131" s="6" t="s">
         <v>15</v>
@@ -3763,14 +3775,14 @@
       <c r="I131" s="2"/>
     </row>
     <row r="132">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="14" t="s">
         <v>146</v>
       </c>
       <c r="B132" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D132" s="6" t="s">
         <v>15</v>
@@ -3941,10 +3953,10 @@
         <v>7</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
@@ -3962,10 +3974,10 @@
         <v>7</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
@@ -3994,14 +4006,14 @@
       <c r="I142" s="2"/>
     </row>
     <row r="143">
-      <c r="A143" s="14" t="s">
+      <c r="A143" s="5" t="s">
         <v>157</v>
       </c>
       <c r="B143" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D143" s="6" t="s">
         <v>15</v>
@@ -4015,14 +4027,14 @@
       <c r="I143" s="2"/>
     </row>
     <row r="144">
-      <c r="A144" s="5" t="s">
+      <c r="A144" s="14" t="s">
         <v>158</v>
       </c>
       <c r="B144" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D144" s="6" t="s">
         <v>15</v>
@@ -4067,10 +4079,10 @@
         <v>7</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
@@ -4082,16 +4094,16 @@
         <v>161</v>
       </c>
       <c r="B147" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C147" s="6" t="s">
         <v>7</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
@@ -4103,7 +4115,7 @@
         <v>162</v>
       </c>
       <c r="B148" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C148" s="6" t="s">
         <v>7</v>
@@ -4148,7 +4160,7 @@
         <v>7</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D150" s="6" t="s">
         <v>15</v>
@@ -4166,7 +4178,7 @@
         <v>165</v>
       </c>
       <c r="B151" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C151" s="6" t="s">
         <v>8</v>
@@ -4183,11 +4195,11 @@
       <c r="I151" s="2"/>
     </row>
     <row r="152">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="14" t="s">
         <v>166</v>
       </c>
       <c r="B152" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C152" s="6" t="s">
         <v>8</v>
@@ -4204,11 +4216,11 @@
       <c r="I152" s="2"/>
     </row>
     <row r="153">
-      <c r="A153" s="5" t="s">
+      <c r="A153" s="14" t="s">
         <v>167</v>
       </c>
       <c r="B153" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C153" s="6" t="s">
         <v>8</v>
@@ -4225,11 +4237,11 @@
       <c r="I153" s="2"/>
     </row>
     <row r="154">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="14" t="s">
         <v>168</v>
       </c>
       <c r="B154" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C154" s="6" t="s">
         <v>8</v>
@@ -4246,44 +4258,84 @@
       <c r="I154" s="2"/>
     </row>
     <row r="155">
-      <c r="A155" s="16"/>
-      <c r="B155" s="17"/>
-      <c r="C155" s="17"/>
-      <c r="D155" s="17"/>
-      <c r="E155" s="17"/>
+      <c r="A155" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D155" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E155" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F155" s="2"/>
       <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
     </row>
     <row r="156">
-      <c r="A156" s="16"/>
-      <c r="B156" s="17"/>
-      <c r="C156" s="17"/>
-      <c r="D156" s="17"/>
-      <c r="E156" s="17"/>
+      <c r="A156" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D156" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E156" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
     </row>
     <row r="157">
-      <c r="A157" s="16"/>
-      <c r="B157" s="17"/>
-      <c r="C157" s="17"/>
-      <c r="D157" s="17"/>
-      <c r="E157" s="17"/>
+      <c r="A157" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B157" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D157" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E157" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F157" s="2"/>
       <c r="G157" s="2"/>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
     </row>
     <row r="158">
-      <c r="A158" s="16"/>
-      <c r="B158" s="17"/>
-      <c r="C158" s="17"/>
-      <c r="D158" s="17"/>
-      <c r="E158" s="17"/>
+      <c r="A158" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="B158" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E158" s="6" t="s">
+        <v>15</v>
+      </c>
       <c r="F158" s="2"/>
       <c r="G158" s="2"/>
       <c r="H158" s="2"/>
@@ -12123,7 +12175,11 @@
     <hyperlink r:id="rId151" ref="A152"/>
     <hyperlink r:id="rId152" ref="A153"/>
     <hyperlink r:id="rId153" ref="A154"/>
+    <hyperlink r:id="rId154" ref="A155"/>
+    <hyperlink r:id="rId155" ref="A156"/>
+    <hyperlink r:id="rId156" ref="A157"/>
+    <hyperlink r:id="rId157" ref="A158"/>
   </hyperlinks>
-  <drawing r:id="rId154"/>
+  <drawing r:id="rId158"/>
 </worksheet>
 </file>